--- a/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0007.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0007.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Sử dụng Móc Neo tăng Sát Thương Basic Attack của Resonator thêm {1} trong {0} giây, tối đa {2} lần.</t>
+          <t>Sử dụng Móc Neo tăng Sát Thương Đòn Basic Attack của Resonator thêm {1} trong {0} giây, tối đa {2} lần.</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Kích hoạt Intro Skill sẽ tăng Tấn Công cho tất cả thành viên trong đội thêm {1} trong {0} giây, có thể cộng dồn tối đa {2} lần.</t>
+          <t>Kích hoạt Kỹ Năng Khởi Động sẽ tăng ATK cho tất cả thành viên trong đội thêm {1} trong {0} giây, có thể cộng dồn tối đa {2} lần.</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Sát thương Intro Skill của toàn đội tăng {0}. Sau khi sử dụng Intro Skill, Crit. Rate của toàn đội tăng {2} trong {1} giây.</t>
+          <t>DMG Kỹ Năng Khởi Động của toàn đội tăng {0}. Sau khi sử dụng Kỹ Năng Khởi Động, Crit. Rate của toàn đội tăng {2} trong {1} giây.</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Khi có khiên, Tấn Công và Phòng Ngự tăng thêm {0}.</t>
+          <t>Khi có khiên, ATK và Phòng Ngự tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Sử dụng Móc Neo tạo khiên có độ bền bằng {0} sức Tấn Công. Hiệu ứng này có Cooldown {1} giây.</t>
+          <t>Sử dụng Móc Neo tạo khiên có độ bền bằng {0} sức ATK. Hiệu ứng này có Thời gian hồi {1} giây.</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Khi được hồi máu, tất cả Resonators trong đội nhận thêm {0} Heavy Attack và Tăng Năng Lượng được tăng {1}. Hiệu ứng kéo dài {2} giây và có thể chồng chất lên đến {3} lần.</t>
+          <t>Khi được hồi máu, tất cả Resonator trong đội nhận thêm {0} Heavy Attack và Tăng Năng Lượng được tăng {1}. Hiệu ứng kéo dài {2} giây và có thể chồng chất lên đến {3} lần.</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Khi sử dụng Heavy Attack, hồi phục thêm {0} Resonance Energy và giảm Cooldown chiêu Resonance Liberation của tất cả thành viên trong đội đi {1} giây. Hiệu ứng này có Cooldown chiêu là {2} giây.</t>
+          <t>Khi sử dụng Đòn Heavy Attack, hồi phục thêm {0} Resonance Energy và giảm Thời gian hồi chiêu Resonance Liberation của tất cả thành viên trong đội đi {1} giây. Hiệu ứng này có Thời gian hồi chiêu là {2} giây.</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Sau khi sử dụng Resonance Liberation, Tái Tạo Năng Lượng của tất cả Resonators trong đội tăng thêm {0} trong {1} giây. Cứ mỗi {2} Tái Tạo Năng Lượng của người sử dụng, tất cả thành viên trong đội sẽ nhận được tăng Crit. DMG trong {3} giây.</t>
+          <t>Sau khi sử dụng Resonance Liberation, Tái Tạo Năng Lượng của tất cả Resonator trong đội tăng thêm {0} trong {1} giây. Cứ mỗi {2} Tái Tạo Năng Lượng của người sử dụng, tất cả thành viên trong đội sẽ nhận được tăng Sát Thương Bạo Kích trong {3} giây.</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Khi bị tấn công, Crit. Rate của tất cả thành viên trong đội tăng {1} trong {0} giây và Crit. DMG tăng {2}.</t>
+          <t>Khi bị tấn công, Crit. Rate của tất cả thành viên trong đội tăng {1} trong {0} giây và Sát Thương Bạo Kích tăng {2}.</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Nhận {0} Tăng Sát Thương Basic Attack.</t>
+          <t>Nhận {0} Tăng Sát Thương Đòn Cơ Bản.</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Increase Tấn Công thêm {0}.</t>
+          <t>Tăng ATK thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Increase Tấn Công cho tất cả thành viên trong đội thêm 50.</t>
+          <t>Tăng ATK cho tất cả thành viên trong đội thêm 50.</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Increase Crit. Rate thêm {0}.</t>
+          <t>Tăng Crit. Rate thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Increase Crit. DMG thêm {0}.</t>
+          <t>Tăng Crit. DMG thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Nhận thêm {0} Tăng Sát Thương Heavy Attack.</t>
+          <t>Nhận thêm {0} Tăng Sát Thương Đòn Heavy Attack.</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Increase Tái Tạo Năng Lượng thêm {0}.</t>
+          <t>Tăng Tái Tạo Năng Lượng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Increase HP tối đa thêm {0}.</t>
+          <t>Tăng HP tối đa thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Tất cả Resonators trong đội nhận được {0} Tăng Sát Thương Thuộc Tính.</t>
+          <t>Tất cả Resonator trong đội nhận được {0} Tăng Sát Thương Thuộc Tính.</t>
         </is>
       </c>
     </row>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Nightmares đã xé toạc màn thực tại, gieo rắc hỗn loạn khắp thế gian. Chỉ còn mình ngươi có thể khôi phục trật tự đang sụp đổ, với ân huệ huyền bí Illusive Sprint nhận được từ con mèo trắng kỳ lạ.</t>
+          <t>Ác Mộng đã xé toạc màn thực tại, gieo rắc hỗn loạn khắp thế gian. Chỉ còn mình ngươi có thể khôi phục trật tự đang sụp đổ, với ân huệ huyền bí Illusive Sprint nhận được từ con mèo trắng kỳ lạ.</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Nightmares đã xé toạc màn thực tại, gieo rắc hỗn loạn khắp thế gian. Chỉ còn mình ngươi có thể khôi phục trật tự đang sụp đổ, với ân huệ huyền bí Illusive Sprint nhận được từ con mèo trắng kỳ lạ.</t>
+          <t>Ác Mộng đã xé toạc màn thực tại, gieo rắc hỗn loạn khắp thế gian. Chỉ còn mình ngươi có thể khôi phục trật tự đang sụp đổ, với ân huệ huyền bí Illusive Sprint nhận được từ con mèo trắng kỳ lạ.</t>
         </is>
       </c>
     </row>
@@ -2074,8 +2074,8 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Nightmares đã xé toạc màn thực tại, gieo rắc hỗn loạn khắp thế gian. Chỉ còn mình ngươi có thể khôi phục trật tự đang sụp đổ, với ân huệ huyền bí Illusive Sprint nhận được từ con mèo trắng kỳ lạ.
-&lt;color=#c25757&gt;Complete Nhiệm Vụ Chính "When the Snow Clears" to unlock the event.&lt;/color&gt;</t>
+          <t>Ác Mộng đã xé toạc màn thực tại, gieo rắc hỗn loạn khắp thế gian. Chỉ còn mình ngươi có thể khôi phục trật tự đang sụp đổ, với ân huệ huyền bí Illusive Sprint nhận được từ con mèo trắng kỳ lạ.
+&lt;color=#c25757&gt;Hoàn thành Nhiệm Vụ Chính "Khi Tuyết Tan" để mở khóa sự kiện.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -2141,8 +2141,8 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Nightmares đã xé toạc màn thực tại, gieo rắc hỗn loạn khắp thế gian. Chỉ còn mình ngươi có thể khôi phục trật tự đang sụp đổ, với ân huệ huyền bí Illusive Sprint nhận được từ con mèo trắng kỳ lạ.
-&lt;color=#c25757&gt;Complete Nhiệm Vụ Chính "From the Echoes of Destruction" to unlock the event.&lt;/color&gt;</t>
+          <t>Ác Mộng đã xé toạc màn thực tại, gieo rắc hỗn loạn khắp thế gian. Chỉ còn mình ngươi có thể khôi phục trật tự đang sụp đổ, với ân huệ huyền bí Illusive Sprint nhận được từ con mèo trắng kỳ lạ.
+&lt;color=#c25757&gt;Hoàn thành Nhiệm Vụ Chính "Từ Tiếng Vọng Hủy Diệt" để mở khóa sự kiện.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Nightmares đã xé toạc màn thực tại, gieo rắc hỗn loạn khắp thế gian. Chỉ còn mình ngươi có thể khôi phục trật tự đang sụp đổ, với ân huệ huyền bí Illusive Sprint nhận được từ con mèo trắng kỳ lạ.</t>
+          <t>Ác Mộng đã xé toạc màn thực tại, gieo rắc hỗn loạn khắp thế gian. Chỉ còn mình ngươi có thể khôi phục trật tự đang sụp đổ, với ân huệ huyền bí Illusive Sprint nhận được từ con mèo trắng kỳ lạ.</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Nightmares đã xé toạc màn thực tại, gieo rắc hỗn loạn khắp thế gian. Chỉ còn mình ngươi có thể khôi phục trật tự đang sụp đổ, với ân huệ huyền bí Illusive Sprint nhận được từ con mèo trắng kỳ lạ.</t>
+          <t>Ác Mộng đã xé toạc màn thực tại, gieo rắc hỗn loạn khắp thế gian. Chỉ còn mình ngươi có thể khôi phục trật tự đang sụp đổ, với ân huệ huyền bí Illusive Sprint nhận được từ con mèo trắng kỳ lạ.</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Nightmares đã xé toạc màn thực tại, gieo rắc hỗn loạn khắp thế gian. Chỉ còn mình ngươi có thể khôi phục trật tự đang sụp đổ, với ân huệ huyền bí Illusive Sprint nhận được từ con mèo trắng kỳ lạ.</t>
+          <t>Ác Mộng đã xé toạc màn thực tại, gieo rắc hỗn loạn khắp thế gian. Chỉ còn mình ngươi có thể khôi phục trật tự đang sụp đổ, với ân huệ huyền bí Illusive Sprint nhận được từ con mèo trắng kỳ lạ.</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Tấn công mục tiêu bằng Basic Attack sẽ tăng {0}% Sát Thương Resonance Skill cho tất cả thành viên trong đội trong {1} giây. Hiệu ứng này có thể kích hoạt &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2} mỗi giây, tối đa {3} lần.</t>
+          <t>Tấn công mục tiêu bằng Đòn Cơ Bản sẽ tăng {0}% Sát Thương Resonance Skill cho tất cả thành viên trong đội trong {1} giây. Hiệu ứng này có thể kích hoạt &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2} mỗi giây, tối đa {3} lần.</t>
         </is>
       </c>
     </row>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Liberation giúp Resonator nhận {0}% Tăng Sát Thương Kỹ Năng Basic trong {1} giây.</t>
+          <t>Kích hoạt Giải Cứu Cộng Hưởng giúp Resonator nhận {0}% Tăng Sát Thương Kỹ Năng Cơ Bản trong {1} giây.</t>
         </is>
       </c>
     </row>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Nhận thêm {0}% Glacio DMG Bonus. Sử dụng Resonance Skill sẽ nhận được &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=tầng P=tầng SapTag=1} Ice Plume trong {2} giây. Khi đạt {3} tầng, toàn bộ tầng Ice Plume sẽ được xóa để tăng Sát Thương gây ra của tất cả thành viên trong đội thêm {4}% trong {5} giây.</t>
+          <t>Nhận thêm {0}% Tăng Sát Thương Glacio. Sử dụng Resonance Skill sẽ nhận được &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=tầng P=tầng SapTag=1} Ice Plume trong {2} giây. Khi đạt {3} tầng, toàn bộ tầng Ice Plume sẽ được xóa để tăng Sát Thương gây ra của tất cả thành viên trong đội thêm {4}% trong {5} giây.</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Nhận thêm {0}% Electro DMG Bonus. Sử dụng Resonance Skill sẽ tăng thêm {1}% Electro DMG trong {2} giây. Hiệu ứng này có thể kích hoạt &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=3} mỗi giây, tối đa {4} tầng.</t>
+          <t>Nhận thêm {0}% Tăng Sát Thương Electro. Sử dụng Resonance Skill sẽ tăng thêm {1}% Sát Thương Electro trong {2} giây. Hiệu ứng này có thể kích hoạt &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=3} mỗi giây, tối đa {4} tầng.</t>
         </is>
       </c>
     </row>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Gây sát thương bằng Kỹ Năng Basic sẽ tăng {0}% Sát Thương Kỹ Năng Basic cho toàn đội trong {1} giây. Hiệu ứng này kích hoạt &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=mỗi giây SapTag=2}, có thể chồng chất lên đến {3} lần. Khi đạt {4} tầng, sát thương của toàn đội sẽ tăng thêm {5}%.</t>
+          <t>Gây DMG bằng Kỹ Năng Cơ Bản sẽ tăng {0}% Sát Thương Kỹ Năng Cơ Bản cho toàn đội trong {1} giây. Hiệu ứng này kích hoạt &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=mỗi giây SapTag=2}, có thể chồng chất lên đến {3} lần. Khi đạt {4} tầng, DMG của toàn đội sẽ tăng thêm {5}%.</t>
         </is>
       </c>
     </row>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Increase Tái Tạo Resonance cho tất cả thành viên trong đội thêm {0}%. Khi sử dụng Resonance Liberation, tăng Tốc Độ Energy Regen cho tất cả thành viên trong đội thêm {1}% trong {2} giây. Hiệu ứng này có thể kích hoạt &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=3} mỗi giây, tối đa {4} lần.</t>
+          <t>Tăng Tái Tạo Cộng Hưởng cho tất cả thành viên trong đội thêm {0}%. Khi sử dụng Resonance Liberation, tăng Tốc Độ Hồi Năng Lượng cho tất cả thành viên trong đội thêm {1}% trong {2} giây. Hiệu ứng này có thể kích hoạt &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=3} mỗi giây, tối đa {4} lần.</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Hồi phục một Resonator trong đội sẽ tăng Tấn Công cho tất cả thành viên trong đội thêm {0}% trong {1} giây. Hiệu ứng này có thể kích hoạt &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2} mỗi giây, tối đa {3} lần.</t>
+          <t>Hồi phục một Resonator trong đội sẽ tăng ATK cho tất cả thành viên trong đội thêm {0}% trong {1} giây. Hiệu ứng này có thể kích hoạt &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2} mỗi giây, tối đa {3} lần.</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Nhận thêm {0}% Sát Thương Nguyên Tố Spectro. Hiệu ứng này giảm {2}% mỗi {1} giây cho đến khi còn {3}%. Sử dụng Resonance Liberation sẽ bổ sung thêm {4}% Spectro DMG, tối đa {5}%.</t>
+          <t>Nhận thêm {0}% Sát Thương Nguyên Tố Spectro. Hiệu ứng này giảm {2}% mỗi {1} giây cho đến khi còn {3}%. Sử dụng Resonance Liberation sẽ bổ sung thêm {4}% Sát Thương Spectro, tối đa {5}%.</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Sử dụng Basic Attack hoặc Resonance Skill sẽ tăng Sát Thương Resonance Skill của Resonator lên {0}% trong {1} giây. Hiệu ứng này có thể kích hoạt &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2} mỗi giây, chồng chất tối đa {3} lần.</t>
+          <t>Sử dụng Đòn Basic Attack hoặc Resonance Skill sẽ tăng Sát Thương Resonance Skill của Resonator lên {0}% trong {1} giây. Hiệu ứng này có thể kích hoạt &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2} mỗi giây, chồng chất tối đa {3} lần.</t>
         </is>
       </c>
     </row>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Nhận thêm {0}% Aero DMG Bonus. Hiệu ứng này giảm {2}% mỗi {1} giây cho đến khi còn {3}%. Sử dụng Resonance Liberation sẽ tăng thêm {4}% Aero DMG Bonus, tối đa {5}%.</t>
+          <t>Nhận thêm {0}% Tăng Sát Thương Aero. Hiệu ứng này giảm {2}% mỗi {1} giây cho đến khi còn {3}%. Sử dụng Resonance Liberation sẽ tăng thêm {4}% Tăng Sát Thương Aero, tối đa {5}%.</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Nhận thêm {0}% Electro DMG Bonus. Sử dụng Basic Attack sẽ tăng thêm {1}% Electro DMG Bonus cho tất cả thành viên trong đội trong {2} giây, tối đa {3} tầng.</t>
+          <t>Nhận thêm {0}% Tăng Sát Thương Electro. Sử dụng Đòn Basic Attack sẽ tăng thêm {1}% Tăng Sát Thương Electro cho tất cả thành viên trong đội trong {2} giây, tối đa {3} tầng.</t>
         </is>
       </c>
     </row>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Tăng {0}% Sát Thương Tàn Phá. Basic Attack cũng gây thêm {1}% Sát Thương Tàn Phá cho Resonator. Hiệu ứng này có thể kích hoạt &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2} mỗi giây, tối đa {3} tầng. Tất cả sẽ bị xóa khi nhận sát thương.</t>
+          <t>Tăng {0}% Sát Thương Tàn Phá. Đòn tấn công cơ bản cũng gây thêm {1}% Sát Thương Tàn Phá cho Resonator. Hiệu ứng này có thể kích hoạt &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2} mỗi giây, tối đa {3} tầng. Tất cả sẽ bị xóa khi nhận DMG.</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Liberation tăng Tấn Công của tất cả thành viên trong đội lên {0}% và hồi {1} Resonance Energy. Hiệu ứng này có thể kích hoạt &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=3} mỗi {2} giây, tối đa {4} lần.</t>
+          <t>Kích hoạt Resonance Liberation tăng ATK của tất cả thành viên trong đội lên {0}% và hồi {1} Resonance Energy. Hiệu ứng này có thể kích hoạt &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=3} mỗi {2} giây, tối đa {4} lần.</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Tăng Intro Skill</t>
+          <t>Tăng Cường Kỹ Năng Khởi Động</t>
         </is>
       </c>
     </row>
@@ -3314,9 +3314,9 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Dodge thành công tăng hiệu suất tiến trình Hạng Combat lên {0}% trong {1} giây.
-Hạng ≥ B: Dodge thành công hồi {2} Resonance Energy cho tất cả thành viên trong đội.
-Hạng ≥ S: Dodge thành công tăng Sát Thương của tất cả thành viên trong đội lên {3}% trong {4} giây.</t>
+          <t>Né tránh thành công tăng hiệu suất tiến trình Hạng Chiến Đấu lên {0}% trong {1} giây.
+Hạng ≥ B: Né tránh thành công hồi {2} Resonance Energy cho tất cả thành viên trong đội.
+Hạng ≥ S: Né tránh thành công tăng Sát Thương của tất cả thành viên trong đội lên {3}% trong {4} giây.</t>
         </is>
       </c>
     </row>
@@ -3383,9 +3383,9 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Counterattack tăng hiệu suất tiến trình Hạng Combat lên {0}% trong {1} giây.
-Hạng ≥ B: Counterattack tăng Sát Thương của tất cả thành viên trong đội lên {2}% trong {3} giây.
-Hạng ≥ S: Counterattack làm mới Cooldown chiêu Resonance Skill của Resonator đang kích hoạt.</t>
+          <t>Phản công tăng hiệu suất tiến trình Hạng Chiến Đấu lên {0}% trong {1} giây.
+Hạng ≥ B: Counterattack increases the DMG dealt by all team members by {2}% for {3}s.
+Rank ≥ S: Counterattack resets the active Resonator's Resonance Skill Thời gian hồi.</t>
         </is>
       </c>
     </row>
@@ -3452,8 +3452,8 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Khi một thành viên trong đội đang ở trên không, hiệu suất tăng tiến Cấp Combat được tăng thêm {0}%.
-Cấp ≥ B: Increase {1}% Sát Thương gây ra bởi Resonator khi ở trên không.
+          <t>Khi một thành viên trong đội đang ở trên không, hiệu suất tăng tiến Cấp Chiến Đấu được tăng thêm {0}%.
+Cấp ≥ B: Tăng {1}% Sát Thương gây ra bởi Resonator khi ở trên không.
 Cấp ≥ S: Thêm vào đó, tăng {2}% Sát Thương gây ra bởi Resonator khi ở trên không.</t>
         </is>
       </c>
@@ -3521,9 +3521,9 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Skill Khởi Động tăng hiệu suất tiến trình Cấp Độ Combat lên {0}% trong {1} giây.
-Cấp ≥ B: Skill Khởi Động hồi {2} Concerto Energy cho Resonator.
-Cấp ≥ S: Skill Khởi Động tăng Sát Thương gây ra bởi tất cả thành viên trong đội lên {3}% trong {4} giây.</t>
+          <t>Kỹ năng Khởi Động tăng hiệu suất tiến trình Cấp Độ Chiến Đấu lên {0}% trong {1} giây.
+Cấp ≥ B: Kỹ năng Khởi Động hồi {2} Concerto Energy cho Resonator.
+Cấp ≥ S: Kỹ năng Khởi Động tăng Sát Thương gây ra bởi tất cả thành viên trong đội lên {3}% trong {4} giây.</t>
         </is>
       </c>
     </row>
@@ -3590,9 +3590,9 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Skill Echo tăng hiệu suất tiến trình Hạng Combat lên {0}% trong {1} giây.
-Hạng ≥ B: Cooldown chiêu Skill Echo giảm {2}%.
-Hạng ≥ S: Sát thương Skill Echo tăng {3}%.</t>
+          <t>Kỹ năng Echo tăng hiệu suất tiến trình Hạng Chiến Đấu lên {0}% trong {1} giây.
+Hạng ≥ B: Thời gian hồi chiêu Kỹ năng Echo giảm {2}%.
+Hạng ≥ S: DMG Kỹ năng Echo tăng {3}%.</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Cộng Hưởng Hoành Tráng</t>
+          <t>Đại Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Trong {0} giây, Cooldown chiêu Kỹ Năng Echo giảm {1}%.</t>
+          <t>Trong {0} giây, Thời gian hồi chiêu Kỹ Năng Echo giảm {1}%.</t>
         </is>
       </c>
     </row>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Khi nhận sát thương, phục hồi 20% HP tối đa của Resonator. Hiệu ứng này chỉ có thể kích hoạt 3 lần.</t>
+          <t>Khi nhận DMG, phục hồi 20% HP tối đa của Resonator. Hiệu ứng này chỉ có thể kích hoạt 3 lần.</t>
         </is>
       </c>
     </row>
@@ -4635,10 +4635,10 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Hiệu Ứng Special:
+          <t>Hiệu Ứng Đặc Biệt:
 Tiêu diệt kẻ địch sẽ nhận thêm Năng Lượng Đồng Bộ.
 Kẻ Địch Mạnh Hơn:
-Một số kẻ địch bị cuồng loạn bởi sức mạnh của những cơn ác mộng, có Kháng Đòn và Concerto Vibrancy cao hơn.</t>
+Một số kẻ địch bị cuồng loạn bởi sức mạnh của những cơn ác mộng, có Kháng Đòn và Sức Mạnh Rung Động cao hơn.</t>
         </is>
       </c>
     </row>
@@ -4706,10 +4706,10 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Hiệu Ứng Special:
+          <t>Hiệu Ứng Đặc Biệt:
 Tiêu diệt kẻ địch sẽ nhận thêm Năng Lượng Đồng Bộ.
 Kẻ Địch Mạnh Hơn:
-Một số kẻ địch bị cuồng loạn bởi sức mạnh của những cơn ác mộng, có Kháng Đòn và Concerto Vibrancy cao hơn.</t>
+Một số kẻ địch bị cuồng loạn bởi sức mạnh của những cơn ác mộng, có Kháng Đòn và Sức Mạnh Rung Động cao hơn.</t>
         </is>
       </c>
     </row>
@@ -4777,10 +4777,9 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Hiệu Ứng Special:
-Dodge thành công, Dodge Counter và Phản Công sẽ nhận thêm Năng Lượng Đồng Bộ.
-Kẻ Địch Mạnh Hơn:
-Một số kẻ địch bị cuồng loạn bởi sức mạnh của những cơn ác mộng, có Kháng Đòn và Concerto Vibrancy cao hơn.</t>
+          <t>Hiệu Ứng Đặc Biệt: Successful Dodge, Dodge Counter, and Counterattack grant extra Sync Energy.
+Stronger Foes:
+Some enemies are fanaticized by the power of nightmares and have higher Poise and Vibration Strength.</t>
         </is>
       </c>
     </row>
@@ -4849,10 +4848,10 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Hiệu Ứng Special:
+          <t>Hiệu Ứng Đặc Biệt:
 Tiêu diệt kẻ địch sẽ nhận thêm Năng Lượng Đồng Bộ.
 Kẻ Địch Mạnh Hơn:
-1. Một số kẻ địch bị cuồng loạn bởi sức mạnh của những cơn ác mộng, có Kháng Đòn và Concerto Vibrancy cao hơn.
+1. Một số kẻ địch bị cuồng loạn bởi sức mạnh của những cơn ác mộng, có Kháng Đòn và Sức Mạnh Rung Động cao hơn.
 2. Kẻ địch nhận được lá chắn tương đương 30% HP tối đa của chúng.</t>
         </is>
       </c>
@@ -4922,11 +4921,11 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Hiệu Ứng Special:
+          <t>Hiệu Ứng Đặc Biệt:
 Tiêu diệt kẻ địch sẽ nhận thêm Năng Lượng Đồng Bộ.
 Kẻ Địch Mạnh Hơn:
-1. Một số kẻ địch bị cuồng loạn bởi sức mạnh của những cơn ác mộng, có Kháng Đòn và Concerto Vibrancy cao hơn.
-2. Mỗi khi tiêu diệt kẻ địch, toàn bộ thành viên trong đội sẽ bị giảm 50 Tấn Công, tối đa chồng chất 10 lần. Hiệu ứng này sẽ bị loại bỏ khi kích hoạt Dream Link.</t>
+1. Một số kẻ địch bị cuồng loạn bởi sức mạnh của những cơn ác mộng, có Kháng Đòn và Sức Mạnh Rung Động cao hơn.
+2. Mỗi khi tiêu diệt kẻ địch, toàn bộ thành viên trong đội sẽ bị giảm 50 ATK, tối đa chồng chất 10 lần. Hiệu ứng này sẽ bị loại bỏ khi kích hoạt Liên Kết Giấc Mơ.</t>
         </is>
       </c>
     </row>
@@ -4995,11 +4994,11 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Hiệu Ứng Special:
-Dodge thành công, Dodge Counter và Phản Công sẽ nhận thêm Năng Lượng Đồng Bộ.
+          <t>Hiệu Ứng Đặc Biệt:
+Né tránh thành công, Dodge Counter và Phản Công sẽ nhận thêm Năng Lượng Đồng Bộ.
 Kẻ Địch Mạnh Hơn:
-1. Một số kẻ địch bị cuồng loạn bởi sức mạnh của những cơn ác mộng, có Kháng Đòn và Concerto Vibrancy cao hơn.
-2. Sát thương nhận vào của kẻ địch giảm 3% mỗi giây, tối đa chồng chất 20 lần. Hiệu ứng này sẽ bị loại bỏ khi chúng bị bất động.</t>
+1. Một số kẻ địch bị cuồng loạn bởi sức mạnh của những cơn ác mộng, có Kháng Đòn và Sức Mạnh Rung Động cao hơn.
+2. DMG nhận vào của kẻ địch giảm 3% mỗi giây, tối đa chồng chất 20 lần. Hiệu ứng này sẽ bị loại bỏ khi chúng bị bất động.</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5067,7 @@
         <is>
           <t>Đội nhận 1 điểm Dấu Hiệu Động Lượng khi trúng mục tiêu. Khi đạt 30 điểm, toàn bộ dấu hiệu sẽ được xóa để giải phóng 1 Vụ Nổ quy mô nhỏ.
 Hiệu ứng Đội I: Khi sử dụng Resonance Skill trúng mục tiêu, đội nhận 1 điểm Dấu Hiệu Động Lượng. Hiệu ứng kéo dài 4 giây.
-Hiệu ứng Đội II: Kích hoạt Vụ Nổ tăng 30% Tấn Công cho tất cả thành viên trong đội trong 30 giây.</t>
+Hiệu ứng Đội II: Kích hoạt Vụ Nổ tăng 30% ATK cho tất cả thành viên trong đội trong 30 giây.</t>
         </is>
       </c>
     </row>
@@ -5137,7 +5136,7 @@
         <is>
           <t>Đội nhận 1 điểm Dấu Hiệu Động Lượng khi trúng mục tiêu. Khi đạt 30 điểm, toàn bộ dấu hiệu sẽ được xóa để giải phóng 1 Vụ Nổ quy mô nhỏ.
 Hiệu ứng Đội I: Khi sử dụng Resonance Skill trúng mục tiêu, đội nhận 1 điểm Dấu Hiệu Động Lượng. Hiệu ứng kéo dài 4 giây.
-Hiệu ứng Đội II: Kích hoạt Vụ Nổ tăng 30% Tấn Công cho tất cả thành viên trong đội trong 30 giây.</t>
+Hiệu ứng Đội II: Kích hoạt Vụ Nổ tăng 30% ATK cho tất cả thành viên trong đội trong 30 giây.</t>
         </is>
       </c>
     </row>
@@ -5204,9 +5203,9 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Đội nhận 1 điểm Dấu Hiệu Động Lượng khi gây Sát Thương Basic Attack. Khi đạt 30 điểm, toàn bộ dấu hiệu sẽ được xóa để giải phóng 1 Vụ Nổ quy mô lớn.
+          <t>Đội nhận 1 điểm Dấu Hiệu Động Lượng khi gây Sát Thương Đòn Basic Attack. Khi đạt 30 điểm, toàn bộ dấu hiệu sẽ được xóa để giải phóng 1 Vụ Nổ quy mô lớn.
 Hiệu ứng Đội I: Khi sử dụng Resonance Skill trúng mục tiêu, đội nhận 1 điểm Dấu Hiệu Động Lượng. Hiệu ứng kéo dài 4 giây.
-Hiệu ứng Đội II: Kích hoạt Vụ Nổ tăng 30% Attack cho tất cả thành viên trong đội trong 30 giây.</t>
+Hiệu ứng Đội II: Kích hoạt Vụ Nổ tăng 30% ATK cho tất cả thành viên trong đội trong 30 giây.</t>
         </is>
       </c>
     </row>
@@ -5273,9 +5272,9 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Đội nhận 1 điểm Dấu Hiệu Động Lượng khi gây Sát Thương Basic Attack. Khi đạt 30 điểm, toàn bộ dấu hiệu sẽ được xóa để giải phóng 2 Vụ Nổ quy mô lớn.
+          <t>Đội nhận 1 điểm Dấu Hiệu Động Lượng khi gây Sát Thương Đòn Basic Attack. Khi đạt 30 điểm, toàn bộ dấu hiệu sẽ được xóa để giải phóng 2 Vụ Nổ quy mô lớn.
 Hiệu ứng Đội I: Khi sử dụng Resonance Skill trúng mục tiêu, đội nhận 1 điểm Dấu Hiệu Động Lượng. Hiệu ứng kéo dài 4 giây.
-Hiệu ứng Đội II: Kích hoạt Vụ Nổ tăng 30% Attack cho tất cả thành viên trong đội trong 30 giây.</t>
+Hiệu ứng Đội II: Kích hoạt Vụ Nổ tăng 30% ATK cho tất cả thành viên trong đội trong 30 giây.</t>
         </is>
       </c>
     </row>
@@ -5342,9 +5341,9 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Đội nhận 1 điểm Dấu Hiệu Động Lượng trong 2 giây khi gây Sát Thương Basic Attack. Khi đạt 30 điểm, toàn bộ dấu hiệu sẽ được xóa để giải phóng 2 Vụ Nổ quy mô nhỏ.
+          <t>Đội nhận 1 điểm Dấu Hiệu Động Lượng trong 2 giây khi gây Sát Thương Đòn Basic Attack. Khi đạt 30 điểm, toàn bộ dấu hiệu sẽ được xóa để giải phóng 2 Vụ Nổ quy mô nhỏ.
 Hiệu ứng Đội I: Khi sử dụng Resonance Skill trúng mục tiêu, đội nhận 1 điểm Dấu Hiệu Động Lượng. Hiệu ứng kéo dài 4 giây.
-Hiệu ứng Đội II: Kích hoạt Vụ Nổ tăng 30% Attack cho tất cả thành viên trong đội trong 30 giây.</t>
+Hiệu ứng Đội II: Kích hoạt Vụ Nổ tăng 30% ATK cho tất cả thành viên trong đội trong 30 giây.</t>
         </is>
       </c>
     </row>
@@ -5412,10 +5411,10 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Khi tấn công mục tiêu bằng bất kỳ đòn đánh nào, đội sẽ nhận 1 điểm Dấu Sấm. Attack cùng mục tiêu chỉ nhận được 1 điểm mỗi 3 giây.
-Dấu Sấm: Đội có thể tích lũy tối đa 30 điểm Dấu Sấm. Khi đạt 30 điểm, toàn bộ Dấu Sấm sẽ được xóa để triệu hồi Sét đánh xuống.
-Hiệu ứng tăng cường Đội I: Khi Resonator đang hoạt động gây Crit. DMG Electro lên mục tiêu, đội sẽ nhận thêm 2 điểm Dấu Sấm. Hiệu ứng này chỉ kích hoạt một lần mỗi giây.
-Hiệu ứng tăng cường Đội II: Khi Resonator đang hoạt động gây Crit. DMG từ Đòn Phối Hợp lên mục tiêu, đội sẽ nhận thêm 1 điểm Dấu Sấm. Hiệu ứng này chỉ kích hoạt một lần mỗi giây.</t>
+          <t>Khi tấn công mục tiêu bằng bất kỳ đòn đánh nào, đội sẽ nhận 1 điểm Dấu Sấm. Tấn công cùng mục tiêu chỉ nhận được 1 điểm mỗi 3 giây.
+Dấu Sấm: The team can hold up to 30 stacks of Thunder Mark. Upon reaching 30 stacks, all Marks are cleared to summon a Lightning to strike.
+Team I Buff: The team gains 2 extra stacks of Thunder Mark when the active Resonator deals Critical Electro DMG to a target. This effect can be triggered once per second.
+Team II Buff: The team gains an extra stack of Thunder Mark when the active Resonator deals Critical Coordinated Attack DMG to a target. This effect can be triggered once per second.</t>
         </is>
       </c>
     </row>
@@ -5483,10 +5482,10 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Khi tấn công mục tiêu bằng bất kỳ đòn đánh nào, đội sẽ nhận 1 điểm Dấu Sấm. Attack cùng mục tiêu chỉ nhận được 1 điểm mỗi 3 giây.
-Dấu Sấm: Đội có thể tích lũy tối đa 30 điểm Dấu Sấm. Khi đạt 30 điểm, toàn bộ Dấu Sấm sẽ được xóa để triệu hồi Sét đánh xuống trong một khoảng thời gian.
-Hiệu ứng tăng cường Đội I: Khi Resonator đang hoạt động gây Crit. DMG Electro lên mục tiêu, đội sẽ nhận thêm 2 điểm Dấu Sấm. Hiệu ứng này chỉ kích hoạt một lần mỗi giây.
-Hiệu ứng tăng cường Đội II: Khi Resonator đang hoạt động gây Crit. DMG từ Đòn Phối Hợp lên mục tiêu, đội sẽ nhận thêm 1 điểm Dấu Sấm. Hiệu ứng này chỉ kích hoạt một lần mỗi giây.</t>
+          <t>Khi tấn công mục tiêu bằng bất kỳ đòn đánh nào, đội sẽ nhận 1 điểm Dấu Sấm. Tấn công cùng mục tiêu chỉ nhận được 1 điểm mỗi 3 giây.
+Dấu Sấm: The team can hold up to 30 stacks of Thunder Mark. Upon reaching 30 stacks, all Marks are cleared to summon Lightning to strike for a period of time.
+Team I Buff: The team gains 2 extra stacks of Thunder Mark when the active Resonator deals Critical Electro DMG to a target. This effect can be triggered once per second.
+Team II Buff: The team gains an extra stack of Thunder Mark when the active Resonator deals Critical Coordinated Attack DMG to a target. This effect can be triggered once per second.</t>
         </is>
       </c>
     </row>
@@ -5554,10 +5553,10 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Khi tấn công mục tiêu bằng Đòn Phối Hợp, đội sẽ nhận 1 điểm Dấu Sấm. Attack cùng mục tiêu chỉ nhận được 1 điểm mỗi giây.
-Dấu Sấm: Đội có thể tích lũy tối đa 60 điểm Dấu Sấm. Khi đạt 30 điểm, tất cả thành viên sẽ hồi một lượng Resonance Energy nhất định; khi đạt 60 điểm, toàn bộ Dấu Sấm sẽ được xóa để triệu hồi Sét đánh xuống trong một khoảng thời gian.
-Hiệu ứng tăng cường Đội I: Khi Resonator đang hoạt động gây Crit. DMG Electro lên mục tiêu, đội sẽ nhận thêm 2 điểm Dấu Sấm. Hiệu ứng này chỉ kích hoạt một lần mỗi giây.
-Hiệu ứng tăng cường Đội II: Khi Resonator đang hoạt động gây Crit. DMG từ Đòn Phối Hợp lên mục tiêu, đội sẽ nhận thêm 1 điểm Dấu Sấm. Hiệu ứng này chỉ kích hoạt một lần mỗi giây.</t>
+          <t>Khi tấn công mục tiêu bằng Đòn Phối Hợp, đội sẽ nhận 1 điểm Dấu Sấm. Tấn công cùng mục tiêu chỉ nhận được 1 điểm mỗi giây.
+Dấu Sấm: The team can hold up to 60 stacks of Thunder Mark. Upon reaching 30 stacks, restore a certain amount of Resonance Energy for all team members; Upon reaching 60 stacks, all Marks are cleared to summon Lightning to strike for a period of time.
+Team I Buff: The team gains 2 extra stacks of Thunder Mark when the active Resonator deals Critical Electro DMG to a target. This effect can be triggered once per second.
+Team II Buff: The team gains an extra stack of Thunder Mark when the active Resonator deals Critical Coordinated Attack DMG to a target. This effect can be triggered once per second.</t>
         </is>
       </c>
     </row>
@@ -5626,9 +5625,9 @@
       <c r="M78" t="inlineStr">
         <is>
           <t>Đội nhận 1 điểm Dấu Sấm khi tấn công phối hợp trúng mục tiêu. Mỗi mục tiêu chỉ nhận 1 điểm mỗi giây.
-Dấu Sấm: Đội có thể giữ tối đa 60 điểm Dấu Sấm. Khi đạt 30 điểm, hồi một lượng Resonance Energy và Concerto Energy nhất định cho tất cả thành viên; khi đạt 60 điểm, toàn bộ dấu hiệu sẽ được xóa để triệu hồi Thunder giáng xuống trong một khoảng thời gian.
-Hiệu ứng Đội I: Đội nhận thêm 2 điểm Dấu Sấm khi Resonator chủ động gây Crit. DMG Electro lên mục tiêu. Hiệu ứng kích hoạt tối đa 1 lần mỗi giây.
-Hiệu ứng Đội II: Đội nhận thêm 1 điểm Dấu Sấm khi Resonator chủ động gây Crit. DMG từ Đòn Attack Phối Hợp lên mục tiêu. Hiệu ứng kích hoạt tối đa 1 lần mỗi giây.</t>
+Dấu Sấm: The team can hold up to 60 stacks of Thunder Mark. Upon reaching 30 stacks, restore a certain amount of Resonance Energy and Concerto Energy for all team members; Upon reaching 60 stacks, all Marks are cleared to summon Lightning to strike for a period of time.
+Team I Buff: The team gains 2 extra stacks of Thunder Mark when the active Resonator deals Critical Electro DMG to a target. This effect can be triggered once per second.
+Team II Buff: The team gains an extra stack of Thunder Mark when the active Resonator deals Critical Coordinated Attack DMG to a target. This effect can be triggered once per second.</t>
         </is>
       </c>
     </row>
@@ -5697,11 +5696,11 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Khi tấn công mục tiêu bằng bất kỳ đòn đánh nào, đội sẽ nhận 1 điểm Dấu Sấm. Attack cùng mục tiêu chỉ nhận được 1 điểm mỗi 3 giây.
-Khi tấn công mục tiêu bằng Đòn Phối Hợp, đội sẽ nhận 1 điểm Dấu Sấm. Attack cùng mục tiêu chỉ nhận được 1 điểm mỗi giây.
-Dấu Sấm: Đội có thể tích lũy tối đa 60 điểm Dấu Sấm. Khi đạt 30 điểm, tất cả thành viên sẽ hồi một lượng Resonance Energy và Concerto Energy nhất định; khi đạt 60 điểm, toàn bộ Dấu Sấm sẽ được xóa để triệu hồi Sét đánh xuống trong một khoảng thời gian.
-Hiệu ứng tăng cường Đội I: Khi Resonator đang hoạt động gây Crit. DMG Electro lên mục tiêu, đội sẽ nhận thêm 2 điểm Dấu Sấm. Hiệu ứng này chỉ kích hoạt một lần mỗi giây.
-Hiệu ứng tăng cường Đội II: Khi Resonator đang hoạt động gây Crit. DMG từ Đòn Phối Hợp lên mục tiêu, đội sẽ nhận thêm 1 điểm Dấu Sấm. Hiệu ứng này chỉ kích hoạt một lần mỗi giây.</t>
+          <t>Khi tấn công mục tiêu bằng bất kỳ đòn đánh nào, đội sẽ nhận 1 điểm Dấu Sấm. Tấn công cùng mục tiêu chỉ nhận được 1 điểm mỗi 3 giây.
+Khi tấn công mục tiêu bằng Đòn Phối Hợp, đội sẽ nhận 1 điểm Dấu Sấm. Tấn công cùng mục tiêu chỉ nhận được 1 điểm mỗi giây.
+Dấu Sấm: The team can hold up to 60 stacks of Thunder Mark. Upon reaching 30 stacks, restore a certain amount of Resonance Energy and Concerto Energy for all team members; Upon reaching 60 stacks, all Marks are cleared to summon Lightning to strike for a period of time.
+Team I Buff: The team gains 2 extra stacks of Thunder Mark when the active Resonator deals Critical Electro DMG to a target. This effect can be triggered once per second.
+Team II Buff: The team gains an extra stack of Thunder Mark when the active Resonator deals Critical Coordinated Attack DMG to a target. This effect can be triggered once per second.</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5765,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Lệnh Điều khiển: DMG+</t>
+          <t>Lệnh bảng điều khiển: DMG+</t>
         </is>
       </c>
     </row>
@@ -5831,7 +5830,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Va chạm giờ gây Havoc DMG thay vì Sát Thương Physical. Gây Havoc DMG sẽ cho đội {0} điểm Đánh Dấu Đà.</t>
+          <t>Va chạm giờ gây Sát Thương Havoc thay vì Sát Thương Vật Lý. Gây Sát Thương Havoc sẽ cho đội {0} điểm Đánh Dấu Đà.</t>
         </is>
       </c>
     </row>
@@ -5896,7 +5895,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Sát thương gây ra bởi Impact tăng thêm {0}%.</t>
+          <t>DMG gây ra bởi Impact tăng thêm {0}%.</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5960,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Sát thương gây ra bởi tất cả thành viên trong đội tăng thêm {0}%.</t>
+          <t>DMG gây ra bởi tất cả thành viên trong đội tăng thêm {0}%.</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6025,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Sát thương gây ra bởi Lightning tăng thêm {0}. Khi kích hoạt Lightning, toàn đội được tăng Crit. Rate thêm {1} trong {2} giây.</t>
+          <t>DMG gây ra bởi Lightning tăng thêm {0}. Khi kích hoạt Lightning, toàn đội được tăng Crit. Rate thêm {1} trong {2} giây.</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6090,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Khi Đòn Phối Hợp của Resonator trúng mục tiêu, sát thương sẽ được cộng thêm {0} Sức Tấn Công.</t>
+          <t>Khi Đòn Phối Hợp của Resonator trúng mục tiêu, DMG sẽ được cộng thêm {0} Sức ATK.</t>
         </is>
       </c>
     </row>
@@ -6156,7 +6155,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Tấn Công của tất cả thành viên trong đội được tăng {0}.</t>
+          <t>ATK của tất cả thành viên trong đội được tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -6221,7 +6220,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Kích hoạt Kỹ Năng Giới Thiệu triệu hồi Sóng Xung Kích kéo kẻ địch vào và gây Havoc DMG bằng 200% Tấn Công của Resonator.</t>
+          <t>Kích hoạt Kỹ Năng Giới Thiệu triệu hồi Sóng Xung Kích kéo kẻ địch vào và gây Sát Thương Havoc bằng 200% ATK của Resonator.</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6285,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Sóng Xung Kích gây Nổ ngay sau đó, gây Sát Thương Hỗn Loạn bằng 600% Tấn Công của Resonator.</t>
+          <t>Sóng Xung Kích gây Nổ ngay sau đó, gây Sát Thương Hỗn Loạn bằng 600% ATK của Resonator.</t>
         </is>
       </c>
     </row>
@@ -6416,7 +6415,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Thực hiện 2 Đòn Phối Hợp hoặc 5 Basic Attack sẽ tích lũy một tầng Tia Lửa Điện. Số tầng của mỗi loại được tính riêng. Khi một trong hai đạt 2 tầng, đòn tấn công sẽ tiêu thụ toàn bộ tầng đó để triệu hồi 2 Tia Sét đánh vào mục tiêu, gây Electro DMG bằng 200% Tấn Công của Resonator.</t>
+          <t>Thực hiện 2 Đòn Phối Hợp hoặc 5 Đòn Basic Attack sẽ tích lũy một tầng Tia Lửa Điện. Số tầng của mỗi loại được tính riêng. Khi một trong hai đạt 2 tầng, đòn tấn công sẽ tiêu thụ toàn bộ tầng đó để triệu hồi 2 Tia Sét đánh vào mục tiêu, gây Sát Thương Electro bằng 200% ATK của Resonator.</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6480,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Các Tia Sét gây thêm Electro DMG bằng 300% Tấn Công của Resonator trong vòng 3 giây sau khi trúng mục tiêu.</t>
+          <t>Các Tia Sét gây thêm Sát Thương Electro bằng 300% ATK của Resonator trong vòng 3 giây sau khi trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6545,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Các Tia Sét kích hoạt Bão Từ, gây Electro DMG bằng 400% Tấn Công của Resonator.</t>
+          <t>Các Tia Sét kích hoạt Bão Từ, gây Sát Thương Electro bằng 400% ATK của Resonator.</t>
         </is>
       </c>
     </row>
@@ -6611,7 +6610,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Thực hiện Mid-air Attack sẽ triệu hồi một Thiên Thạch, gây Fusion DMG bằng 300% Attack của Resonator. Hiệu ứng này có thể kích hoạt mỗi 3 giây một lần.</t>
+          <t>Thực hiện Đòn Trên Không sẽ triệu hồi một Thiên Thạch, gây Sát Thương Fusion bằng 300% ATK của Resonator. Hiệu ứng này có thể kích hoạt mỗi 3 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -6741,7 +6740,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Thiên Thạch phát nổ khi va chạm, gây Fusion DMG bằng 200% Tấn Công của Resonator và tạo ra một vùng lửa gây Fusion DMG bằng 380% Tấn Công của Resonator.</t>
+          <t>Thiên Thạch phát nổ khi va chạm, gây Sát Thương Fusion bằng 200% ATK của Resonator và tạo ra một vùng lửa gây Sát Thương Fusion bằng 380% ATK của Resonator.</t>
         </is>
       </c>
     </row>
@@ -6806,7 +6805,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Gây Sát Thương Heavy Attack 2 lần sẽ tăng Crit. DMG của Resonator đang kích hoạt lên 5% (kích hoạt mỗi 0.1 giây), tối đa 20 lần.</t>
+          <t>Gây Sát Thương Đòn Nặng 2 lần sẽ tăng Crit. DMG của Resonator đang kích hoạt lên 5% (kích hoạt mỗi 0.1 giây), tối đa 20 lần.</t>
         </is>
       </c>
     </row>
@@ -6871,7 +6870,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Gây Sát Thương Heavy Attack 5 lần sẽ tạo ra một vụ nổ băng (kích hoạt mỗi 0.1 giây), gây Glacio DMG bằng 400% Attack của Resonator.</t>
+          <t>Gây Sát Thương Đòn Nặng 5 lần sẽ tạo ra một vụ nổ băng (kích hoạt mỗi 0.1 giây), gây Sát Thương Glacio bằng 400% ATK của Resonator.</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6935,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Increase Crit. Rate của Heavy Attack lên 50%.</t>
+          <t>Tăng Crit. Rate của Đòn Tấn Công Mạnh lên 50%.</t>
         </is>
       </c>
     </row>
@@ -7001,7 +7000,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG tăng thêm 500%</t>
+          <t>Sát Thương Né Tránh Phản Công tăng thêm 500%</t>
         </is>
       </c>
     </row>
@@ -7066,7 +7065,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Đánh trúng kẻ địch bằng Dodge Counter sẽ tăng Crit. Rate và Crit. DMG của Resonator thêm 10%, có thể tích lũy tối đa 10 lần.</t>
+          <t>Đánh trúng kẻ địch bằng Dodge Counter Tránh sẽ tăng Crit. Rate và Crit. DMG của Resonator thêm 10%, có thể tích lũy tối đa 10 lần.</t>
         </is>
       </c>
     </row>
@@ -7131,7 +7130,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Sát Thương của Dodge Counter tăng thêm 100%. Khi thực hiện Dodge Counter, một Vụ Nổ Xoáy sẽ xuất hiện, gây Aero DMG bằng 600% Tấn Công của Resonator.</t>
+          <t>Sát Thương của Dodge Counter Tránh tăng thêm 100%. Khi thực hiện Dodge Counter Tránh, một Vụ Nổ Xoáy sẽ xuất hiện, gây Sát Thương Aero bằng 600% ATK của Resonator.</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7195,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Dodge thành công tăng Tấn Công của Resonator lên 20% trong 10 giây, có thể chồng chất lên đến 10 lần.</t>
+          <t>Né tránh thành công tăng ATK của Resonator lên 20% trong 10 giây, có thể chồng chất lên đến 10 lần.</t>
         </is>
       </c>
     </row>
@@ -7261,7 +7260,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Crit. DMG của toàn đội tăng 100%. Nhận sát thương sẽ giảm Crit. DMG xuống 100% trong 3 giây.</t>
+          <t>Crit. DMG của toàn đội tăng 100%. Nhận DMG sẽ giảm Crit. DMG xuống 100% trong 3 giây.</t>
         </is>
       </c>
     </row>
@@ -7326,7 +7325,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Tấn công mục tiêu lần nữa trong vòng 2 giây sau đòn tấn công trước sẽ tăng Attack của Resonator thêm 3% trong 5 giây. Hiệu ứng này chỉ kích hoạt mỗi 0,5 giây một lần.</t>
+          <t>ATK mục tiêu lần nữa trong vòng 2 giây sau đòn tấn công trước sẽ tăng ATK của Resonator thêm 3% trong 5 giây. Hiệu ứng này chỉ kích hoạt mỗi 0,5 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -7391,7 +7390,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Tất cả thành viên trong đội nhận được 20 Concerto Energy mỗi 2 giây và không thể bị hạ gục trong thử thách. Kích hoạt Kỹ Năng Giới Thiệu làm tăng Tấn Công của tất cả thành viên lên 15%, có thể cộng dồn tối đa 10 lần.</t>
+          <t>Tất cả thành viên trong đội nhận được 20 Concerto Energy mỗi 2 giây và không thể bị hạ gục trong thử thách. Kích hoạt Kỹ Năng Giới Thiệu làm tăng ATK của tất cả thành viên lên 15%, có thể cộng dồn tối đa 10 lần.</t>
         </is>
       </c>
     </row>
@@ -7521,7 +7520,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Tất cả thành viên trong đội được tăng 50% Tấn Công khi ở trên không và không thể bị hạ gục trong thử thách.</t>
+          <t>Tất cả thành viên trong đội được tăng 50% ATK khi ở trên không và không thể bị hạ gục trong thử thách.</t>
         </is>
       </c>
     </row>
@@ -7651,7 +7650,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Dodge thành công triệu hồi một luồng xoáy, gây Aero DMG bằng 300% Tấn Công của Resonator. Tất cả thành viên trong đội sẽ không bị hạ gục trong thử thách.</t>
+          <t>Né tránh thành công triệu hồi một luồng xoáy, gây Sát Thương Aero bằng 300% ATK của Resonator. Tất cả thành viên trong đội sẽ không bị hạ gục trong thử thách.</t>
         </is>
       </c>
     </row>
@@ -7716,7 +7715,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Không nhận sát thương trong 5 giây sẽ tăng Crit. DMG của Resonator lên 50%, tối đa 5 tầng. Mất 1 tầng mỗi khi nhận sát thương.</t>
+          <t>Không nhận DMG trong 5 giây sẽ tăng Crit. DMG của Resonator lên 50%, tối đa 5 tầng. Mất 1 tầng mỗi khi nhận DMG.</t>
         </is>
       </c>
     </row>
@@ -7781,7 +7780,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Lệnh Điều khiển: DMG+</t>
+          <t>Lệnh bảng điều khiển: DMG+</t>
         </is>
       </c>
     </row>
@@ -8041,7 +8040,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Đánh trúng kẻ địch bằng Intro Skill sẽ tung một đợt Sóng Shadow tấn công kẻ địch.</t>
+          <t>Đánh trúng kẻ địch bằng Kỹ Năng Khởi Động sẽ tung một đợt Sóng Bóng Tối tấn công kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -8106,7 +8105,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Resonators nhận thêm {0} Havoc DMG.</t>
+          <t>Resonator nhận thêm {0} Sát Thương Havoc.</t>
         </is>
       </c>
     </row>
@@ -8171,7 +8170,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Tấn Công của tất cả thành viên trong đội được tăng {0}.</t>
+          <t>ATK của tất cả thành viên trong đội được tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -8240,11 +8239,11 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Khi Resonators làm giảm Vibration Strength của mục tiêu xuống còn 50% hoặc khiến mục tiêu bị bất động, tất cả thành viên trong đội hồi phục 50% Resonance Energy và Cooldown chiêu của Resonance Liberation giảm 50%. Hiệu ứng này có thể kích hoạt tối đa 2 lần trên mỗi mục tiêu.
-Mục tiêu bị bất động sẽ chịu thêm 200% sát thương.
-Buff Đội I: Khi sử dụng Resonance Liberation, Resonators nhận được 10 tầng Dấu Băng Giá, và tất cả thành viên trong đội nhận thêm 20 Concerto Energy và 20 Resonance Energy.
-Khi Dấu Băng Giá đạt 40 tầng, Skill Băng Giá sẽ tự động kích hoạt, gây sát thương Hệ Băng và giảm 50% Vibration Strength của mục tiêu.
-Buff Đội II: Khi sử dụng Skill Khởi Động, tất cả thành viên trong đội hồi phục 20 Concerto Energy và 20 Resonance Energy, đồng thời giảm 15% Cooldown chiêu Resonance Liberation.</t>
+          <t>Khi Resonator làm giảm Sức Rung của mục tiêu xuống còn 50% hoặc khiến mục tiêu bị bất động, tất cả thành viên trong đội hồi phục 50% Resonance Energy và thời gian hồi chiêu của Resonance Liberation giảm 50%. Hiệu ứng này có thể kích hoạt tối đa 2 lần trên mỗi mục tiêu.
+Mục tiêu bị bất động sẽ chịu thêm 200% DMG.
+Buff Đội I: Khi sử dụng Resonance Liberation, Resonator nhận được 10 tầng Dấu Băng Giá, và tất cả thành viên trong đội nhận thêm 20 Năng Lượng Giao Hưởng và 20 Resonance Energy.
+Khi Dấu Băng Giá đạt 40 tầng, Kỹ năng Băng Giá sẽ tự động kích hoạt, gây DMG Hệ Băng và giảm 50% Sức Rung của mục tiêu.
+Buff Đội II: Khi sử dụng Kỹ năng Khởi Động, tất cả thành viên trong đội hồi phục 20 Năng Lượng Giao Hưởng và 20 Resonance Energy, đồng thời giảm 15% thời gian hồi chiêu Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -8313,11 +8312,11 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Khi Resonators làm giảm Vibration Strength của mục tiêu xuống còn 50% hoặc khiến mục tiêu bị bất động, tất cả thành viên trong đội hồi phục 50% Resonance Energy và Cooldown chiêu của Resonance Liberation giảm 50%. Hiệu ứng này có thể kích hoạt tối đa 2 lần trên mỗi mục tiêu.
-Mục tiêu bị bất động sẽ chịu thêm 200% sát thương.
-Buff Đội I: Khi sử dụng Resonance Liberation, Resonators nhận được 10 tầng Dấu Băng Giá, và tất cả thành viên trong đội nhận thêm 20 Concerto Energy và 20 Resonance Energy.
-Khi Dấu Băng Giá đạt 40 tầng, Skill Băng Giá sẽ tự động kích hoạt, gây sát thương Hệ Băng và giảm 50% Vibration Strength của mục tiêu.
-Buff Đội II: Khi sử dụng Skill Khởi Động, tất cả thành viên trong đội hồi phục 20 Concerto Energy và 20 Resonance Energy, đồng thời giảm 15% Cooldown chiêu Resonance Liberation.</t>
+          <t>Khi Resonator làm giảm Sức Rung của mục tiêu xuống còn 50% hoặc khiến mục tiêu bị bất động, tất cả thành viên trong đội hồi phục 50% Resonance Energy và thời gian hồi chiêu của Resonance Liberation giảm 50%. Hiệu ứng này có thể kích hoạt tối đa 2 lần trên mỗi mục tiêu.
+Mục tiêu bị bất động sẽ chịu thêm 200% DMG.
+Buff Đội I: Khi sử dụng Resonance Liberation, Resonator nhận được 10 tầng Dấu Băng Giá, và tất cả thành viên trong đội nhận thêm 20 Năng Lượng Giao Hưởng và 20 Resonance Energy.
+Khi Dấu Băng Giá đạt 40 tầng, Kỹ năng Băng Giá sẽ tự động kích hoạt, gây DMG Hệ Băng và giảm 50% Sức Rung của mục tiêu.
+Buff Đội II: Khi sử dụng Kỹ năng Khởi Động, tất cả thành viên trong đội hồi phục 20 Năng Lượng Giao Hưởng và 20 Resonance Energy, đồng thời giảm 15% thời gian hồi chiêu Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -8386,11 +8385,11 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Khi Resonators làm giảm Vibration Strength của mục tiêu xuống 50% hoặc khiến mục tiêu bị bất động, tất cả thành viên trong đội phục hồi 100% Resonance Energy và giảm 100% Cooldown chiêu của Resonance Liberation. Hiệu ứng này có thể kích hoạt tối đa 2 lần cho mỗi mục tiêu.
+          <t>Khi Resonator làm giảm Sức Rung của mục tiêu xuống 50% hoặc khiến mục tiêu bị bất động, tất cả thành viên trong đội phục hồi 100% Resonance Energy và giảm 100% thời gian hồi chiêu của Resonance Liberation. Hiệu ứng này có thể kích hoạt tối đa 2 lần cho mỗi mục tiêu.
 Mục tiêu bị bất động sẽ chịu Sát Thương tăng 200%.
-Buff Đội I: Khi sử dụng Resonance Liberation, Resonators nhận 10 tầng Dấu Hiệu Đông Cứng, và tất cả thành viên trong đội nhận 20 Concerto Energy cùng 20 Resonance Energy.
-Khi Dấu Hiệu Đông Cứng đạt 40 tầng, Băng Giá sẽ tự động kích hoạt, gây Glacio DMG và giảm 50% Vibration Strength của mục tiêu.
-Buff Đội II: Khi sử dụng Intro Skill, tất cả thành viên trong đội phục hồi 20 Concerto Energy và 20 Resonance Energy, đồng thời giảm 15% Cooldown chiêu của Resonance Liberation.</t>
+Buff Đội I: Khi sử dụng Resonance Liberation, Resonator nhận 10 tầng Dấu Hiệu Đông Cứng, và tất cả thành viên trong đội nhận 20 Năng Lượng Giao Hưởng cùng 20 Resonance Energy.
+Khi Dấu Hiệu Đông Cứng đạt 40 tầng, Băng Giá sẽ tự động kích hoạt, gây Sát Thương Glacio và giảm 50% Sức Rung của mục tiêu.
+Buff Đội II: Khi sử dụng Kỹ Năng Khởi Động, tất cả thành viên trong đội phục hồi 20 Năng Lượng Giao Hưởng và 20 Resonance Energy, đồng thời giảm 15% thời gian hồi chiêu của Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -8459,11 +8458,11 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Khi Resonators làm giảm Vibration Strength của mục tiêu xuống 50% hoặc khiến mục tiêu bị bất động, tất cả thành viên trong đội phục hồi 100% Resonance Energy và giảm 100% Cooldown chiêu của Resonance Liberation. Hiệu ứng này có thể kích hoạt tối đa 2 lần cho mỗi mục tiêu.
+          <t>Khi Resonator làm giảm Sức Rung của mục tiêu xuống 50% hoặc khiến mục tiêu bị bất động, tất cả thành viên trong đội phục hồi 100% Resonance Energy và giảm 100% thời gian hồi chiêu của Resonance Liberation. Hiệu ứng này có thể kích hoạt tối đa 2 lần cho mỗi mục tiêu.
 Mục tiêu bị bất động sẽ chịu Sát Thương tăng 200%.
-Buff Đội I: Khi sử dụng Resonance Liberation, Resonators nhận 10 tầng Dấu Hiệu Đông Cứng, và tất cả thành viên trong đội nhận 20 Concerto Energy cùng 20 Resonance Energy.
-Khi Dấu Hiệu Đông Cứng đạt 40 tầng, Băng Giá sẽ tự động kích hoạt, gây Glacio DMG và giảm 50% Vibration Strength của mục tiêu.
-Buff Đội II: Khi sử dụng Intro Skill, tất cả thành viên trong đội phục hồi 20 Concerto Energy và 20 Resonance Energy, đồng thời giảm 15% Cooldown chiêu của Resonance Liberation.</t>
+Buff Đội I: Khi sử dụng Resonance Liberation, Resonator nhận 10 tầng Dấu Hiệu Đông Cứng, và tất cả thành viên trong đội nhận 20 Năng Lượng Giao Hưởng cùng 20 Resonance Energy.
+Khi Dấu Hiệu Đông Cứng đạt 40 tầng, Băng Giá sẽ tự động kích hoạt, gây Sát Thương Glacio và giảm 50% Sức Rung của mục tiêu.
+Buff Đội II: Khi sử dụng Kỹ Năng Khởi Động, tất cả thành viên trong đội phục hồi 20 Năng Lượng Giao Hưởng và 20 Resonance Energy, đồng thời giảm 15% thời gian hồi chiêu của Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -8532,11 +8531,11 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Khi Resonators làm giảm Vibration Strength của mục tiêu xuống 50% hoặc khiến mục tiêu bị bất động, tất cả thành viên trong đội phục hồi 100% Resonance Energy và giảm 100% Cooldown chiêu của Resonance Liberation. Hiệu ứng này có thể kích hoạt tối đa 2 lần cho mỗi mục tiêu.
+          <t>Khi Resonator làm giảm Sức Rung của mục tiêu xuống 50% hoặc khiến mục tiêu bị bất động, tất cả thành viên trong đội phục hồi 100% Resonance Energy và giảm 100% thời gian hồi chiêu của Resonance Liberation. Hiệu ứng này có thể kích hoạt tối đa 2 lần cho mỗi mục tiêu.
 Mục tiêu bị bất động sẽ chịu Sát Thương tăng 200%.
-Buff Đội I: Khi sử dụng Resonance Liberation, Resonators nhận 10 tầng Dấu Hiệu Đông Cứng, và tất cả thành viên trong đội nhận 20 Concerto Energy cùng 20 Resonance Energy.
-Khi Dấu Hiệu Đông Cứng đạt 40 tầng, Băng Giá sẽ tự động kích hoạt, gây Glacio DMG và giảm 50% Vibration Strength của mục tiêu.
-Buff Đội II: Khi sử dụng Intro Skill, tất cả thành viên trong đội phục hồi 20 Concerto Energy và 20 Resonance Energy, đồng thời giảm 15% Cooldown chiêu của Resonance Liberation.</t>
+Buff Đội I: Khi sử dụng Resonance Liberation, Resonator nhận 10 tầng Dấu Hiệu Đông Cứng, và tất cả thành viên trong đội nhận 20 Năng Lượng Giao Hưởng cùng 20 Resonance Energy.
+Khi Dấu Hiệu Đông Cứng đạt 40 tầng, Băng Giá sẽ tự động kích hoạt, gây Sát Thương Glacio và giảm 50% Sức Rung của mục tiêu.
+Buff Đội II: Khi sử dụng Kỹ Năng Khởi Động, tất cả thành viên trong đội phục hồi 20 Năng Lượng Giao Hưởng và 20 Resonance Energy, đồng thời giảm 15% thời gian hồi chiêu của Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -8603,7 +8602,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Sau khi sử dụng Resonance Skill, một Sóng Shadow sẽ được tạo ra sau 1,5 giây để tấn công kẻ địch, gây Havoc DMG. Hiệu ứng này có Cooldown 3 giây, Cooldown được tính riêng cho từng Resonator.
+          <t>Sau khi sử dụng Resonance Skill, một Sóng Bóng Tối sẽ được tạo ra sau 1,5 giây để tấn công kẻ địch, gây Sát Thương Havoc. Hiệu ứng này có thời gian hồi 3 giây, thời gian hồi được tính riêng cho từng Resonator.
 Hiệu ứng tăng cường đội hình I: Tất cả thành viên trong đội thuộc hệ Havoc hồi phục thêm 4 Concerto Energy mỗi giây.
 Hiệu ứng tăng cường đội hình II: Tất cả thành viên trong đội hồi phục thêm 2 Concerto Energy mỗi giây.</t>
         </is>
@@ -8672,7 +8671,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Hồi chiêu Resonance Skill giảm 30%. Sau 1,5 giây kể từ khi sử dụng Resonance Skill, một Shadow Wave sẽ được tạo ra để tấn công kẻ địch, gây Havoc DMG. Hiệu ứng này có Cooldown 3 giây, tính riêng cho từng Resonator.
+          <t>Hồi chiêu Resonance Skill giảm 30%. Sau 1,5 giây kể từ khi sử dụng Resonance Skill, một Shadow Wave sẽ được tạo ra để tấn công kẻ địch, gây DMG Havoc. Hiệu ứng này có hồi chiêu 3 giây, tính riêng cho từng Resonator.
 Hiệu ứng tăng cường đội hình I: Tất cả thành viên trong đội thuộc hệ Havoc phục hồi thêm 4 Concerto Energy mỗi giây.
 Hiệu ứng tăng cường đội hình II: Tất cả thành viên trong đội phục hồi thêm 2 Concerto Energy mỗi giây.</t>
         </is>
@@ -8741,7 +8740,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Sau khi sử dụng Kỹ Năng Giới Thiệu, trong 6 giây tiếp theo, Resonators gây thêm 40% sát thương. Một Đợt Sóng Shadow sẽ xuất hiện sau 1,5 giây kể từ khi sử dụng Resonance Skill để tấn công kẻ địch, gây Havoc DMG. Hiệu ứng này có Cooldown 3 giây, tính riêng cho từng Resonators.
+          <t>Sau khi sử dụng Kỹ Năng Giới Thiệu, trong 6 giây tiếp theo, Resonator gây thêm 40% DMG. Một Đợt Sóng Bóng Tối sẽ xuất hiện sau 1,5 giây kể từ khi sử dụng Resonance Skill để tấn công kẻ địch, gây Sát Thương Havoc. Hiệu ứng này có thời gian hồi 3 giây, tính riêng cho từng Resonator.
 Hiệu ứng Đội I: Các thành viên trong đội thuộc hệ Havoc hồi thêm 4 Concerto Energy mỗi giây.
 Hiệu ứng Đội II: Các thành viên trong đội hồi thêm 2 Concerto Energy mỗi giây.</t>
         </is>
@@ -8810,7 +8809,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Hồi chiêu Resonance Skill giảm 30%. Sau 1,5 giây kể từ khi sử dụng Resonance Skill, một Enhanced Shadow Wave sẽ được tạo ra để tấn công kẻ địch, gây Havoc DMG. Hiệu ứng này có Cooldown 3 giây, tính riêng cho từng Resonator.
+          <t>Hồi chiêu Resonance Skill giảm 30%. Sau 1,5 giây kể từ khi sử dụng Resonance Skill, một Enhanced Shadow Wave sẽ được tạo ra để tấn công kẻ địch, gây DMG Havoc. Hiệu ứng này có hồi chiêu 3 giây, tính riêng cho từng Resonator.
 Hiệu ứng tăng cường đội hình I: Tất cả thành viên trong đội thuộc hệ Havoc phục hồi thêm 4 Concerto Energy mỗi giây.
 Hiệu ứng tăng cường đội hình II: Tất cả thành viên trong đội phục hồi thêm 2 Concerto Energy mỗi giây.</t>
         </is>
@@ -8879,7 +8878,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Sau khi sử dụng Kỹ Năng Giới Thiệu, trong 6 giây tiếp theo, Resonators gây thêm 40% sát thương. Cooldown Resonance Skill giảm 50%. Một Đợt Sóng Shadow Cường Hóa sẽ xuất hiện sau 1,5 giây kể từ khi sử dụng Resonance Skill để tấn công kẻ địch, gây Havoc DMG. Hiệu ứng này có Cooldown 3 giây, tính riêng cho từng Resonators.
+          <t>Sau khi sử dụng Kỹ Năng Giới Thiệu, trong 6 giây tiếp theo, Resonator gây thêm 40% DMG. Thời gian hồi Resonance Skill giảm 50%. Một Đợt Sóng Bóng Tối Cường Hóa sẽ xuất hiện sau 1,5 giây kể từ khi sử dụng Resonance Skill để tấn công kẻ địch, gây Sát Thương Havoc. Hiệu ứng này có thời gian hồi 3 giây, tính riêng cho từng Resonator.
 Hiệu ứng Đội I: Các thành viên trong đội thuộc hệ Havoc hồi thêm 4 Concerto Energy mỗi giây.
 Hiệu ứng Đội II: Các thành viên trong đội hồi thêm 2 Concerto Energy mỗi giây.</t>
         </is>
@@ -8949,10 +8948,10 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;increased RES&lt;/color&gt; trước &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; trước &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
 Một sinh vật Dư Âm hình rồng ẩn náu trên đỉnh Penitent's End vì lý do bí ẩn, nuốt chửng mọi tần số không phân biệt. Bị vặn xoắn bởi những tần số của sự mục nát và cái chết, giờ đây nó hiện hình như một quái thú khủng khiếp với bộ xương trần trụi.
 Nơi từng là thánh địa giờ chỉ còn là nấm mồ của đau thương, và bất cứ ai đến tìm sự cứu rỗi đều phải đối mặt với ngọn lửa phán xét của nó.
-Đó chính là Gehinom, Dragon Than Khóc, ngọn lửa thiêu đốt đến tận xương tủy, nỗi đau vang vọng, khát khao một sự giải thoát cuối cùng.</t>
+Đó chính là Gehinom, Rồng Than Khóc, ngọn lửa thiêu đốt đến tận xương tủy, nỗi đau vang vọng, khát khao một sự giải thoát cuối cùng.</t>
         </is>
       </c>
     </row>
@@ -9020,7 +9019,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;increased RES&lt;/color&gt; trước &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; trước &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.
 Sinh ra từ Nimbus Sanctum, Lorelei từng được trao trí tuệ nhờ sức mạnh của Sentinel Imperator, giao phó nhiệm vụ thanh tẩy những tần số ô uế trôi dạt giữa mây trời.
 Nhưng dục vọng độc ác đã biến nàng thành "Nữ Hoàng Bóng Đêm", khao khát phủ bóng tối vĩnh cửu lên Nimbus để xóa sạch mọi tội lỗi.
 Với chút lý trí cuối cùng, Lorelei tự giam mình trong khu vườn của nàng, cất lên khúc bi ca ám ảnh, chờ đợi ai đó có thể đánh thức nàng khỏi giấc ngủ u tối này.</t>
@@ -9091,7 +9090,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;increased RES&lt;/color&gt; trước &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; trước &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;.
 Được cải tiến bằng công nghệ đặc biệt, Echo này đã biến thành một cỗ máy chiến đấu chính xác và mạnh mẽ, thực thi mệnh lệnh của chủ nhân với lòng trung thành tuyệt đối.
 Mọi dấu vết về hình dạng ban đầu đều đã phai mờ, chỉ còn lại bản năng chiến đấu được mài giũa tinh vi trong tần số của nó. Một kẻ bảo vệ bất khuất, nó thích nghi hoàn hảo với mọi loại hình chiến đấu, và khi cần, sẽ mở khóa một bộ phận đặc biệt để tăng cường khả năng di chuyển hoặc giải phóng toàn bộ năng lượng trong một vụ nổ hủy diệt.
 Gia tộc Montelli, những lữ khách từ phương xa, đã chứng kiến một thế giới rộng lớn hơn—và họ sẵn sàng trả bất cứ giá nào để có được sức mạnh cần thiết hồi sinh quê hương.</t>
@@ -9162,8 +9161,8 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; cao hơn đối với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-Nàng là người bảo vệ Thành Phố Glory, một sư tử cái dũng mãnh của đấu trường.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;Kháng&lt;/color&gt; cao hơn đối với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
+Nàng là người bảo vệ Thành Phố Vinh Quang, một sư tử cái dũng mãnh của đấu trường.
 Thân thể nàng được tạc từ đá cẩm thạch trắng như tượng Gryphon. Tinh thần nàng được tôi luyện từ tiếng gào thét chiến trận và nụ cười của những anh hùng.
 Đây là Arsinosa, kiên trung bất khuất, mãi mãi canh giữ vinh quang của Septimont.</t>
         </is>
@@ -9233,7 +9232,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Wind&gt;Aero DMG&lt;/color&gt; cao hơn.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;Kháng&lt;/color&gt; &lt;color=Wind&gt;Aero DMG&lt;/color&gt; cao hơn.
 Một tín đồ của tuyệt vọng, linh hồn sa ngã bị nuốt chửng bởi thiên đường ảo mộng.
 Khi chiếc mặt nạ Dark Tide rơi xuống, hắn tìm thấy sự tỉnh ngộ ở cuối con đường—hi vọng và cứu rỗi đổi lấy thân xác đã tàn.
 Hắn sẽ mãi yên nghỉ dưới đáy biển sâu, bởi đó cũng là con đường về nhà.</t>
@@ -9304,9 +9303,9 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Thunder&gt;Electro DMG&lt;/color&gt; và &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
-Một hình người được tạo từ bùn nhơ. False Sovereign, ý chí của Dark Tide hiện thân.
-Sinh ra từ giấc mơ utopia về Sự Thống Nhất của Threnodian, nó là khối bùn đen vô định hình được trao cho hình hài, một chiếc bình chỉ để nuốt chửng. Mọi thứ đều phải hòa nhập vào thân thể của False Sovereign và tái sinh thành tôi tớ, con cái của Leviathan.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt; và &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.
+Một hình người được tạo từ bùn nhơ. Kẻ Giả Vương, ý chí của Dark Tide hiện thân.
+Sinh ra từ giấc mơ utopia về Sự Thống Nhất của Threnodian, nó là khối bùn đen vô định hình được trao cho hình hài, một chiếc bình chỉ để nuốt chửng. Mọi thứ đều phải hòa nhập vào thân thể của Kẻ Giả Vương và tái sinh thành tôi tớ, con cái của Leviathan.
 Nó không suy nghĩ. Nó không cảm nhận. Chỉ có những làn sóng bùn nhơ thì thầm những bài thánh ca giả dối, ca tụng quyền năng của Leviathan đến muôn đời.</t>
         </is>
       </c>
@@ -9375,7 +9374,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Wind&gt;Aero DMG&lt;/color&gt; cao hơn.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; cao hơn.
 Một kẻ sa ngã trôi dạt trong dòng nước băng giá, tàn tích vỡ nát nơi năng lượng còn sót lại của Threnodian trú ngụ.
 Nàng đã tự đâm xuyên trái tim mình và rơi xuống biển sâu. Nhưng số phận, tàn nhẫn như những xoáy nước dưới kia, lại kéo nàng xuống sâu hơn nữa.
 Giờ đây, kẻ tạo ra nàng đã chiếm lấy xác thất bại này, nằm chờ dưới đáy biển để nuốt chửng cả thế giới.</t>
@@ -9445,7 +9444,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng Spectro DMG&lt;/color&gt; &lt;color=Light&gt;cao hơn&lt;/color&gt;.
 Hyvatia là hệ thống dò tìm đầu tiên của Spacetrek Collective, được xây dựng tại Sundermere để giám sát và ổn định trạng thái năng lượng của Reactor Drive theo thời gian thực.
 Chức năng cốt lõi của nó là phát hiện các dao động năng lượng bất thường hoặc nguy hiểm, hiệu chỉnh khẩn cấp ngay lập tức, và truyền dữ liệu này về Drive để đảm bảo hoạt động ổn định.</t>
         </is>
@@ -9514,7 +9513,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
 Sau khi Reactor Drive được Exostrider đặt lên Lahai-Roi, nó luôn cảnh giác cao độ với hoạt động của Aleph-1. Khi phản ứng miễn dịch của Drive được kích hoạt, một "Reactor Husk" cơ khí sẽ trỗi dậy từ sâu thẳm giếng năng lượng, với mục đích duy nhất là tiêu diệt kẻ xâm nhập bằng mọi giá.
 Cho đến khi thân xác sụp đổ, cho đến khi tia sáng sao cuối cùng tắt lịm.</t>
         </is>
@@ -9581,7 +9580,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Nhận thêm {0}% Fusion DMG Bonus. Sát Thương Resonance Skill của tất cả thành viên trong đội tăng thêm {1}% trong {2} giây, tối đa {3} tầng. Khi đạt {4} tầng, Tấn Công của tất cả thành viên trong đội sẽ tăng thêm {5}%.</t>
+          <t>Nhận thêm {0}% Tăng Sát Thương Fusion. Sát Thương Resonance Skill của tất cả thành viên trong đội tăng thêm {1}% trong {2} giây, tối đa {3} tầng. Khi đạt {4} tầng, ATK của tất cả thành viên trong đội sẽ tăng thêm {5}%.</t>
         </is>
       </c>
     </row>
@@ -9711,7 +9710,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Mỗi điểm Đánh Basic sẽ tăng thêm &lt;color=#c89a45&gt;10%&lt;/color&gt; sát thương của Resonator hiện tại lên mục tiêu bị bất động.</t>
+          <t>Mỗi điểm Đánh Cơ Bản sẽ tăng thêm &lt;color=#c89a45&gt;10%&lt;/color&gt; sát thương của Resonator hiện tại lên mục tiêu bị bất động.</t>
         </is>
       </c>
     </row>
@@ -9776,7 +9775,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Mỗi điểm Đánh Basic sẽ tăng thêm &lt;color=#c89a45&gt;5%&lt;/color&gt; sát thương của Resonator hiện tại lên mục tiêu bị bất động. Nhận điểm đánh dấu sẽ hồi &lt;color=#c89a45&gt;5%&lt;/color&gt; Resonance Energy cho Resonator hiện tại.</t>
+          <t>Mỗi điểm Đánh Cơ Bản sẽ tăng thêm &lt;color=#c89a45&gt;5%&lt;/color&gt; sát thương của Resonator hiện tại lên mục tiêu bị bất động. Nhận điểm đánh dấu sẽ hồi &lt;color=#c89a45&gt;5%&lt;/color&gt; Resonance Energy cho Resonator hiện tại.</t>
         </is>
       </c>
     </row>
@@ -9848,8 +9847,8 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>&lt;color=#c89a45&gt;Combat Rank Buff: Basic Attack grants Basic Attack Mark. Damage dealt to the immobilized target scales with the number of marks owned.&lt;/color&gt;
-Tấn công mục tiêu bằng Basic Attack sẽ tăng hiệu suất Tăng Cấp Combat lên &lt;color=#c89a45&gt;20%&lt;/color&gt; trong 3 giây, tạo &lt;color=#c89a45&gt;1 stack&lt;/color&gt; Đánh Dấu Basic Attack cho tất cả thành viên trong đội và giảm Vibration Strength Động của mục tiêu đi &lt;color=#c89a45&gt;1%&lt;/color&gt;.
+          <t>&lt;color=#c89a45&gt;Tăng Cấp Chiến Đấu: Đòn Basic Attack tạo ra Đánh Dấu Basic Attack. Sát thương gây ra lên mục tiêu bị bất động sẽ tăng theo số lượng đánh dấu đã tích lũy.&lt;/color&gt;
+Tấn công mục tiêu bằng Đòn Basic Attack sẽ tăng hiệu suất Tăng Cấp Chiến Đấu lên &lt;color=#c89a45&gt;20%&lt;/color&gt; trong 3 giây, tạo &lt;color=#c89a45&gt;1 điểm&lt;/color&gt; Đánh Dấu Basic Attack cho tất cả thành viên trong đội và giảm Độ Mạnh Rung Động của mục tiêu đi &lt;color=#c89a45&gt;1%&lt;/color&gt;.
 &lt;size=5&gt; &lt;/size&gt;
 A: Mỗi điểm Đánh Dấu Basic Attack tăng sát thương của Resonator đang kích hoạt lên mục tiêu bất động thêm &lt;color=#c89a45&gt;2%&lt;/color&gt;. Nhận đánh dấu sẽ hồi &lt;color=#c89a45&gt;5&lt;/color&gt; Concerto Energy cho Resonator đang kích hoạt.
 &lt;size=5&gt; &lt;/size&gt;
@@ -9920,7 +9919,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Tấn công mục tiêu bằng Basic Attack sẽ tạo Dấu Basic Attack, tăng sát thương của Resonator đang hoạt động lên mục tiêu bị bất động.</t>
+          <t>Tấn công mục tiêu bằng Đòn Cơ Bản sẽ tạo Dấu Đòn Cơ Bản, tăng sát thương của Resonator đang hoạt động lên mục tiêu bị bất động.</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10049,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Mỗi &lt;color=#c89a45&gt;8 stacks&lt;/color&gt; Đánh Nặng tích lũy, tất cả thành viên trong đội hồi phục &lt;color=#c89a45&gt;10&lt;/color&gt; Concerto Energy và &lt;color=#c89a45&gt;10%&lt;/color&gt; Resonance Energy.</t>
+          <t>Mỗi &lt;color=#c89a45&gt;8 điểm&lt;/color&gt; Đánh Nặng tích lũy, tất cả thành viên trong đội hồi phục &lt;color=#c89a45&gt;10&lt;/color&gt; Concerto Energy và &lt;color=#c89a45&gt;10%&lt;/color&gt; Resonance Energy.</t>
         </is>
       </c>
     </row>
@@ -10115,7 +10114,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Khi đạt &lt;color=#c89a45&gt;8 stacks&lt;/color&gt; Heavy Attack Mark, mục tiêu sẽ bị gắn &lt;color=#c89a45&gt;1 stack&lt;/color&gt; Collapse Mark, gây sát thương. Mỗi tầng Collapse Mark nhân đôi sát thương, kích hoạt tối đa 10 lần.</t>
+          <t>Khi đạt &lt;color=#c89a45&gt;8 tầng&lt;/color&gt; Heavy Attack Mark, mục tiêu sẽ bị gắn &lt;color=#c89a45&gt;1 tầng&lt;/color&gt; Collapse Mark, gây sát thương. Mỗi tầng Collapse Mark nhân đôi sát thương, kích hoạt tối đa 10 lần.</t>
         </is>
       </c>
     </row>
@@ -10180,7 +10179,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Khi đạt &lt;color=#c89a45&gt;8 stacks&lt;/color&gt; Heavy Attack Mark, Vibration Strength của mục tiêu giảm thêm &lt;color=#c89a45&gt;25%&lt;/color&gt;.</t>
+          <t>Khi đạt &lt;color=#c89a45&gt;8 tầng&lt;/color&gt; Heavy Attack Mark, Vibration Strength của mục tiêu giảm thêm &lt;color=#c89a45&gt;25%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -10252,14 +10251,14 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>&lt;color=#c89a45&gt;Combat Rank Buff: Dealing Heavy Attack DMG grants Heavy Attack Mark. Damage dealt to the target scales with the number of marks owned.&lt;/color&gt;
-Gây sát thương bằng Heavy Attack sẽ tăng hiệu suất Tăng Cấp Combat lên &lt;color=#c89a45&gt;20%&lt;/color&gt; trong 5 giây và áp &lt;color=#c89a45&gt;1 stack&lt;/color&gt; Đánh Dấu Heavy Attack lên mục tiêu. Khi đạt &lt;color=#c89a45&gt;8 stacks&lt;/color&gt; Đánh Dấu Heavy Attack, tất cả đánh dấu sẽ bị xóa để giảm Vibration Strength Động của mục tiêu đi &lt;color=#c89a45&gt;25%&lt;/color&gt;.
+          <t>&lt;color=#c89a45&gt;Tăng Cấp Chiến Đấu: Gây DMG bằng Đòn Heavy Attack tạo ra Đánh Dấu Heavy Attack. DMG gây ra lên mục tiêu sẽ tăng theo số lượng đánh dấu đã tích lũy.&lt;/color&gt;
+Gây DMG bằng Đòn Heavy Attack sẽ tăng hiệu suất Tăng Cấp Chiến Đấu lên &lt;color=#c89a45&gt;20%&lt;/color&gt; trong 5 giây và áp &lt;color=#c89a45&gt;1 điểm&lt;/color&gt; Đánh Dấu Heavy Attack lên mục tiêu. Khi đạt &lt;color=#c89a45&gt;8 điểm&lt;/color&gt; Đánh Dấu Heavy Attack, tất cả đánh dấu sẽ bị xóa để giảm Độ Mạnh Rung Động của mục tiêu đi &lt;color=#c89a45&gt;25%&lt;/color&gt;.
 &lt;size=5&gt; &lt;/size&gt;
-A: Cứ mỗi &lt;color=#c89a45&gt;8 stacks&lt;/color&gt; Đánh Dấu Heavy Attack, tất cả thành viên trong đội hồi &lt;color=#c89a45&gt;10&lt;/color&gt; Concerto Energy và &lt;color=#c89a45&gt;10%&lt;/color&gt; Resonance Energy.
+A: Cứ mỗi &lt;color=#c89a45&gt;8 điểm&lt;/color&gt; Đánh Dấu Heavy Attack, tất cả thành viên trong đội hồi &lt;color=#c89a45&gt;10&lt;/color&gt; Concerto Energy và &lt;color=#c89a45&gt;10%&lt;/color&gt; Resonance Energy.
 &lt;size=5&gt; &lt;/size&gt;
-S: Khi đạt &lt;color=#c89a45&gt;8 stacks&lt;/color&gt; Đánh Dấu Heavy Attack, Vibration Strength Động của mục tiêu sẽ bị giảm thêm &lt;color=#c89a45&gt;25%&lt;/color&gt;.
+S: Khi đạt &lt;color=#c89a45&gt;8 điểm&lt;/color&gt; Đánh Dấu Heavy Attack, Độ Mạnh Rung Động của mục tiêu sẽ bị giảm thêm &lt;color=#c89a45&gt;25%&lt;/color&gt;.
 &lt;size=5&gt; &lt;/size&gt;
-SS: Khi đạt &lt;color=#c89a45&gt;8 stacks&lt;/color&gt; Đánh Dấu Heavy Attack, mục tiêu sẽ bị áp &lt;color=#c89a45&gt;1 stack&lt;/color&gt; Đánh Dấu Sụp Đổ, gây sát thương. Mỗi điểm Đánh Dấu Sụp Đổ nhân đôi sát thương gây ra, kích hoạt tối đa 10 lần.</t>
+SS: Khi đạt &lt;color=#c89a45&gt;8 điểm&lt;/color&gt; Đánh Dấu Heavy Attack, mục tiêu sẽ bị áp &lt;color=#c89a45&gt;1 điểm&lt;/color&gt; Đánh Dấu Sụp Đổ, gây DMG. Mỗi điểm Đánh Dấu Sụp Đổ nhân đôi DMG gây ra, kích hoạt tối đa 10 lần.</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10323,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Gây Sát Thương Heavy Attack sẽ đánh dấu Heavy Attack lên mục tiêu. Khi đạt 8 lớp, tất cả sẽ bị xóa để giảm Concerto Vibrancy của mục tiêu, đồng thời gây sát thương.</t>
+          <t>Gây Sát Thương Đòn Nặng sẽ đánh dấu Đòn Nặng lên mục tiêu. Khi đạt 8 lớp, tất cả sẽ bị xóa để giảm Sức Mạnh Rung Động của mục tiêu, đồng thời gây DMG.</t>
         </is>
       </c>
     </row>
@@ -10389,7 +10388,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Heavy Attack: Tinh Thần High</t>
+          <t>Đòn Heavy Attack: Tinh Thần Cao</t>
         </is>
       </c>
     </row>
@@ -10454,7 +10453,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Nhận Dấu Resonance Liberation sẽ hồi &lt;color=#c89a45&gt;10&lt;/color&gt; Năng Lượng Khúc Tấu. Sử dụng Resonance Liberation sẽ xóa toàn bộ tầng Dấu Resonance Liberation, mỗi tầng tăng sát thương Resonance Liberation thêm &lt;color=#c89a45&gt;10%&lt;/color&gt;.</t>
+          <t>Nhận Dấu Resonance Liberation sẽ hồi &lt;color=#c89a45&gt;10&lt;/color&gt; Năng Lượng Khúc Tấu. Sử dụng Resonance Liberation sẽ xóa toàn bộ tầng Dấu Resonance Liberation, mỗi tầng tăng DMG Resonance Liberation thêm &lt;color=#c89a45&gt;10%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10518,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Khi Resonance Energy đạt tối đa, mỗi giây sẽ nhận thêm &lt;color=#c89a45&gt;1 stack&lt;/color&gt; Đánh Dấu Resonance Liberation. Mỗi tầng Đánh Dấu Resonance Liberation làm tăng Sát Thương Resonance Liberation thêm &lt;color=#c89a45&gt;40%&lt;/color&gt;.</t>
+          <t>Khi Resonance Energy đạt tối đa, mỗi giây sẽ nhận thêm &lt;color=#c89a45&gt;1 tầng&lt;/color&gt; Đánh Dấu Resonance Liberation. Mỗi tầng Đánh Dấu Resonance Liberation làm tăng Sát Thương Resonance Liberation thêm &lt;color=#c89a45&gt;40%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10583,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Mỗi điểm Đánh Dấu Resonance Liberation bị loại bỏ sẽ phục hồi &lt;color=#c89a45&gt;10%&lt;/color&gt; Resonance Energy cho Resonator đang hoạt động. Khi đạt &lt;color=#c89a45&gt;10 stacks&lt;/color&gt; Đánh Dấu Resonance Liberation, Cooldown chiêu của Resonance Liberation tiếp theo của Resonator sẽ giảm &lt;color=#c89a45&gt;100%&lt;/color&gt;.</t>
+          <t>Mỗi điểm Đánh Dấu Resonance Liberation bị loại bỏ sẽ phục hồi &lt;color=#c89a45&gt;10%&lt;/color&gt; Resonance Energy cho Resonator đang hoạt động. Khi đạt &lt;color=#c89a45&gt;10 điểm&lt;/color&gt; Đánh Dấu Resonance Liberation, thời gian hồi chiêu của Resonance Liberation tiếp theo của Resonator sẽ giảm &lt;color=#c89a45&gt;100%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -10656,14 +10655,14 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>&lt;color=#c89a45&gt;Combat Rank Buff: Resonance Liberation DMG scales with the number of Resonance Liberation Marks owned.&lt;/color&gt;
-Khi bắt đầu thử thách, Resonance Energy được hồi phục thêm &lt;color=#c89a45&gt;49%&lt;/color&gt;. Khi Resonance Energy đầy, mỗi giây sẽ nhận được &lt;color=#c89a45&gt;1 stack&lt;/color&gt; Resonance Liberation. Với Điểm Resonance Liberation, đánh trúng mục tiêu sẽ giảm Vibration Strength của chúng đi &lt;color=#c89a45&gt;2%&lt;/color&gt;, kích hoạt mỗi 0,3 giây. Sử dụng Resonance Liberation sẽ tăng hiệu suất Cấp Độ Combat lên &lt;color=#c89a45&gt;20%&lt;/color&gt; trong 15 giây.
+          <t>&lt;color=#c89a45&gt;Hiệu ứng Cấp Độ Chiến Đấu: Sát Thương Resonance Liberation tăng theo số lượng Điểm Resonance Liberation sở hữu.&lt;/color&gt;
+Khi bắt đầu thử thách, Resonance Energy được hồi phục thêm &lt;color=#c89a45&gt;49%&lt;/color&gt;. Khi Resonance Energy đầy, mỗi giây sẽ nhận được &lt;color=#c89a45&gt;1 Điểm&lt;/color&gt; Resonance Liberation. Với Điểm Resonance Liberation, đánh trúng mục tiêu sẽ giảm Độ Rung của chúng đi &lt;color=#c89a45&gt;2%&lt;/color&gt;, kích hoạt mỗi 0,3 giây. Sử dụng Resonance Liberation sẽ tăng hiệu suất Cấp Độ Chiến Đấu lên &lt;color=#c89a45&gt;20%&lt;/color&gt; trong 15 giây.
 &lt;size=5&gt; &lt;/size&gt;
-A: Nhận Điểm Resonance Liberation sẽ hồi phục &lt;color=#c89a45&gt;10&lt;/color&gt; Concerto Energy. Sử dụng Resonance Liberation sẽ loại bỏ tất cả Điểm Resonance Liberation, mỗi Điểm Resonance Liberation tăng Sát Thương Resonance Liberation lên &lt;color=#c89a45&gt;10%&lt;/color&gt;.
+A: Nhận Điểm Resonance Liberation sẽ hồi phục &lt;color=#c89a45&gt;10&lt;/color&gt; Năng Lượng Giao Hưởng. Sử dụng Resonance Liberation sẽ loại bỏ tất cả Điểm Resonance Liberation, mỗi Điểm Resonance Liberation tăng Sát Thương Resonance Liberation lên &lt;color=#c89a45&gt;10%&lt;/color&gt;.
 &lt;size=5&gt; &lt;/size&gt;
-S: Mỗi Điểm Resonance Liberation bị loại bỏ sẽ hồi phục Resonance Energy của Resonator hiện tại lên &lt;color=#c89a45&gt;10%&lt;/color&gt;. Khi đạt &lt;color=#c89a45&gt;10 stacks&lt;/color&gt; Resonance Liberation, Cooldown chiêu Resonance Liberation tiếp theo của Resonator hiện tại sẽ giảm &lt;color=#c89a45&gt;100%&lt;/color&gt;.
+S: Mỗi Điểm Resonance Liberation bị loại bỏ sẽ hồi phục Resonance Energy của Resonator hiện tại lên &lt;color=#c89a45&gt;10%&lt;/color&gt;. Khi đạt &lt;color=#c89a45&gt;10 Điểm&lt;/color&gt; Resonance Liberation, thời gian hồi chiêu Resonance Liberation tiếp theo của Resonator hiện tại sẽ giảm &lt;color=#c89a45&gt;100%&lt;/color&gt;.
 &lt;size=5&gt; &lt;/size&gt;
-SS: Khi Resonance Energy đầy, mỗi giây sẽ nhận thêm &lt;color=#c89a45&gt;1 stack&lt;/color&gt; Resonance Liberation. Mỗi Điểm Resonance Liberation tăng thêm Sát Thương Resonance Liberation lên &lt;color=#c89a45&gt;40%&lt;/color&gt;.</t>
+SS: Khi Resonance Energy đầy, mỗi giây sẽ nhận thêm &lt;color=#c89a45&gt;1 Điểm&lt;/color&gt; Resonance Liberation. Mỗi Điểm Resonance Liberation tăng thêm Sát Thương Resonance Liberation lên &lt;color=#c89a45&gt;40%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -10923,7 +10922,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Dấu Dodge Counter làm tăng DMG của Resonator đang kích hoạt thêm &lt;color=#c89a45&gt;1200%&lt;/color&gt; và cấp khả năng miễn nhiễm gián đoạn trong 6 giây. Đánh trúng mục tiêu bằng Dodge Counter còn phục hồi Concerto Energy của tất cả thành viên trong đội thêm &lt;color=#c89a45&gt;50&lt;/color&gt; và Resonance Energy thêm &lt;color=#c89a45&gt;50%&lt;/color&gt;, đồng thời giảm Cooldown của Resonance Skill và Resonance Liberation xuống &lt;color=#c89a45&gt;50%&lt;/color&gt;.</t>
+          <t>Đánh Dấu Né Tránh Phản Công làm tăng thêm &lt;color=#c89a45&gt;1200%&lt;/color&gt; Sát Thương của Resonator đang hoạt động và miễn nhiễm với gián đoạn trong 6 giây. Khi đánh trúng mục tiêu bằng Né Tránh Phản Công, toàn đội hồi phục &lt;color=#c89a45&gt;50&lt;/color&gt; Năng Lượng Giao Hưởng và &lt;color=#c89a45&gt;50%&lt;/color&gt; Resonance Energy, đồng thời giảm 50% thời gian hồi chiêu Resonance Skill và Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -10988,7 +10987,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Dodge Counter trúng mục tiêu sẽ giảm &lt;color=#c89a45&gt;50%&lt;/color&gt; Cooldown chiêu Resonance Skill và Resonance Liberation của tất cả thành viên trong đội.</t>
+          <t>Dodge Counter trúng mục tiêu sẽ giảm &lt;color=#c89a45&gt;50%&lt;/color&gt; thời gian hồi chiêu Resonance Skill và Resonance Liberation của tất cả thành viên trong đội.</t>
         </is>
       </c>
     </row>
@@ -11062,16 +11061,16 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>&lt;color=#c89a45&gt;Combat Rank Buff: Hitting a target with Dodge Counter grants Dodge Counter Mark, increasing the DMG dealt.&lt;/color&gt;
-Tất cả Resonator trong đội gây &lt;color=#c89a45&gt;50%&lt;/color&gt; Sát Thương thêm nhưng không thể giảm Vibration Strength của mục tiêu bằng các đòn tấn công khác ngoài Dodge Counter.
+          <t>&lt;color=#c89a45&gt;Hiệu ứng Cấp Độ Chiến Đấu: Đánh trúng mục tiêu bằng Dodge Counter Tránh sẽ tạo Hiệu Ứng Dodge Counter Tránh, gia tăng Sát Thương gây ra.&lt;/color&gt;
+Tất cả Resonator trong đội gây &lt;color=#c89a45&gt;50%&lt;/color&gt; Sát Thương thêm nhưng không thể giảm Độ Rung của mục tiêu bằng các đòn tấn công khác ngoài Dodge Counter Tránh.
 &lt;size=5&gt; &lt;/size&gt;
-Đánh trúng mục tiêu bằng Dodge Counter sẽ tăng hiệu suất Cấp Độ Combat lên &lt;color=#c89a45&gt;20%&lt;/color&gt;, tạo Hiệu Ứng Dodge Counter cho tất cả Resonator trong đội và tăng Sát Thương của Resonator hiện tại lên &lt;color=#c89a45&gt;300%&lt;/color&gt; trong 6 giây.
+Đánh trúng mục tiêu bằng Dodge Counter Tránh sẽ tăng hiệu suất Cấp Độ Chiến Đấu lên &lt;color=#c89a45&gt;20%&lt;/color&gt;, tạo Hiệu Ứng Dodge Counter Tránh cho tất cả Resonator trong đội và tăng Sát Thương của Resonator hiện tại lên &lt;color=#c89a45&gt;300%&lt;/color&gt; trong 6 giây.
 &lt;size=5&gt; &lt;/size&gt;
-A: Đánh trúng mục tiêu bằng Dodge Counter sẽ hồi phục Concerto Energy cho tất cả Resonator trong đội lên &lt;color=#c89a45&gt;50&lt;/color&gt; và Resonance Energy lên &lt;color=#c89a45&gt;50%&lt;/color&gt;.
+A: Đánh trúng mục tiêu bằng Dodge Counter Tránh sẽ hồi phục Năng Lượng Giao Hưởng cho tất cả Resonator trong đội lên &lt;color=#c89a45&gt;50&lt;/color&gt; và Resonance Energy lên &lt;color=#c89a45&gt;50%&lt;/color&gt;.
 &lt;size=5&gt; &lt;/size&gt;
-S: Đánh trúng mục tiêu bằng Dodge Counter sẽ giảm Cooldown chiêu Resonance Skill và Resonance Liberation của tất cả Resonator trong đội xuống &lt;color=#c89a45&gt;50%&lt;/color&gt;.
+S: Đánh trúng mục tiêu bằng Dodge Counter Tránh sẽ giảm thời gian hồi chiêu Resonance Skill và Resonance Liberation của tất cả Resonator trong đội xuống &lt;color=#c89a45&gt;50%&lt;/color&gt;.
 &lt;size=5&gt; &lt;/size&gt;
-SS: Hiệu Ứng Dodge Counter tăng thêm Sát Thương của Resonator hiện tại lên &lt;color=#c89a45&gt;1200%&lt;/color&gt; và miễn nhiễm với gián đoạn trong 6 giây. Đánh trúng mục tiêu bằng Dodge Counter sẽ hồi phục thêm Concerto Energy cho tất cả Resonator trong đội lên &lt;color=#c89a45&gt;50&lt;/color&gt; và Resonance Energy lên &lt;color=#c89a45&gt;50%&lt;/color&gt;, đồng thời giảm Cooldown chiêu Resonance Skill và Resonance Liberation xuống &lt;color=#c89a45&gt;50%&lt;/color&gt;.</t>
+SS: Hiệu Ứng Dodge Counter Tránh tăng thêm Sát Thương của Resonator hiện tại lên &lt;color=#c89a45&gt;1200%&lt;/color&gt; và miễn nhiễm với gián đoạn trong 6 giây. Đánh trúng mục tiêu bằng Dodge Counter Tránh sẽ hồi phục thêm Năng Lượng Giao Hưởng cho tất cả Resonator trong đội lên &lt;color=#c89a45&gt;50&lt;/color&gt; và Resonance Energy lên &lt;color=#c89a45&gt;50%&lt;/color&gt;, đồng thời giảm thời gian hồi chiêu Resonance Skill và Resonance Liberation xuống &lt;color=#c89a45&gt;50%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11135,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Dodge Counter trúng mục tiêu sẽ hồi Concerto Energy và Resonance Energy, giảm Cooldown chiêu và tăng sát thương.</t>
+          <t>Dodge Counter trúng mục tiêu sẽ hồi Concerto Energy và Resonance Energy, giảm thời gian hồi chiêu và tăng sát thương.</t>
         </is>
       </c>
     </row>
@@ -11201,7 +11200,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Dodge Counter: Dance Xoay Tròn</t>
+          <t>Dodge Counter: Vũ Điệu Xoay Tròn</t>
         </is>
       </c>
     </row>
@@ -11266,7 +11265,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Đánh trúng mục tiêu bằng Kỹ Năng Echo sẽ giảm thêm &lt;color=#c89a45&gt;18%&lt;/color&gt; Vibration Strength của mục tiêu và hồi toàn bộ Concerto Energy cho các thành viên trong đội lên &lt;color=#c89a45&gt;50&lt;/color&gt;. Hiệu ứng này chỉ kích hoạt một lần mỗi 5 giây.</t>
+          <t>Đánh trúng mục tiêu bằng Kỹ Năng Echo sẽ giảm thêm &lt;color=#c89a45&gt;18%&lt;/color&gt; Sức Rung của mục tiêu và hồi toàn bộ Concerto Energy cho các thành viên trong đội lên &lt;color=#c89a45&gt;50&lt;/color&gt;. Hiệu ứng này chỉ kích hoạt một lần mỗi 5 giây.</t>
         </is>
       </c>
     </row>
@@ -11331,7 +11330,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Sát thương Skill Echo tăng thêm &lt;color=#c89a45&gt;1500%&lt;/color&gt;.</t>
+          <t>DMG Kỹ năng Echo tăng thêm &lt;color=#c89a45&gt;1500%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11396,7 +11395,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Đánh trúng mục tiêu sẽ giảm Cooldown chiêu của Kỹ Năng Echo xuống &lt;color=#c89a45&gt;50%&lt;/color&gt;. Hiệu ứng này chỉ kích hoạt mỗi 5 giây một lần.</t>
+          <t>Đánh trúng mục tiêu sẽ giảm thời gian hồi chiêu của Kỹ Năng Echo xuống &lt;color=#c89a45&gt;50%&lt;/color&gt;. Hiệu ứng này chỉ kích hoạt mỗi 5 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -11468,14 +11467,14 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>&lt;color=#c89a45&gt;Combat Rank Buff: Echo Skill cooldown is reduced, and Echo Skill DMG is increased.&lt;/color&gt;
-Sử dụng Kỹ Năng Echo sẽ tăng hiệu suất Tăng Cấp Combat lên &lt;color=#c89a45&gt;20%&lt;/color&gt; trong 12 giây, kích hoạt mỗi 5 giây. Đánh trúng mục tiêu bằng Kỹ Năng Echo sẽ giảm Vibration Strength Động của chúng đi &lt;color=#c89a45&gt;18%&lt;/color&gt;, kích hoạt mỗi 5 giây.
+          <t>&lt;color=#c89a45&gt;Tăng Cấp Chiến Đấu: Giảm thời gian hồi chiêu Kỹ Năng Echo và tăng DMG Kỹ Năng Echo.&lt;/color&gt;
+Sử dụng Kỹ Năng Echo sẽ tăng hiệu suất Tăng Cấp Chiến Đấu lên &lt;color=#c89a45&gt;20%&lt;/color&gt; trong 12 giây, kích hoạt mỗi 5 giây. Đánh trúng mục tiêu bằng Kỹ Năng Echo sẽ giảm Độ Mạnh Rung Động của chúng đi &lt;color=#c89a45&gt;18%&lt;/color&gt;, kích hoạt mỗi 5 giây.
 &lt;size=5&gt; &lt;/size&gt;
-A: Đánh trúng mục tiêu bằng Kỹ Năng Echo sẽ giảm thêm &lt;color=#c89a45&gt;18%&lt;/color&gt; Vibration Strength Động của chúng và hồi &lt;color=#c89a45&gt;50&lt;/color&gt; Concerto Energy cho tất cả thành viên trong đội. Hiệu ứng này kích hoạt mỗi 5 giây.
+A: Đánh trúng mục tiêu bằng Kỹ Năng Echo sẽ giảm thêm &lt;color=#c89a45&gt;18%&lt;/color&gt; Độ Mạnh Rung Động của chúng và hồi &lt;color=#c89a45&gt;50&lt;/color&gt; Concerto Energy cho tất cả thành viên trong đội. Hiệu ứng này kích hoạt mỗi 5 giây.
 &lt;size=5&gt; &lt;/size&gt;
-S: Đánh trúng mục tiêu sẽ giảm Cooldown chiêu Kỹ Năng Echo đi &lt;color=#c89a45&gt;50%&lt;/color&gt;. Hiệu ứng này kích hoạt mỗi 5 giây.
+S: Đánh trúng mục tiêu sẽ giảm thời gian hồi chiêu Kỹ Năng Echo đi &lt;color=#c89a45&gt;50%&lt;/color&gt;. Hiệu ứng này kích hoạt mỗi 5 giây.
 &lt;size=5&gt; &lt;/size&gt;
-SS: Sát thương Kỹ Năng Echo tăng thêm &lt;color=#c89a45&gt;1500%&lt;/color&gt;.</t>
+SS: DMG Kỹ Năng Echo tăng thêm &lt;color=#c89a45&gt;1500%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11540,7 +11539,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Đánh trúng mục tiêu bằng Kỹ Năng Echo sẽ giảm Vibration Strength của mục tiêu.</t>
+          <t>Đánh trúng mục tiêu bằng Kỹ Năng Echo sẽ giảm Sức Rung của mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -11605,7 +11604,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Kỹ Năng Echo: Rapid Shade</t>
+          <t>Kỹ Năng Hồi Âm: Bóng Tối Thần Tốc</t>
         </is>
       </c>
     </row>
@@ -11670,7 +11669,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Tấn Công mục tiêu bị Spectro Frazzle sẽ giảm thêm &lt;color=#c89a45&gt;5%&lt;/color&gt; Vibration Strength mỗi 0,3 giây và hồi &lt;color=#c89a45&gt;10&lt;/color&gt; Concerto Energy cho toàn đội mỗi 3 giây.</t>
+          <t>Tấn Công mục tiêu bị Spectro Frazzle sẽ giảm thêm &lt;color=#c89a45&gt;5%&lt;/color&gt; Độ Rung mỗi 0,3 giây và hồi &lt;color=#c89a45&gt;10&lt;/color&gt; Năng Lượng Giao Hưởng cho toàn đội mỗi 3 giây.</t>
         </is>
       </c>
     </row>
@@ -11735,7 +11734,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Mỗi điểm Spectro Frazzle tăng thêm &lt;color=#c89a45&gt;18%&lt;/color&gt; sát thương của Resonator hiện tại. Tấn công mục tiêu có Spectro Frazzle sẽ giảm &lt;color=#c89a45&gt;10%&lt;/color&gt; Cooldown chiêu Kỹ Năng Resonance Liberation cho tất cả thành viên trong đội. Hiệu ứng này chỉ kích hoạt một lần mỗi 3 giây.</t>
+          <t>Mỗi điểm Spectro Frazzle tăng thêm &lt;color=#c89a45&gt;18%&lt;/color&gt; sát thương của Resonator hiện tại. Tấn công mục tiêu có Spectro Frazzle sẽ giảm &lt;color=#c89a45&gt;10%&lt;/color&gt; thời gian hồi chiêu Kỹ Năng Resonance Liberation cho tất cả thành viên trong đội. Hiệu ứng này chỉ kích hoạt một lần mỗi 3 giây.</t>
         </is>
       </c>
     </row>
@@ -11872,14 +11871,14 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>&lt;color=#c89a45&gt;Combat Rank Buff: Attacking targets with Spectro Frazzle increases damage dealt.&lt;/color&gt;
-Khi bắt đầu thử thách, Resonance Energy được hồi phục thêm 50%. Tấn công mục tiêu bị Spectro Frazzle làm tăng hiệu suất Cấp Độ Combat lên &lt;color=#c89a45&gt;20%&lt;/color&gt; trong 5 giây và cấp cho tất cả thành viên trong đội &lt;color=#c89a45&gt;1 stack&lt;/color&gt; Spectro Frazzle. Hai hiệu ứng này được kích hoạt mỗi 3 giây một lần. Mỗi tầng Spectro Frazzle làm tăng sát thương của Resonator đang hoạt động lên &lt;color=#c89a45&gt;2%&lt;/color&gt;.
+          <t>&lt;color=#c89a45&gt;Buff Cấp Độ Chiến Đấu: Tấn công mục tiêu bị Spectro Frazzle làm tăng sát thương gây ra.&lt;/color&gt;
+Khi bắt đầu thử thách, Resonance Energy được hồi phục thêm 50%. Tấn công mục tiêu bị Spectro Frazzle làm tăng hiệu suất Cấp Độ Chiến Đấu lên &lt;color=#c89a45&gt;20%&lt;/color&gt; trong 5 giây và cấp cho tất cả thành viên trong đội &lt;color=#c89a45&gt;1 tầng&lt;/color&gt; Spectro Frazzle. Hai hiệu ứng này được kích hoạt mỗi 3 giây một lần. Mỗi tầng Spectro Frazzle làm tăng sát thương của Resonator đang hoạt động lên &lt;color=#c89a45&gt;2%&lt;/color&gt;.
 &lt;size=5&gt; &lt;/size&gt;
 A: Tấn công mục tiêu bị Spectro Frazzle làm giảm thêm &lt;color=#c89a45&gt;5%&lt;/color&gt; Độ Bền Dao Động của chúng, kích hoạt mỗi 0,3 giây một lần, và hồi phục Concerto Energy của cả đội lên &lt;color=#c89a45&gt;10&lt;/color&gt;, kích hoạt mỗi 3 giây một lần.
 &lt;size=5&gt; &lt;/size&gt;
 S: Tấn công mục tiêu bị Spectro Frazzle hồi phục Resonance Energy của cả đội lên &lt;color=#c89a45&gt;10%&lt;/color&gt;. Hiệu ứng này có thể kích hoạt mỗi 3 giây một lần.
 &lt;size=5&gt; &lt;/size&gt;
-SS: Mỗi tầng Spectro Frazzle làm tăng sát thương của Resonator đang hoạt động thêm &lt;color=#c89a45&gt;18%&lt;/color&gt;. Tấn công mục tiêu bị Spectro Frazzle làm giảm Cooldown chiêu Resonance Liberation của cả đội đi &lt;color=#c89a45&gt;10%&lt;/color&gt;. Hiệu ứng này có thể kích hoạt mỗi 3 giây một lần.</t>
+SS: Mỗi tầng Spectro Frazzle làm tăng sát thương của Resonator đang hoạt động thêm &lt;color=#c89a45&gt;18%&lt;/color&gt;. Tấn công mục tiêu bị Spectro Frazzle làm giảm thời gian hồi chiêu Resonance Liberation của cả đội đi &lt;color=#c89a45&gt;10%&lt;/color&gt;. Hiệu ứng này có thể kích hoạt mỗi 3 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -11944,7 +11943,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Tấn Công mục tiêu bị Spectro Frazzle sẽ hồi Concerto Energy, Resonance Energy cho toàn đội và tăng sát thương của họ.</t>
+          <t>Tấn Công mục tiêu bị Spectro Frazzle sẽ hồi Năng Lượng Giao Hưởng, Resonance Energy cho toàn đội và tăng sát thương của họ.</t>
         </is>
       </c>
     </row>
@@ -12009,7 +12008,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Spectro Frazzle: Hội Tụ Năng Lượng</t>
+          <t>Rối Loạn Spectro: Hội Tụ Năng Lượng</t>
         </is>
       </c>
     </row>
@@ -12269,7 +12268,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Hạ gục kẻ địch đang có hiệu ứng Heavy Attack: Tinh Thần Chiến Đấu</t>
+          <t>Hạ gục kẻ địch đang có hiệu ứng Đòn Nặng: Tinh Thần Chiến Đấu</t>
         </is>
       </c>
     </row>
@@ -12923,8 +12922,8 @@
       <c r="M187" t="inlineStr">
         <is>
           <t>Tốc độ di chuyển tăng {0}.
-Khi chạy nước rút, một Xoáy Năng Lượng sẽ xuất hiện quanh Resonator trong {1} giây. Nó sẽ phát nổ khi Resonator dừng di chuyển, gây sát thương diện rộng. Hiệu ứng này có Cooldown chiêu {2} giây.
-Sau khi sử dụng Resonance Liberation hoặc đánh bại &lt;SapTag=3&gt;{3}&lt;/SapTag&gt;, Cooldown chiêu của Ma Trận Bão sẽ được đặt lại.
+Khi chạy nước rút, một Xoáy Năng Lượng sẽ xuất hiện quanh Resonator trong {1} giây. Nó sẽ phát nổ khi Resonator dừng di chuyển, gây DMG diện rộng. Hiệu ứng này có thời gian hồi chiêu {2} giây.
+Sau khi sử dụng Resonance Liberation hoặc đánh bại &lt;SapTag=3&gt;{3}&lt;/SapTag&gt;, thời gian hồi chiêu của Ma Trận Bão sẽ được đặt lại.
 Khi Roccia kích hoạt Ma Trận Bão, Hệ Số Sát Thương của Xoáy Năng Lượng sẽ được tăng thêm.</t>
         </is>
       </c>
@@ -12991,7 +12990,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Thực hiện Đòn Lao Xuống, Dodge thành công và Phản Đòn thành công sẽ tạo ra 1 Xoáy Năng Lượng kéo dài {0} giây, Cooldown {1} giây.
+          <t>Thực hiện Đòn Lao Xuống, Né Tránh thành công và Phản Đòn thành công sẽ tạo ra 1 Xoáy Năng Lượng kéo dài {0} giây, thời gian hồi {1} giây.
 Kích hoạt hiệu ứng này sẽ tạo khiên trong {2} giây cho Resonator đang hoạt động. Kích hoạt lại sẽ làm mới khiên.</t>
         </is>
       </c>
@@ -13057,7 +13056,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Khi di chuyển nhanh, mỗi giây bạn nhận được 1 tầng Sức Mạnh Bùng Nổ. Mỗi tầng tăng Tấn Công của Resonator đang kích hoạt thêm {0}, Havoc DMG thêm {1}, hiệu ứng kéo dài {2} giây. Hiệu ứng này có thể chồng chất tối đa &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=3}. Nhận tầng mới không làm kéo dài thời gian hiệu ứng.</t>
+          <t>Khi di chuyển nhanh, mỗi giây bạn nhận được 1 tầng Sức Mạnh Bùng Nổ. Mỗi tầng tăng ATK của Resonator đang kích hoạt thêm {0}, Sát Thương Havoc thêm {1}, hiệu ứng kéo dài {2} giây. Hiệu ứng này có thể chồng chất tối đa &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=3}. Nhận tầng mới không làm kéo dài thời gian hiệu ứng.</t>
         </is>
       </c>
     </row>
@@ -13122,7 +13121,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Basic Attack giữa không trung, Dodge thành công và Dodge Counter thành công sẽ cấp &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S= tầng P=tầng} Sức Mạnh Tuôn Trào. Hiệu ứng của Sức Mạnh Tuôn Trào sẽ được nhân đôi.</t>
+          <t>Basic Attack giữa không trung, né thành công và Dodge Counter thành công sẽ cấp &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S= tầng P=tầng} Sức Mạnh Tuôn Trào. Hiệu ứng của Sức Mạnh Tuôn Trào sẽ được nhân đôi.</t>
         </is>
       </c>
     </row>
@@ -13187,7 +13186,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Sau khi sử dụng Kỹ Năng Giới Thiệu, một vùng Đất Chaotic sẽ xuất hiện để tấn công các mục tiêu lân cận, gây Spectro DMG trong {0} giây. Mục tiêu bị tấn công nhận &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm} Erosion Aero và Spectro Frazzle.</t>
+          <t>Sau khi sử dụng Kỹ Năng Giới Thiệu, một vùng Đất Hỗn Loạn sẽ xuất hiện để tấn công các mục tiêu lân cận, gây Sát Thương Spectro trong {0} giây. Mục tiêu bị tấn công nhận &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm} Xói Mòn Aero và Rối Loạn Spectro.</t>
         </is>
       </c>
     </row>
@@ -13252,7 +13251,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Vùng Chaos gây hiệu ứng Hỗn Độn lên mục tiêu khi trúng đòn. Mục tiêu bị Hỗn Độn sẽ chịu thêm {0} sát thương Vụ Nổ Chaos khi trúng Aero Erosion và Spectro Frazzle.</t>
+          <t>Vùng Hỗn Loạn gây hiệu ứng Hỗn Độn lên mục tiêu khi trúng đòn. Mục tiêu bị Hỗn Độn sẽ chịu thêm {0} DMG Vụ Nổ Hỗn Loạn khi trúng Aero Erosion và Spectro Frazzle.</t>
         </is>
       </c>
     </row>
@@ -13382,7 +13381,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Mục tiêu bị ảnh hưởng bởi Đất Chaotic sẽ bị giảm {0} Phòng Ngự.</t>
+          <t>Mục tiêu bị ảnh hưởng bởi Đất Hỗn Loạn sẽ bị giảm {0} Phòng Ngự.</t>
         </is>
       </c>
     </row>
@@ -13447,7 +13446,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Sát thương của Aero Erosion và Spectro Frazzle tăng {0} lần khi tấn công mục tiêu trong Echo Chaotic.</t>
+          <t>DMG của Aero Erosion và Spectro Frazzle tăng {0} lần khi tấn công mục tiêu trong Tổ Tacet Hỗn Loạn.</t>
         </is>
       </c>
     </row>
@@ -13512,7 +13511,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Resonators trong Echo phục hồi HP bằng {0} HP tối đa mỗi giây.</t>
+          <t>Resonator trong Tổ Tacet phục hồi HP bằng {0} HP tối đa mỗi giây.</t>
         </is>
       </c>
     </row>
@@ -13577,7 +13576,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Resonators trong Echo Chaotic nhận Tấn Công tăng thêm {0} mỗi giây trong {1} giây. Hiệu ứng này có thể chồng chất lên đến &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2}.</t>
+          <t>Resonator trong Tổ Tacet Hỗn Loạn nhận ATK tăng thêm {0} mỗi giây trong {1} giây. Hiệu ứng này có thể chồng chất lên đến &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2}.</t>
         </is>
       </c>
     </row>
@@ -13642,7 +13641,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Khi Resonator đánh trúng mục tiêu bằng Đòn Mid-air Attack, một thiên thạch sẽ được triệu hồi thêm, Cooldown chiêu là {0} giây.</t>
+          <t>Khi Resonator đánh trúng mục tiêu bằng Đòn Tấn Công Giữa Không, một thiên thạch sẽ được triệu hồi thêm, thời gian hồi chiêu là {0} giây.</t>
         </is>
       </c>
     </row>
@@ -13772,7 +13771,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Khi ở trên không, sát thương của Resonator tăng thêm {1} sau mỗi {0} giây, tối đa &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2}. Tất cả cộng dồn sẽ bị xóa khi Resonator chạm đất.</t>
+          <t>Khi ở trên không, DMG của Resonator tăng thêm {1} sau mỗi {0} giây, tối đa &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2}. Tất cả cộng dồn sẽ bị xóa khi Resonator chạm đất.</t>
         </is>
       </c>
     </row>
@@ -13902,7 +13901,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Phòng Ngự của mục tiêu trong Echo Cháy Bỏng bị giảm {0}.</t>
+          <t>Phòng Ngự của mục tiêu trong Tổ Tacet Cháy Bỏng bị giảm {0}.</t>
         </is>
       </c>
     </row>
@@ -14097,7 +14096,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Khi Resonator đánh trúng mục tiêu bằng Basic Attack hoặc gây Sát Thương Basic Attack, một Sao Băng sẽ được triệu hồi thêm, kích hoạt mỗi {0} giây một lần.</t>
+          <t>Khi Resonator đánh trúng mục tiêu bằng Đòn Cơ Bản hoặc gây Sát Thương Đòn Cơ Bản, một Sao Băng sẽ được triệu hồi thêm, kích hoạt mỗi {0} giây một lần.</t>
         </is>
       </c>
     </row>
@@ -14227,7 +14226,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Mục tiêu trúng Đòn Thunder sẽ bị giảm {0} Phòng Ngự.</t>
+          <t>Mục tiêu trúng Đòn Sấm Sét sẽ bị giảm {0} Phòng Ngự.</t>
         </is>
       </c>
     </row>
@@ -14292,7 +14291,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Khi Resonators đạt STA tối đa, Phòng Ngự và Tấn Công của họ sẽ tăng thêm {0}, Crit. Rate tăng thêm {1}.</t>
+          <t>Khi Resonator đạt STA tối đa, Phòng Ngự và ATK của họ sẽ tăng thêm {0}, Crit. Rate tăng thêm {1}.</t>
         </is>
       </c>
     </row>
@@ -14357,7 +14356,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Liberation hồi phục 200 Thể Lực. Đánh trúng mục tiêu bằng Dodge Counter sẽ hồi phục 100 Thể Lực.</t>
+          <t>Kích hoạt Resonance Liberation hồi phục 200 STA. Đánh trúng mục tiêu bằng Dodge Counter Tránh sẽ hồi phục 100 STA.</t>
         </is>
       </c>
     </row>
@@ -14422,7 +14421,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Khi di chuyển nhanh, Resonators hồi phục {0} Resonance Energy mỗi giây và nhận &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=tầng P=tầng SapTag=1} Dâng Trào Năng Lượng. Mỗi tầng tăng Crit. Rate cho tất cả thành viên trong đội thêm {2} trong {4} giây, có thể chồng chất tối đa &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=3}.</t>
+          <t>Khi di chuyển nhanh, Resonator hồi phục {0} Resonance Energy mỗi giây và nhận &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=tầng P=tầng SapTag=1} Dâng Trào Năng Lượng. Mỗi tầng tăng Crit. Rate cho tất cả thành viên trong đội thêm {2} trong {4} giây, có thể chồng chất tối đa &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=3}.</t>
         </is>
       </c>
     </row>
@@ -14487,7 +14486,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Tất cả thành viên trong đội được Khuếch Đại Electro DMG thêm {0}.</t>
+          <t>Tất cả thành viên trong đội được Khuếch Đại Sát Thương Electro thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -14552,7 +14551,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Tấn Công của tất cả thành viên trong đội được tăng {0}.</t>
+          <t>ATK của tất cả thành viên trong đội được tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -14617,7 +14616,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Tăng {0} Tấn Công Attribute</t>
+          <t>Tăng {0} Tấn Công Thuộc tính</t>
         </is>
       </c>
     </row>
@@ -14682,7 +14681,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Resonators nhận Crit. Rate tăng {0} và Crit. DMG tăng {1}.</t>
+          <t>Resonator nhận Crit. Rate tăng {0} và Sát Thương Bạo Kích tăng {1}.</t>
         </is>
       </c>
     </row>
@@ -14747,7 +14746,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Khi hồi sinh, Tấn Công của Resonators tăng {1}, Crit. Rate tăng {2}, và Crit. DMG tăng {3} trong {0} giây.</t>
+          <t>Khi hồi sinh, ATK của Resonator tăng {1}, Crit. Rate tăng {2}, và Crit. DMG tăng {3} trong {0} giây.</t>
         </is>
       </c>
     </row>
@@ -14812,7 +14811,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Khuếch đại {0} Sát Thương Attribute</t>
+          <t>Khuếch đại {0} Sát Thương Thuộc tính</t>
         </is>
       </c>
     </row>
@@ -14877,7 +14876,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Tấn Công của Resonators tăng {1} sau mỗi {0} giây, có thể chồng chất lên đến &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2}. Tất cả chồng chất sẽ bị xóa khi Resonators bị hạ gục.</t>
+          <t>ATK của Resonator tăng {1} sau mỗi {0} giây, có thể chồng chất lên đến &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2}. Tất cả chồng chất sẽ bị xóa khi Resonator bị hạ gục.</t>
         </is>
       </c>
     </row>
@@ -14942,7 +14941,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Crit. DMG của Resonators tăng {1} sau mỗi {0} giây, có thể chồng chất lên đến &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2}. Tất cả chồng chất sẽ bị xóa khi Resonators bị hạ gục.</t>
+          <t>Crit. DMG của Resonator tăng {1} sau mỗi {0} giây, có thể chồng chất lên đến &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2}. Tất cả chồng chất sẽ bị xóa khi Resonator bị hạ gục.</t>
         </is>
       </c>
     </row>
@@ -15007,7 +15006,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Tất cả Resonators trong đội nhận được lá chắn tương đương {1} HP tối đa mỗi {0} giây.</t>
+          <t>Tất cả Resonator trong đội nhận được lá chắn tương đương {1} HP tối đa mỗi {0} giây.</t>
         </is>
       </c>
     </row>
@@ -15072,7 +15071,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Khi Resonators đánh trúng mục tiêu, có {0}% cơ hội hồi phục {1} HP cho tất cả Resonators trong đội, và {2}% cơ hội hồi phục {3} HP cho tất cả thành viên trong đội.</t>
+          <t>Khi Resonator đánh trúng mục tiêu, có {0}% cơ hội hồi phục {1} HP cho tất cả Resonator trong đội, và {2}% cơ hội hồi phục {3} HP cho tất cả thành viên trong đội.</t>
         </is>
       </c>
     </row>
@@ -15137,7 +15136,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Kích hoạt Intro Skill hoặc Resonance Liberation sẽ hồi phục thêm {0} Concerto Energy cho Resonator đang hoạt động.</t>
+          <t>Kích hoạt Kỹ Năng Khởi Động hoặc Resonance Liberation sẽ hồi phục thêm {0} Concerto Energy cho Resonator đang hoạt động.</t>
         </is>
       </c>
     </row>
@@ -15202,7 +15201,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Kích hoạt Intro Skill hoặc Resonance Liberation sẽ hồi phục thêm {0} Resonance Energy cho Resonator đang hoạt động.</t>
+          <t>Kích hoạt Kỹ Năng Khởi Động hoặc Resonance Liberation sẽ hồi phục thêm {0} Resonance Energy cho Resonator đang hoạt động.</t>
         </is>
       </c>
     </row>
@@ -15267,7 +15266,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Khi Resonators đánh trúng mục tiêu, có {0}% cơ hội hồi phục thêm {1} Concerto Energy cho tất cả Resonators trong đội, và {2}% cơ hội hồi phục {3} Concerto Energy cho tất cả Resonators trong đội.</t>
+          <t>Khi Resonator đánh trúng mục tiêu, có {0}% cơ hội hồi phục thêm {1} Concerto Energy cho tất cả Resonator trong đội, và {2}% cơ hội hồi phục {3} Concerto Energy cho tất cả Resonator trong đội.</t>
         </is>
       </c>
     </row>
@@ -15332,7 +15331,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Khi Resonators chủ động đánh bại mục tiêu, Sát Thương tăng thêm {0}, có thể tích lũy tối đa &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=1}. Tất cả hiệu ứng tích lũy sẽ mất khi Resonators bị hạ gục.</t>
+          <t>Khi Resonator chủ động đánh bại mục tiêu, Sát Thương tăng thêm {0}, có thể tích lũy tối đa &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=1}. Tất cả hiệu ứng tích lũy sẽ mất khi Resonator bị hạ gục.</t>
         </is>
       </c>
     </row>
@@ -15462,7 +15461,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>DEF tăng {0}.</t>
+          <t>Phòng Ngự tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -15527,7 +15526,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Glacio RES tăng thêm {0}.</t>
+          <t>Kháng Glacio tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -15592,7 +15591,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Fusion RES tăng thêm {0}.</t>
+          <t>Kháng Hợp Thể tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -15722,7 +15721,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Aero RES tăng {0}.</t>
+          <t>Kháng Gió tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -15917,7 +15916,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>ATK tăng thêm {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -16112,7 +16111,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Tăng {0} Sát Thương Basic.</t>
+          <t>Tăng {0} Sát Thương Cơ Bản.</t>
         </is>
       </c>
     </row>
@@ -16372,7 +16371,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Glacio DMG Bonus được tăng thêm {0}.</t>
+          <t>Thêm Sát Thương Băng giá được tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -16437,7 +16436,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Fusion DMG Bonus thêm {0}.</t>
+          <t>Tăng Sát Thương Fusion thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -16502,7 +16501,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Electro DMG Bonus được tăng thêm {0}.</t>
+          <t>Thêm Sát Thương Electro được tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -16567,7 +16566,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Aero DMG Bonus được tăng thêm {0}.</t>
+          <t>Tăng Sát Thương Aero được tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -16632,7 +16631,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Spectro DMG Bonus tăng thêm {0}.</t>
+          <t>Thêm Sát Thương Spectro tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -16697,7 +16696,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Havoc DMG Bonus thêm {0}.</t>
+          <t>Tăng Sát Thương Havoc thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -17347,7 +17346,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Restoration Station hồi sinh Resonators của bạn và khôi phục HP của họ về 100%.</t>
+          <t>Trạm Phục Hồi hồi sinh Resonator của bạn và khôi phục HP của họ về 100%.</t>
         </is>
       </c>
     </row>
@@ -17412,7 +17411,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Thời Gian Trận Đấu</t>
+          <t>Thời gian trận đấu</t>
         </is>
       </c>
     </row>
@@ -17542,7 +17541,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Xếp chồng &lt;color=Highlight&gt;on top of all Cubes&lt;/color&gt;</t>
+          <t>Xếp chồng &lt;color=Highlight&gt;lên tất cả các Khối Lập Phương&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -17607,7 +17606,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Cộng dồn &lt;color=Highlight&gt;Stack&lt;/color&gt; với các Khối Lập Phương trên bệ hiện tại và di chuyển cùng nhau.</t>
+          <t>Xếp chồng cùng các Khối Lập Phương trên bệ hiện tại và di chuyển cùng nhau.</t>
         </is>
       </c>
     </row>
@@ -17737,7 +17736,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Kỹ năng đã kích hoạt!</t>
+          <t>Kỹ năng kích hoạt!</t>
         </is>
       </c>
     </row>
@@ -17803,8 +17802,8 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;DMG Enhancement&lt;/te&gt;]&lt;/color&gt;
-Combat Machines trên tường gây thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương, trong khi Combat Machines trên mặt đất và trần nhà gây ít hơn &lt;color=Highlight&gt;{1}&lt;/color&gt; Sát Thương.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;Tăng Sát Thương&lt;/te&gt;]&lt;/color&gt;
+Máy Chiến Đấu trên tường gây thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương, trong khi Máy Chiến Đấu trên mặt đất và trần nhà gây ít hơn &lt;color=Highlight&gt;{1}&lt;/color&gt; Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -17870,8 +17869,8 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;DMG Enhancement&lt;/te&gt;]&lt;/color&gt;
-Combat Machines trên trần gây thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương, trong khi Combat Machines trên mặt đất và tường gây ít hơn &lt;color=Highlight&gt;{1}&lt;/color&gt; Sát Thương.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;Tăng Sát Thương&lt;/te&gt;]&lt;/color&gt;
+Máy Chiến Đấu trên trần gây thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương, trong khi Máy Chiến Đấu trên mặt đất và tường gây ít hơn &lt;color=Highlight&gt;{1}&lt;/color&gt; Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -17937,8 +17936,8 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;DMG Enhancement&lt;/te&gt;]&lt;/color&gt;
-Combat Machines trên mặt đất gây thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương, trong khi Combat Machines trên tường và trần gây ít hơn &lt;color=Highlight&gt;{1}&lt;/color&gt; Sát Thương.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;Tăng Sát Thương&lt;/te&gt;]&lt;/color&gt;
+Máy Chiến Đấu trên mặt đất gây thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương, trong khi Máy Chiến Đấu trên tường và trần gây ít hơn &lt;color=Highlight&gt;{1}&lt;/color&gt; Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -18005,9 +18004,9 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;DMG Enhancement&lt;/te&gt;]&lt;/color&gt;
-&lt;color=#e8aa32&gt;[&lt;te href=750023&gt;Fusion-Type Combat Machine&lt;/te&gt;]&lt;/color&gt;
-Combat Machines Loại Fusion gây thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;Tăng Sát Thương&lt;/te&gt;]&lt;/color&gt;
+&lt;color=#e8aa32&gt;[&lt;te href=750023&gt;Máy Chiến Đấu Loại Fusion&lt;/te&gt;]&lt;/color&gt;
+Máy Chiến Đấu Loại Fusion gây thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -18074,9 +18073,9 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;DMG Enhancement&lt;/te&gt;]&lt;/color&gt;
-&lt;color=#e8aa32&gt;[&lt;te href=750025&gt;Electro-Type Combat Machine&lt;/te&gt;]&lt;/color&gt;
-Combat Machines Kiểu Electro gây thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; sát thương.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;Tăng Sát Thương&lt;/te&gt;]&lt;/color&gt;
+&lt;color=#e8aa32&gt;[&lt;te href=750025&gt;Máy Chiến Đấu Kiểu Electro&lt;/te&gt;]&lt;/color&gt;
+Máy Chiến Đấu Kiểu Electro gây thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; DMG.</t>
         </is>
       </c>
     </row>
@@ -18143,9 +18142,9 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;DMG Enhancement&lt;/te&gt;]&lt;/color&gt;
-&lt;color=#e8aa32&gt;[&lt;te href=750024&gt;Aero-Type Combat Machine&lt;/te&gt;]&lt;/color&gt;
-Combat Machines Loại Aero gây thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;Tăng Sát Thương&lt;/te&gt;]&lt;/color&gt;
+&lt;color=#e8aa32&gt;[&lt;te href=750024&gt;Máy Chiến Đấu Loại Aero&lt;/te&gt;]&lt;/color&gt;
+Máy Chiến Đấu Loại Aero gây thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -18212,9 +18211,9 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;DMG Enhancement&lt;/te&gt;]&lt;/color&gt;
-&lt;color=#e8aa32&gt;[&lt;te href=750022&gt;Glacio-Type Combat Machine&lt;/te&gt;]&lt;/color&gt;
-Combat Machines Loại Glacio gây thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;Tăng Sát Thương&lt;/te&gt;]&lt;/color&gt;
+&lt;color=#e8aa32&gt;[&lt;te href=750022&gt;Máy Chiến Đấu Loại Glacio&lt;/te&gt;]&lt;/color&gt;
+Máy Chiến Đấu Loại Glacio gây thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -18280,8 +18279,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750034&gt;Hunting Trap&lt;/te&gt;]&lt;/color&gt;
-Thời gian Burn được kéo dài thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>Thời gian Bỏng kéo dài thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -18347,8 +18345,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750034&gt;Hunting Trap&lt;/te&gt;]&lt;/color&gt;
-Thời gian Frozen được kéo dài thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>Thời gian Đông Cứng kéo dài thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -18414,8 +18411,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750034&gt;Hunting Trap&lt;/te&gt;]&lt;/color&gt;
-Thời gian **Paralysis** được kéo dài thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>Thời gian Tê Liệt kéo dài thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -18481,8 +18477,8 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;DMG Enhancement&lt;/te&gt;]&lt;/color&gt;
-Combat Machines trên tường gây thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương, trong khi Combat Machines trên mặt đất và trần nhà gây ít hơn &lt;color=Highlight&gt;{1}&lt;/color&gt; Sát Thương.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;Tăng Sát Thương&lt;/te&gt;]&lt;/color&gt;
+Máy Chiến Đấu trên tường gây thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương, trong khi Máy Chiến Đấu trên mặt đất và trần nhà gây ít hơn &lt;color=Highlight&gt;{1}&lt;/color&gt; Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -18548,8 +18544,8 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;DMG Enhancement&lt;/te&gt;]&lt;/color&gt;
-Combat Machines trên trần gây thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương, trong khi Combat Machines trên mặt đất và tường gây ít hơn &lt;color=Highlight&gt;{1}&lt;/color&gt; Sát Thương.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;Tăng Sát Thương&lt;/te&gt;]&lt;/color&gt;
+Máy Chiến Đấu trên trần gây thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương, trong khi Máy Chiến Đấu trên mặt đất và tường gây ít hơn &lt;color=Highlight&gt;{1}&lt;/color&gt; Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -18615,8 +18611,8 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;DMG Enhancement&lt;/te&gt;]&lt;/color&gt;
-Combat Machines trên mặt đất gây thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương, trong khi Combat Machines trên tường và trần gây ít hơn &lt;color=Highlight&gt;{1}&lt;/color&gt; Sát Thương.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;Tăng Sát Thương&lt;/te&gt;]&lt;/color&gt;
+Máy Chiến Đấu trên mặt đất gây thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương, trong khi Máy Chiến Đấu trên tường và trần gây ít hơn &lt;color=Highlight&gt;{1}&lt;/color&gt; Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -18683,9 +18679,9 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;DMG Enhancement&lt;/te&gt;]&lt;/color&gt;
-&lt;color=#e8aa32&gt;[&lt;te href=750023&gt;Fusion-Type Combat Machine&lt;/te&gt;]&lt;/color&gt;
-Combat Machines Loại Fusion gây thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;Tăng Sát Thương&lt;/te&gt;]&lt;/color&gt;
+&lt;color=#e8aa32&gt;[&lt;te href=750023&gt;Máy Chiến Đấu Loại Fusion&lt;/te&gt;]&lt;/color&gt;
+Máy Chiến Đấu Loại Fusion gây thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -18752,9 +18748,9 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;DMG Enhancement&lt;/te&gt;]&lt;/color&gt;
-&lt;color=#e8aa32&gt;[&lt;te href=750025&gt;Electro-Type Combat Machine&lt;/te&gt;]&lt;/color&gt;
-Máy Kiểu Electro gây thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; sát thương.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;Tăng Sát Thương&lt;/te&gt;]&lt;/color&gt;
+&lt;color=#e8aa32&gt;[&lt;te href=750025&gt;Máy Chiến Đấu Kiểu Electro&lt;/te&gt;]&lt;/color&gt;
+Máy Kiểu Electro gây thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; DMG.</t>
         </is>
       </c>
     </row>
@@ -18821,9 +18817,9 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;DMG Enhancement&lt;/te&gt;]&lt;/color&gt;
-&lt;color=#e8aa32&gt;[&lt;te href=750024&gt;Aero-Type Combat Machine&lt;/te&gt;]&lt;/color&gt;
-Máy Combat Kiểu Aero gây thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; sát thương.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;Tăng Sát Thương&lt;/te&gt;]&lt;/color&gt;
+&lt;color=#e8aa32&gt;[&lt;te href=750024&gt;Máy Chiến Đấu Kiểu Aero&lt;/te&gt;]&lt;/color&gt;
+Máy Chiến Đấu Kiểu Aero gây thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; DMG.</t>
         </is>
       </c>
     </row>
@@ -18890,9 +18886,9 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;DMG Enhancement&lt;/te&gt;]&lt;/color&gt;
-&lt;color=#e8aa32&gt;[&lt;te href=750022&gt;Glacio-Type Combat Machine&lt;/te&gt;]&lt;/color&gt;
-Combat Machines Loại Glacio gây thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;Tăng Sát Thương&lt;/te&gt;]&lt;/color&gt;
+&lt;color=#e8aa32&gt;[&lt;te href=750022&gt;Máy Chiến Đấu Loại Glacio&lt;/te&gt;]&lt;/color&gt;
+Máy Chiến Đấu Loại Glacio gây thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -18958,8 +18954,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750034&gt;Hunting Trap&lt;/te&gt;]&lt;/color&gt;
-Thời gian Burn được kéo dài thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>Thời gian Bỏng kéo dài thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -19025,8 +19020,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750034&gt;Hunting Trap&lt;/te&gt;]&lt;/color&gt;
-Thời gian Frozen được kéo dài thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>Thời gian Đông Cứng kéo dài thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -19092,8 +19086,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750034&gt;Hunting Trap&lt;/te&gt;]&lt;/color&gt;
-Thời gian &lt;color=Highlight&gt;Paralysis&lt;/color&gt; được kéo dài thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>Thời gian Tê Liệt kéo dài thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -19159,8 +19152,8 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750030&gt;Saturation Fire&lt;/te&gt;]&lt;/color&gt;
-Mỗi khi Máy Combat tấn công &lt;color=Highlight&gt;{0}&lt;/color&gt; lần, Attack Speed của nó sẽ tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt; trong &lt;color=Highlight&gt;{4}s&lt;/color&gt;, có thể tích lũy tối đa &lt;color=Highlight&gt;{2}&lt;/color&gt; lần. Khi đạt tối đa, Crit. DMG của nó tăng thêm &lt;color=Highlight&gt;{3}&lt;/color&gt;.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750030&gt;Bắn Phủ Kín&lt;/te&gt;]&lt;/color&gt;
+Mỗi khi Máy Chiến Đấu tấn công &lt;color=Highlight&gt;{0}&lt;/color&gt; lần, Tốc Độ Tấn Công của nó sẽ tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt; trong &lt;color=Highlight&gt;{4} giây&lt;/color&gt;, có thể tích lũy tối đa &lt;color=Highlight&gt;{2}&lt;/color&gt; lần. Khi đạt tối đa, Crit. DMG của nó tăng thêm &lt;color=Highlight&gt;{3}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -19227,9 +19220,9 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750030&gt;Saturation Fire&lt;/te&gt;]&lt;/color&gt;
-&lt;color=#e8aa32&gt;[&lt;te href=750031&gt;Core&lt;/te&gt;]&lt;/color&gt;
-Khi đánh bại Tacet Discord bị Đông Cứng/Bối Rối/Chậm Chạp, chúng sẽ Đông Cứng các Tacet Discord gần đó trong &lt;color=Highlight&gt;{0} giây&lt;/color&gt;, gây &lt;color=Highlight&gt;{1}&lt;/color&gt; Glacio DMG.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750030&gt;Bắn Phủ Kín&lt;/te&gt;]&lt;/color&gt;
+&lt;color=#e8aa32&gt;[&lt;te href=750031&gt;Lõi&lt;/te&gt;]&lt;/color&gt;
+Khi đánh bại Tacet Discord bị Đông Cứng/Bối Rối/Chậm Chạp, chúng sẽ Đông Cứng các Tacet Discord gần đó trong &lt;color=Highlight&gt;{0} giây&lt;/color&gt;, gây &lt;color=Highlight&gt;{1}&lt;/color&gt; Sát Thương Glacio.</t>
         </is>
       </c>
     </row>
@@ -19296,9 +19289,9 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750030&gt;Saturation Fire&lt;/te&gt;]&lt;/color&gt;
-&lt;color=#e8aa32&gt;[&lt;te href=750031&gt;Core&lt;/te&gt;]&lt;/color&gt;
-Khi Tacet Discord chịu Glacio DMG hoặc Electro, chúng sẽ tích lũy Năng Lượng Nổ. Khi đạt &lt;color=Highlight&gt;{0}&lt;/color&gt; tầng, năng lượng sẽ phát nổ, gây &lt;color=Highlight&gt;{1}&lt;/color&gt; Glacio DMG trong phạm vi nhất định và Đông Cứng các Tacet Discord trúng đòn trong &lt;color=Highlight&gt;{2} giây&lt;/color&gt;.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750030&gt;Bắn Phủ Kín&lt;/te&gt;]&lt;/color&gt;
+&lt;color=#e8aa32&gt;[&lt;te href=750031&gt;Lõi&lt;/te&gt;]&lt;/color&gt;
+Khi Tacet Discord chịu Sát Thương Glacio hoặc Electro, chúng sẽ tích lũy Năng Lượng Nổ. Khi đạt &lt;color=Highlight&gt;{0}&lt;/color&gt; tầng, năng lượng sẽ phát nổ, gây &lt;color=Highlight&gt;{1}&lt;/color&gt; Sát Thương Glacio trong phạm vi nhất định và Đông Cứng các Tacet Discord trúng đòn trong &lt;color=Highlight&gt;{2} giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -19364,8 +19357,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750034&gt;Hunting Trap&lt;/te&gt;]&lt;/color&gt;
-Thời gian Frozen/Confusion/Slow được kéo dài thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>Thời gian Đông Cứng/Mê Muội/Làm Chậm kéo dài thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -19432,9 +19424,9 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750030&gt;Saturation Fire&lt;/te&gt;]&lt;/color&gt;
-&lt;color=#e8aa32&gt;[&lt;te href=750033&gt;Enhancement Field&lt;/te&gt;]&lt;/color&gt;
-Combat Machines loại Electro tăng Crit. Rate cho các Combat Machines trong 9 ô lưới lân cận thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;, có thể tích lũy tối đa &lt;color=Highlight&gt;{1}&lt;/color&gt; lần.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750030&gt;Bắn Phủ Kín&lt;/te&gt;]&lt;/color&gt;
+&lt;color=#e8aa32&gt;[&lt;te href=750033&gt;Trường Tăng Cường&lt;/te&gt;]&lt;/color&gt;
+Máy Chiến Đấu loại Electro tăng Crit. Rate cho các Máy Chiến Đấu trong 9 ô lưới lân cận thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;, có thể tích lũy tối đa &lt;color=Highlight&gt;{1}&lt;/color&gt; lần.</t>
         </is>
       </c>
     </row>
@@ -19501,9 +19493,9 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750030&gt;Saturation Fire&lt;/te&gt;]&lt;/color&gt;
-&lt;color=#e8aa32&gt;[&lt;te href=750033&gt;Enhancement Field&lt;/te&gt;]&lt;/color&gt;
-Combat Machines loại Glacio tăng Attack Speed cho các Combat Machines trong 9 ô lưới lân cận thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;, có thể tích lũy tối đa &lt;color=Highlight&gt;{1}&lt;/color&gt; lần.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750030&gt;Bắn Phủ Kín&lt;/te&gt;]&lt;/color&gt;
+&lt;color=#e8aa32&gt;[&lt;te href=750033&gt;Trường Tăng Cường&lt;/te&gt;]&lt;/color&gt;
+Máy Chiến Đấu loại Glacio tăng Tốc Độ Tấn Công cho các Máy Chiến Đấu trong 9 ô lưới lân cận thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;, có thể tích lũy tối đa &lt;color=Highlight&gt;{1}&lt;/color&gt; lần.</t>
         </is>
       </c>
     </row>
@@ -19569,8 +19561,8 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750030&gt;Saturation Fire&lt;/te&gt;]&lt;/color&gt;
-Tất cả Combat Machines giảm Attack đi &lt;color=Highlight&gt;{0}&lt;/color&gt; và tăng Attack Speed lên &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750030&gt;Bắn Phủ Kín&lt;/te&gt;]&lt;/color&gt;
+Tất cả Máy Chiến Đấu giảm ATK đi &lt;color=Highlight&gt;{0}&lt;/color&gt; và tăng Tốc Độ ATK lên &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -19636,7 +19628,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750034&gt;Hunting Trap&lt;/te&gt;]&lt;/color&gt;
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750034&gt;Bẫy Săn Mồi&lt;/te&gt;]&lt;/color&gt;
 Mỗi loại hiệu ứng suy yếu trên Tacet Discord sẽ tăng Crit. Rate khi tấn công chúng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
@@ -19703,8 +19695,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750034&gt;Hunting Trap&lt;/te&gt;]&lt;/color&gt;
-Tacet Discord bị làm chậm chịu thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; DMG.</t>
+          <t>Tổ Tacet bị Làm Chậm nhận thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -19770,7 +19761,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Tacet Discords bị &lt;color=#e8aa32&gt;[&lt;te href=750034&gt;Hunting Trap&lt;/te&gt;]&lt;/color&gt; **Frozen** và **Confused** chịu thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; DMG.</t>
+          <t>Tổ Tacet bị Đông Cứng và Mê Muội nhận thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -19836,8 +19827,8 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750034&gt;Hunting Trap&lt;/te&gt;]&lt;/color&gt;
-Crit. Rate của Combat Machines Kiểu Electro tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750034&gt;Bẫy Săn Mồi&lt;/te&gt;]&lt;/color&gt;
+Crit. Rate của Máy Chiến Đấu Kiểu Electro tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -19903,8 +19894,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750034&gt;Hunting Trap&lt;/te&gt;]&lt;/color&gt;
-Tỉ lệ Crit. Rate của Combat Machines Loại Băng tăng &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>Crit. Rate của Máy Chiến Đấu Loại Glacio tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -19970,8 +19960,8 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750030&gt;Saturation Fire&lt;/te&gt;]&lt;/color&gt;
-Mỗi khi Máy Combat tấn công &lt;color=Highlight&gt;{0}&lt;/color&gt; lần, Attack Speed của nó sẽ tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt; trong &lt;color=Highlight&gt;{4}s&lt;/color&gt;, có thể tích lũy tối đa &lt;color=Highlight&gt;{2}&lt;/color&gt; lần. Khi đạt tối đa, Crit. DMG của nó tăng thêm &lt;color=Highlight&gt;{3}&lt;/color&gt;.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750030&gt;Bắn Phủ Kín&lt;/te&gt;]&lt;/color&gt;
+Mỗi khi Máy Chiến Đấu tấn công &lt;color=Highlight&gt;{0}&lt;/color&gt; lần, Tốc Độ Tấn Công của nó sẽ tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt; trong &lt;color=Highlight&gt;{4} giây&lt;/color&gt;, có thể tích lũy tối đa &lt;color=Highlight&gt;{2}&lt;/color&gt; lần. Khi đạt tối đa, Crit. DMG của nó tăng thêm &lt;color=Highlight&gt;{3}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -20038,9 +20028,9 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750030&gt;Saturation Fire&lt;/te&gt;]&lt;/color&gt;
-&lt;color=#e8aa32&gt;[&lt;te href=750031&gt;Core&lt;/te&gt;]&lt;/color&gt;
-Khi đánh bại Tacet Discord bị Đông Cứng/Bối Rối/Chậm Chạp, chúng sẽ Đông Cứng các Tacet Discord gần đó trong &lt;color=Highlight&gt;{0} giây&lt;/color&gt;, gây &lt;color=Highlight&gt;{1}&lt;/color&gt; Glacio DMG.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750030&gt;Bắn Phủ Kín&lt;/te&gt;]&lt;/color&gt;
+&lt;color=#e8aa32&gt;[&lt;te href=750031&gt;Lõi&lt;/te&gt;]&lt;/color&gt;
+Khi đánh bại Tacet Discord bị Đông Cứng/Bối Rối/Chậm Chạp, chúng sẽ Đông Cứng các Tacet Discord gần đó trong &lt;color=Highlight&gt;{0} giây&lt;/color&gt;, gây &lt;color=Highlight&gt;{1}&lt;/color&gt; Sát Thương Glacio.</t>
         </is>
       </c>
     </row>
@@ -20107,9 +20097,9 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750030&gt;Saturation Fire&lt;/te&gt;]&lt;/color&gt;
-&lt;color=#e8aa32&gt;[&lt;te href=750031&gt;Core&lt;/te&gt;]&lt;/color&gt;
-Khi Tacet Discord chịu Glacio DMG hoặc Electro, chúng sẽ tích lũy Năng Lượng Nổ. Khi đạt &lt;color=Highlight&gt;{0}&lt;/color&gt; tầng, năng lượng sẽ phát nổ, gây &lt;color=Highlight&gt;{1}&lt;/color&gt; Glacio DMG trong phạm vi nhất định và Đông Cứng các Tacet Discord trúng đòn trong &lt;color=Highlight&gt;{2} giây&lt;/color&gt;.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750030&gt;Bắn Phủ Kín&lt;/te&gt;]&lt;/color&gt;
+&lt;color=#e8aa32&gt;[&lt;te href=750031&gt;Lõi&lt;/te&gt;]&lt;/color&gt;
+Khi Tacet Discord chịu Sát Thương Glacio hoặc Electro, chúng sẽ tích lũy Năng Lượng Nổ. Khi đạt &lt;color=Highlight&gt;{0}&lt;/color&gt; tầng, năng lượng sẽ phát nổ, gây &lt;color=Highlight&gt;{1}&lt;/color&gt; Sát Thương Glacio trong phạm vi nhất định và Đông Cứng các Tacet Discord trúng đòn trong &lt;color=Highlight&gt;{2} giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -20175,8 +20165,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750034&gt;Hunting Trap&lt;/te&gt;]&lt;/color&gt;
-Thời gian Frozen/Confusion/Slow được kéo dài thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>Thời gian Đông Cứng/Mê Muội/Làm Chậm kéo dài thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -20243,9 +20232,9 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750030&gt;Saturation Fire&lt;/te&gt;]&lt;/color&gt;
-&lt;color=#e8aa32&gt;[&lt;te href=750033&gt;Enhancement Field&lt;/te&gt;]&lt;/color&gt;
-Combat Machines loại Electro tăng Crit. Rate cho các Combat Machines trong 9 ô lưới lân cận thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;, có thể tích lũy tối đa &lt;color=Highlight&gt;{1}&lt;/color&gt; lần.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750030&gt;Bắn Phủ Kín&lt;/te&gt;]&lt;/color&gt;
+&lt;color=#e8aa32&gt;[&lt;te href=750033&gt;Trường Tăng Cường&lt;/te&gt;]&lt;/color&gt;
+Máy Chiến Đấu loại Electro tăng Crit. Rate cho các Máy Chiến Đấu trong 9 ô lưới lân cận thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;, có thể tích lũy tối đa &lt;color=Highlight&gt;{1}&lt;/color&gt; lần.</t>
         </is>
       </c>
     </row>
@@ -20312,9 +20301,9 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750030&gt;Saturation Fire&lt;/te&gt;]&lt;/color&gt;
-&lt;color=#e8aa32&gt;[&lt;te href=750033&gt;Enhancement Field&lt;/te&gt;]&lt;/color&gt;
-Combat Machines loại Glacio tăng Attack Speed cho các Combat Machines trong 9 ô lưới lân cận thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;, có thể tích lũy tối đa &lt;color=Highlight&gt;{1}&lt;/color&gt; lần.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750030&gt;Bắn Phủ Kín&lt;/te&gt;]&lt;/color&gt;
+&lt;color=#e8aa32&gt;[&lt;te href=750033&gt;Trường Tăng Cường&lt;/te&gt;]&lt;/color&gt;
+Máy Chiến Đấu loại Glacio tăng Tốc Độ Tấn Công cho các Máy Chiến Đấu trong 9 ô lưới lân cận thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;, có thể tích lũy tối đa &lt;color=Highlight&gt;{1}&lt;/color&gt; lần.</t>
         </is>
       </c>
     </row>
@@ -20380,8 +20369,8 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750030&gt;Saturation Fire&lt;/te&gt;]&lt;/color&gt;
-Tất cả Combat Machines giảm Attack đi &lt;color=Highlight&gt;{0}&lt;/color&gt; và tăng Attack Speed lên &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750030&gt;Bắn Phủ Kín&lt;/te&gt;]&lt;/color&gt;
+Tất cả Máy Chiến Đấu giảm ATK đi &lt;color=Highlight&gt;{0}&lt;/color&gt; và tăng Tốc Độ ATK lên &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -20447,7 +20436,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750034&gt;Hunting Trap&lt;/te&gt;]&lt;/color&gt;
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750034&gt;Bẫy Săn Mồi&lt;/te&gt;]&lt;/color&gt;
 Mỗi loại hiệu ứng suy yếu trên Tacet Discord sẽ tăng Crit. Rate khi tấn công chúng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
@@ -20514,8 +20503,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750034&gt;Hunting Trap&lt;/te&gt;]&lt;/color&gt;
-Tacet Discord bị làm chậm chịu thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; DMG.</t>
+          <t>Tổ Tacet bị Làm Chậm nhận thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -20581,7 +20569,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Tacet Discords bị &lt;color=#e8aa32&gt;[&lt;te href=750034&gt;Hunting Trap&lt;/te&gt;]&lt;/color&gt; **Frozen** và **Confused** chịu thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; DMG.</t>
+          <t>Tổ Tacet bị Đông Cứng và Mê Muội nhận thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -20647,8 +20635,8 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750034&gt;Hunting Trap&lt;/te&gt;]&lt;/color&gt;
-Crit. Rate của Combat Machines Kiểu Electro tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750034&gt;Bẫy Săn Mồi&lt;/te&gt;]&lt;/color&gt;
+Crit. Rate của Máy Chiến Đấu Kiểu Electro tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -20714,8 +20702,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750034&gt;Hunting Trap&lt;/te&gt;]&lt;/color&gt;
-Tỉ lệ Crit của Combat Machines Loại Băng tăng &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>Crit. Rate của Máy Chiến Đấu Loại Glacio tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -20847,9 +20834,9 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi nhận Nhiệm Vụ Phụ &lt;color=Highlight&gt;Pulses of the Plains&lt;/color&gt;.
-Dưới Học Viện là một loạt máy in nhỏ. Khi Void Storm gây gián đoạn nghiêm trọng, chúng triển khai Cube để bảo vệ các bộ phận lõi.
-Sau khi Void Storm qua đi, các máy bị ảnh hưởng nặng cần được thiết lập lại thủ công. Người vận hành phải vô hiệu hóa Cube để khôi phục hoạt động bình thường.</t>
+          <t>Mở khóa sau khi nhận Nhiệm Vụ Phụ &lt;color=Highlight&gt;Nhịp Điệu Của Thảo Nguyên&lt;/color&gt;.
+Dưới Học Viện là một loạt máy in nhỏ. Khi Bão Hư Không gây gián đoạn nghiêm trọng, chúng triển khai Khối Lập Phương để bảo vệ các bộ phận lõi.
+Sau khi Bão Hư Không qua đi, các máy bị ảnh hưởng nặng cần được thiết lập lại thủ công. Người vận hành phải vô hiệu hóa Khối Lập Phương để khôi phục hoạt động bình thường.</t>
         </is>
       </c>
     </row>
@@ -20915,8 +20902,8 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Void Storm gây gián đoạn nghiêm trọng, chúng triển khai Cube Chặn để bảo vệ các bộ phận lõi.
-Sau khi Void Storm qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
+          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Bão Hư Không gây gián đoạn nghiêm trọng, chúng triển khai Khối Lập Phương Chặn để bảo vệ các bộ phận lõi.
+Sau khi Bão Hư Không qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
         </is>
       </c>
     </row>
@@ -20982,8 +20969,8 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Void Storm gây gián đoạn nghiêm trọng, chúng triển khai Cube Chặn để bảo vệ các bộ phận lõi.
-Sau khi Void Storm qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
+          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Bão Hư Không gây gián đoạn nghiêm trọng, chúng triển khai Khối Lập Phương Chặn để bảo vệ các bộ phận lõi.
+Sau khi Bão Hư Không qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
         </is>
       </c>
     </row>
@@ -21049,8 +21036,8 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Void Storm gây gián đoạn nghiêm trọng, chúng triển khai Cube Chặn để bảo vệ các bộ phận lõi.
-Sau khi Void Storm qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
+          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Bão Hư Không gây gián đoạn nghiêm trọng, chúng triển khai Khối Lập Phương Chặn để bảo vệ các bộ phận lõi.
+Sau khi Bão Hư Không qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
         </is>
       </c>
     </row>
@@ -21116,8 +21103,8 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Void Storm gây gián đoạn nghiêm trọng, chúng triển khai Cube Chặn để bảo vệ các bộ phận lõi.
-Sau khi Void Storm qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
+          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Bão Hư Không gây gián đoạn nghiêm trọng, chúng triển khai Khối Lập Phương Chặn để bảo vệ các bộ phận lõi.
+Sau khi Bão Hư Không qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
         </is>
       </c>
     </row>
@@ -21183,8 +21170,8 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Void Storm gây gián đoạn nghiêm trọng, chúng triển khai Cube Chặn để bảo vệ các bộ phận lõi.
-Sau khi Void Storm qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
+          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Bão Hư Không gây gián đoạn nghiêm trọng, chúng triển khai Khối Lập Phương Chặn để bảo vệ các bộ phận lõi.
+Sau khi Bão Hư Không qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
         </is>
       </c>
     </row>
@@ -21250,8 +21237,8 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Void Storm gây gián đoạn nghiêm trọng, chúng triển khai Cube Chặn để bảo vệ các bộ phận lõi.
-Sau khi Void Storm qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
+          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Bão Hư Không gây gián đoạn nghiêm trọng, chúng triển khai Khối Lập Phương Chặn để bảo vệ các bộ phận lõi.
+Sau khi Bão Hư Không qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
         </is>
       </c>
     </row>
@@ -21317,8 +21304,8 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Void Storm gây gián đoạn nghiêm trọng, chúng triển khai Cube Chặn để bảo vệ các bộ phận lõi.
-Sau khi Void Storm qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
+          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Bão Hư Không gây gián đoạn nghiêm trọng, chúng triển khai Khối Lập Phương Chặn để bảo vệ các bộ phận lõi.
+Sau khi Bão Hư Không qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
         </is>
       </c>
     </row>
@@ -21384,8 +21371,8 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Void Storm gây gián đoạn nghiêm trọng, chúng triển khai Cube Chặn để bảo vệ các bộ phận lõi.
-Sau khi Void Storm qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
+          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Bão Hư Không gây gián đoạn nghiêm trọng, chúng triển khai Khối Lập Phương Chặn để bảo vệ các bộ phận lõi.
+Sau khi Bão Hư Không qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
         </is>
       </c>
     </row>
@@ -21451,8 +21438,8 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Void Storm gây gián đoạn nghiêm trọng, chúng triển khai Cube Chặn để bảo vệ các bộ phận lõi.
-Sau khi Void Storm qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
+          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Bão Hư Không gây gián đoạn nghiêm trọng, chúng triển khai Khối Lập Phương Chặn để bảo vệ các bộ phận lõi.
+Sau khi Bão Hư Không qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
         </is>
       </c>
     </row>
@@ -21518,8 +21505,8 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Void Storm gây gián đoạn nghiêm trọng, chúng triển khai Cube Chặn để bảo vệ các bộ phận lõi.
-Sau khi Void Storm qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
+          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Bão Hư Không gây gián đoạn nghiêm trọng, chúng triển khai Khối Lập Phương Chặn để bảo vệ các bộ phận lõi.
+Sau khi Bão Hư Không qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
         </is>
       </c>
     </row>
@@ -21585,8 +21572,8 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Void Storm gây gián đoạn nghiêm trọng, chúng triển khai Cube Chặn để bảo vệ các bộ phận lõi.
-Sau khi Void Storm qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
+          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Bão Hư Không gây gián đoạn nghiêm trọng, chúng triển khai Khối Lập Phương Chặn để bảo vệ các bộ phận lõi.
+Sau khi Bão Hư Không qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
         </is>
       </c>
     </row>
@@ -21652,8 +21639,8 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Void Storm gây gián đoạn nghiêm trọng, chúng triển khai Cube Chặn để bảo vệ các bộ phận lõi.
-Sau khi Void Storm qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
+          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Bão Hư Không gây gián đoạn nghiêm trọng, chúng triển khai Khối Lập Phương Chặn để bảo vệ các bộ phận lõi.
+Sau khi Bão Hư Không qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
         </is>
       </c>
     </row>
@@ -21719,8 +21706,8 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Void Storm gây gián đoạn nghiêm trọng, chúng triển khai Cube Chặn để bảo vệ các bộ phận lõi.
-Sau khi Void Storm qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
+          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Bão Hư Không gây gián đoạn nghiêm trọng, chúng triển khai Khối Lập Phương Chặn để bảo vệ các bộ phận lõi.
+Sau khi Bão Hư Không qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
         </is>
       </c>
     </row>
@@ -21786,8 +21773,8 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Void Storm gây gián đoạn nghiêm trọng, chúng triển khai Cube Chặn để bảo vệ các bộ phận lõi.
-Sau khi Void Storm qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
+          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Bão Hư Không gây gián đoạn nghiêm trọng, chúng triển khai Khối Lập Phương Chặn để bảo vệ các bộ phận lõi.
+Sau khi Bão Hư Không qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
         </is>
       </c>
     </row>
@@ -21853,8 +21840,8 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Void Storm gây gián đoạn nghiêm trọng, chúng triển khai Cube Chặn để bảo vệ các bộ phận lõi.
-Sau khi Void Storm qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
+          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Bão Hư Không gây gián đoạn nghiêm trọng, chúng triển khai Khối Lập Phương Chặn để bảo vệ các bộ phận lõi.
+Sau khi Bão Hư Không qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
         </is>
       </c>
     </row>
@@ -21920,8 +21907,8 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Void Storm gây gián đoạn nghiêm trọng, chúng triển khai Cube Chặn để bảo vệ các bộ phận lõi.
-Sau khi Void Storm qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
+          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Bão Hư Không gây gián đoạn nghiêm trọng, chúng triển khai Khối Lập Phương Chặn để bảo vệ các bộ phận lõi.
+Sau khi Bão Hư Không qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
         </is>
       </c>
     </row>
@@ -21987,8 +21974,8 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Void Storm gây gián đoạn nghiêm trọng, chúng triển khai Cube Chặn để bảo vệ các bộ phận lõi.
-Sau khi Void Storm qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
+          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Bão Hư Không gây gián đoạn nghiêm trọng, chúng triển khai Khối Lập Phương Chặn để bảo vệ các bộ phận lõi.
+Sau khi Bão Hư Không qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
         </is>
       </c>
     </row>
@@ -22054,8 +22041,8 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Void Storm gây gián đoạn nghiêm trọng, chúng triển khai Cube Chặn để bảo vệ các bộ phận lõi.
-Sau khi Void Storm qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
+          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Bão Hư Không gây gián đoạn nghiêm trọng, chúng triển khai Khối Lập Phương Chặn để bảo vệ các bộ phận lõi.
+Sau khi Bão Hư Không qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
         </is>
       </c>
     </row>
@@ -22121,8 +22108,8 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Void Storm gây gián đoạn nghiêm trọng, chúng triển khai Cube Chặn để bảo vệ các bộ phận lõi.
-Sau khi Void Storm qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
+          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Bão Hư Không gây gián đoạn nghiêm trọng, chúng triển khai Khối Lập Phương Chặn để bảo vệ các bộ phận lõi.
+Sau khi Bão Hư Không qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
         </is>
       </c>
     </row>
@@ -22188,8 +22175,8 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Void Storm gây gián đoạn nghiêm trọng, chúng triển khai Cube Chặn để bảo vệ các bộ phận lõi.
-Sau khi Void Storm qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
+          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Bão Hư Không gây gián đoạn nghiêm trọng, chúng triển khai Khối Lập Phương Chặn để bảo vệ các bộ phận lõi.
+Sau khi Bão Hư Không qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
         </is>
       </c>
     </row>
@@ -22255,8 +22242,8 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Void Storm gây gián đoạn nghiêm trọng, chúng triển khai Cube Chặn để bảo vệ các bộ phận lõi.
-Sau khi Void Storm qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
+          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Bão Hư Không gây gián đoạn nghiêm trọng, chúng triển khai Khối Lập Phương Chặn để bảo vệ các bộ phận lõi.
+Sau khi Bão Hư Không qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
         </is>
       </c>
     </row>
@@ -22322,8 +22309,8 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Void Storm gây gián đoạn nghiêm trọng, chúng triển khai Cube Chặn để bảo vệ các bộ phận lõi.
-Sau khi Void Storm qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
+          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Bão Hư Không gây gián đoạn nghiêm trọng, chúng triển khai Khối Lập Phương Chặn để bảo vệ các bộ phận lõi.
+Sau khi Bão Hư Không qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
         </is>
       </c>
     </row>
@@ -22389,8 +22376,8 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Void Storm gây gián đoạn nghiêm trọng, chúng triển khai Cube Chặn để bảo vệ các bộ phận lõi.
-Sau khi Void Storm qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
+          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Bão Hư Không gây gián đoạn nghiêm trọng, chúng triển khai Khối Lập Phương Chặn để bảo vệ các bộ phận lõi.
+Sau khi Bão Hư Không qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
         </is>
       </c>
     </row>
@@ -22456,8 +22443,8 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Void Storm gây gián đoạn nghiêm trọng, chúng triển khai Cube Chặn để bảo vệ các bộ phận lõi.
-Sau khi Void Storm qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
+          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Bão Hư Không gây gián đoạn nghiêm trọng, chúng triển khai Khối Lập Phương Chặn để bảo vệ các bộ phận lõi.
+Sau khi Bão Hư Không qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
         </is>
       </c>
     </row>
@@ -22523,8 +22510,8 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Void Storm gây gián đoạn nghiêm trọng, chúng triển khai Cube Chặn để bảo vệ các bộ phận lõi.
-Sau khi Void Storm qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
+          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Bão Hư Không gây gián đoạn nghiêm trọng, chúng triển khai Khối Lập Phương Chặn để bảo vệ các bộ phận lõi.
+Sau khi Bão Hư Không qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
         </is>
       </c>
     </row>
@@ -22590,8 +22577,8 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Void Storm gây gián đoạn nghiêm trọng, chúng triển khai Cube Chặn để bảo vệ các bộ phận lõi.
-Sau khi Void Storm qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
+          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Bão Hư Không gây gián đoạn nghiêm trọng, chúng triển khai Khối Lập Phương Chặn để bảo vệ các bộ phận lõi.
+Sau khi Bão Hư Không qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
         </is>
       </c>
     </row>
@@ -22658,9 +22645,9 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi xây dựng lại &lt;color=Highlight&gt;Orbit Valley Pass - South&lt;/color&gt;.
-Dưới Học Viện là một loạt máy in nhỏ. Khi Void Storm gây ra sự gián đoạn nghiêm trọng, chúng triển khai Cube để bảo vệ các bộ phận lõi.
-Sau khi Void Storm đi qua, những máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng cần được thiết lập lại thủ công.</t>
+          <t>Mở khóa sau khi xây dựng lại &lt;color=Highlight&gt;Đèo Orbit Valley - Nam&lt;/color&gt;.
+Dưới Học Viện là một loạt máy in nhỏ. Khi Bão Hư Không gây ra sự gián đoạn nghiêm trọng, chúng triển khai Khối Lập Phương để bảo vệ các bộ phận lõi.
+Sau khi Bão Hư Không đi qua, những máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng cần được thiết lập lại thủ công.</t>
         </is>
       </c>
     </row>
@@ -22726,8 +22713,8 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Void Storm gây gián đoạn nghiêm trọng, chúng triển khai Cube Chặn để bảo vệ các bộ phận lõi.
-Sau khi Void Storm qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
+          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Bão Hư Không gây gián đoạn nghiêm trọng, chúng triển khai Khối Lập Phương Chặn để bảo vệ các bộ phận lõi.
+Sau khi Bão Hư Không qua đi, các máy bị ảnh hưởng nhẹ sẽ tự động khôi phục. Tuy nhiên, những máy bị ảnh hưởng nặng vẫn cần được thiết lập lại thủ công.</t>
         </is>
       </c>
     </row>
@@ -22989,7 +22976,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Resonance Nexus</t>
+          <t>Mạng Lưới Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -23122,8 +23109,8 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; khi ở dạng người.
-Khi nổi giận, hắn biến thành một tử thần dê u ám với &lt;color=HighlightB&gt;higher RES&lt;/color&gt; đối với &lt;color=Light&gt;Spectro DMG&lt;/color&gt; và &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; khi ở dạng người.
+Khi nổi giận, hắn biến thành một tử thần dê u ám với &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; đối với &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; và &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -23188,7 +23175,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; trước &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao hơn&lt;/color&gt; trước &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -23253,7 +23240,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Light&gt;Spectro DMG&lt;/color&gt; và &lt;color=Thunder&gt;Electro DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; và &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -23318,7 +23305,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; trước &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao hơn&lt;/color&gt; trước &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -23383,7 +23370,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Wind&gt;Aero DMG&lt;/color&gt; cao hơn.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; cao hơn.</t>
         </is>
       </c>
     </row>
@@ -23448,7 +23435,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Wind&gt;Aero DMG&lt;/color&gt; và &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; cao hơn.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; và &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; cao hơn.</t>
         </is>
       </c>
     </row>
@@ -23513,7 +23500,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Light&gt;Spectro DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -23578,7 +23565,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -23644,8 +23631,8 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Một loạt máy in nhỏ do Học Viện lắp đặt. Khi Void Storm gây gián đoạn nghiêm trọng, chúng triển khai Cube Blocker Lập Phương để bảo vệ các bộ phận cốt lõi.
-Sau khi Void Storm đi qua, các máy bị ảnh hưởng nặng cần được khởi động lại thủ công. Người vận hành phải vô hiệu hóa Cube Blocker Lập Phương để khôi phục hoạt động bình thường.</t>
+          <t>Một loạt máy in nhỏ do Học Viện lắp đặt. Khi Bão Hư Không gây gián đoạn nghiêm trọng, chúng triển khai Khối Chặn Lập Phương để bảo vệ các bộ phận cốt lõi.
+Sau khi Bão Hư Không đi qua, các máy bị ảnh hưởng nặng cần được khởi động lại thủ công. Người vận hành phải vô hiệu hóa Khối Chặn Lập Phương để khôi phục hoạt động bình thường.</t>
         </is>
       </c>
     </row>
@@ -23714,7 +23701,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Wind&gt;Aero DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
 Trạm không gian rơi xuống như một ngôi sao đang tàn, chôn vùi giấc mơ của một thời đại dưới băng và đất.
 Hắn từng là một trong những kẻ mộng mơ, từng sải bước giữa các vì sao.
 Nhưng giờ đây, hắn lẩn trốn trong bóng tối, bị Void tha hóa.
@@ -23783,7 +23770,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Cây Trưởng Lão Voidbane ở Sealed Fissure được bảo vệ bởi Năng Lực Resonance của Hiyuki. Dù không bị Voidmatter ô nhiễm nặng, cây vẫn bị đóng băng dưới lớp băng dày.</t>
+          <t>Cây Trưởng Lão Voidbane ở Khe Nứt Bị Phong Ấn được bảo vệ bởi Năng Lực Cộng Hưởng của Hiyuki. Dù không bị Voidmatter ô nhiễm nặng, cây vẫn bị đóng băng dưới lớp băng dày.</t>
         </is>
       </c>
     </row>
@@ -23913,7 +23900,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Sống sót trong thời gian mục tiêu</t>
+          <t>Cố gắng trụ vững đến thời gian mục tiêu</t>
         </is>
       </c>
     </row>
@@ -24043,7 +24030,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Một cánh cổng kỳ lạ dẫn đến Somnoire hiện ra, phía sau là một Dreamland bị bỏ hoang. Khi Phrolova lạc vào thế giới này, cô phát hiện vô số Echoes kỳ dị đã tụ tập ở đây, đóng vai trò như những người hầu của vùng đất thần tiên đã mất. Conductor quyết định ở lại để khôi phục vinh quang xưa, đồng thời lặng lẽ chờ đợi giấc mơ này hé lộ...</t>
+          <t>Một cánh cổng kỳ lạ dẫn đến Somnoire hiện ra, phía sau là một Dreamland bị bỏ hoang. Khi Phrolova lạc vào thế giới này, cô phát hiện vô số Echo kỳ dị đã tụ tập ở đây, đóng vai trò như những người hầu của vùng đất thần tiên đã mất. Nhạc trưởng quyết định ở lại để khôi phục vinh quang xưa, đồng thời lặng lẽ chờ đợi giấc mơ này hé lộ...</t>
         </is>
       </c>
     </row>
@@ -24175,7 +24162,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>COST 3 (Glacio DMG)</t>
+          <t>CHI PHÍ 3 (Sát Thương Glacio)</t>
         </is>
       </c>
     </row>
@@ -24240,7 +24227,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>COST 3 (Fusion DMG)</t>
+          <t>CHI PHÍ 3 (Sát Thương Fusion)</t>
         </is>
       </c>
     </row>
@@ -24305,7 +24292,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>COST 3 (Electro DMG)</t>
+          <t>CHI PHÍ 3 (Sát Thương Electro)</t>
         </is>
       </c>
     </row>
@@ -24370,7 +24357,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>COST 3 (Aero DMG)</t>
+          <t>CHI PHÍ 3 (Sát Thương Aero)</t>
         </is>
       </c>
     </row>
@@ -24435,7 +24422,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>COST 3 (Spectro DMG)</t>
+          <t>CHI PHÍ 3 (Sát Thương Spectro)</t>
         </is>
       </c>
     </row>
@@ -24500,7 +24487,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>COST 3 (Havoc DMG)</t>
+          <t>CHI PHÍ 3 (Sát Thương Havoc)</t>
         </is>
       </c>
     </row>
@@ -24704,13 +24691,13 @@
       <c r="M365" t="inlineStr">
         <is>
           <t>Về Sự Kiện
-Câu lạc bộ Peaks of Prestige tại Startorch Academy đang đối mặt với cuộc khủng hoảng lớn nhất từ trước đến nay. Nhưng mối đe dọa không đến từ bên ngoài những bức tường này, mà từ... chính những giáo viên luôn tự nhận là vì lợi ích của học sinh. Giờ đây, vận mệnh của câu lạc bộ nằm trọn trong tay cậu. Hãy giành lấy chiến thắng và đập tan bóng tối đang phủ xuống!
+Câu lạc bộ Peaks of Prestige tại Học viện Startorch đang đối mặt với cuộc khủng hoảng lớn nhất từ trước đến nay. Nhưng mối đe dọa không đến từ bên ngoài những bức tường này, mà từ... chính những giáo viên luôn tự nhận là vì lợi ích của học sinh. Giờ đây, vận mệnh của câu lạc bộ nằm trọn trong tay cậu. Hãy giành lấy chiến thắng và đập tan bóng tối đang phủ xuống!
 Điều Kiện Tham Gia
-Đạt Cấp Liên Minh 14 và kích hoạt Points Resonance Startorch Academy trong Nhiệm Vụ Chính \"Ngọn Lửa Dưới Băng Giá\" để mở khóa.
-Event Rules
+Đạt Cấp Liên Minh 14 và kích hoạt Điểm Cộng Hưởng Học viện Startorch trong Nhiệm Vụ Chính \"Ngọn Lửa Dưới Băng Giá\" để mở khóa.
+Quy Tắc Sự Kiện
 - Xây dựng bộ bài Peaks of Prestige riêng của bạn bằng những lá bài đặc biệt mới và đối đầu với mọi đấu thủ ở Lahai-Roi!
-- Kiếm điểm Xếp hạng Lahai-Roi bằng cách đánh bại đối thủ để tăng Cấp Bậc. Leo lên các bậc thang để mở khóa lá bài mới và Tactics mạnh mẽ.
-- Hoàn thành Challenges Phân Hạng để nhận những phần thưởng hậu hĩnh, bao gồm Phantom: Chop Chop độc quyền.
+- Kiếm điểm Xếp hạng Lahai-Roi bằng cách đánh bại đối thủ để tăng Cấp Bậc. Leo lên các bậc thang để mở khóa lá bài mới và Chiến Thuật mạnh mẽ.
+- Hoàn thành Thử Thách Phân Hạng để nhận những phần thưởng hậu hĩnh, bao gồm Phantom: Chop Chop độc quyền.
 - Tiến trình sự kiện không khả dụng trong Chế Độ Hợp Tác. Vui lòng thoát Chế Độ Hợp Tác để hoàn thành nhiệm vụ sự kiện.</t>
         </is>
       </c>
@@ -24785,13 +24772,13 @@
       <c r="M366" t="inlineStr">
         <is>
           <t>Về Sự Kiện
-Câu lạc bộ Peaks of Prestige tại Startorch Academy đang đối mặt với cuộc khủng hoảng lớn nhất từ trước đến nay. Nhưng mối đe dọa không đến từ bên ngoài những bức tường này, mà từ... chính những giáo viên luôn tự nhận là vì lợi ích của học sinh. Giờ đây, vận mệnh của câu lạc bộ nằm trọn trong tay cậu. Hãy giành lấy chiến thắng và đập tan bóng tối đang phủ xuống!
+Câu lạc bộ Peaks of Prestige tại Học viện Startorch đang đối mặt với cuộc khủng hoảng lớn nhất từ trước đến nay. Nhưng mối đe dọa không đến từ bên ngoài những bức tường này, mà từ... chính những giáo viên luôn tự nhận là vì lợi ích của học sinh. Giờ đây, vận mệnh của câu lạc bộ nằm trọn trong tay cậu. Hãy giành lấy chiến thắng và đập tan bóng tối đang phủ xuống!
 Điều Kiện Tham Gia
-Đạt Cấp Liên Minh 14 và kích hoạt Points Resonance Startorch Academy trong Nhiệm Vụ Chính \"Ngọn Lửa Dưới Băng Giá\" để mở khóa.
-Event Rules
+Đạt Cấp Liên Minh 14 và kích hoạt Điểm Cộng Hưởng Học viện Startorch trong Nhiệm Vụ Chính \"Ngọn Lửa Dưới Băng Giá\" để mở khóa.
+Quy Tắc Sự Kiện
 - Xây dựng bộ bài Peaks of Prestige riêng của bạn bằng những lá bài đặc biệt mới và đối đầu với mọi đấu thủ ở Lahai-Roi!
-- Kiếm điểm Xếp hạng Lahai-Roi bằng cách đánh bại đối thủ để tăng Cấp Bậc. Leo lên các bậc thang để mở khóa lá bài mới và Tactics mạnh mẽ.
-- Hoàn thành Challenges Phân Hạng để nhận những phần thưởng hậu hĩnh, bao gồm Phantom: Chop Chop độc quyền.
+- Kiếm điểm Xếp hạng Lahai-Roi bằng cách đánh bại đối thủ để tăng Cấp Bậc. Leo lên các bậc thang để mở khóa lá bài mới và Chiến Thuật mạnh mẽ.
+- Hoàn thành Thử Thách Phân Hạng để nhận những phần thưởng hậu hĩnh, bao gồm Phantom: Chop Chop độc quyền.
 - Tiến trình sự kiện không khả dụng trong Chế Độ Hợp Tác. Vui lòng thoát Chế Độ Hợp Tác để hoàn thành nhiệm vụ sự kiện.</t>
         </is>
       </c>
@@ -24858,7 +24845,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>KU-Raji từ Bờ Đen gửi lời nhắn tới cậu: Đài quan sát Spacetrek đã bị Void Storm phá hủy. Dù nó đóng vai trò then chốt trong việc lập bản đồ địa hình, hệ sinh thái và khí hậu của Lahai-Roi, việc tái thiết vẫn đang đình trệ…
+          <t>KU-Raji từ Bờ Đen gửi lời nhắn tới cậu: Đài quan sát Spacetrek đã bị Bão Hư Không phá hủy. Dù nó đóng vai trò then chốt trong việc lập bản đồ địa hình, hệ sinh thái và khí hậu của Lahai-Roi, việc tái thiết vẫn đang đình trệ…
 Giờ là lúc khôi phục vùng đất biên cương này. Hãy xây dựng lại mạng lưới tuyến đường của Lahai-Roi và hỗ trợ tái thiết Đài quan sát Spacetrek!</t>
         </is>
       </c>
@@ -25383,7 +25370,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Chúc cậu một ngày thật tuyệt vời, {PlayerName}. (Đã nhận hiệu ứng: Giảm Thời Gian Cooldown của Kỹ Năng Bám Đu lên 25% đến 4 giờ sáng)</t>
+          <t>Chúc cậu một ngày thật tuyệt vời, {PlayerName}. (Đã nhận hiệu ứng: Giảm Thời Gian hồi của Kỹ Năng Bám Đu lên 25% đến 4 giờ sáng)</t>
         </is>
       </c>
     </row>
@@ -25578,7 +25565,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Dùng năng lực Resonance quá nhiều chỉ khiến tình trạng của cô ấy tệ hơn thôi...</t>
+          <t>Dùng năng lực Cộng Hưởng quá nhiều chỉ khiến tình trạng của cô ấy tệ hơn thôi...</t>
         </is>
       </c>
     </row>
@@ -25643,7 +25630,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Ta cảm thấy Năng Lực Resonance của mình đang yếu dần, và sức mạnh của ta đến từ Người Bảo Vệ. Điều này chỉ có thể có nghĩa là tình trạng của Người Bảo Vệ đang trở nên tồi tệ hơn.</t>
+          <t>Ta cảm thấy Năng Lực Cộng Hưởng của mình đang yếu dần, và sức mạnh của ta đến từ Người Bảo Vệ. Điều này chỉ có thể có nghĩa là tình trạng của Người Bảo Vệ đang trở nên tồi tệ hơn.</t>
         </is>
       </c>
     </row>
@@ -25708,7 +25695,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Không phải ta đói đâu nhé. Chỉ là ta hay buồn ngủ thôi. Cơ thể ta như chỉ xử lý được thức ăn khi ta ngủ vậy.</t>
+          <t>Không phải tao đói đâu nhé. Chỉ là tao hay buồn ngủ thôi. Cơ thể tao như chỉ xử lý được thức ăn khi tao ngủ vậy.</t>
         </is>
       </c>
     </row>
@@ -25773,7 +25760,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Jinhsi được chọn từ khi còn là đứa trẻ sơ sinh nhờ năng lực Resonance, rồi được nuôi dưỡng tại City Hall để trở thành Resonator Được Chỉ Định của Sentinel.</t>
+          <t>Jinhsi được chọn từ khi còn là đứa trẻ sơ sinh nhờ năng lực Cộng Hưởng, rồi được nuôi dưỡng tại City Hall để trở thành Resonator Được Chỉ Định của Sentinel.</t>
         </is>
       </c>
     </row>
@@ -25838,7 +25825,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Dù đội tử thần của chúng không phải là đối thủ của Sentinel, nhưng bằng cách buộc nó phải ra tay, năng lực Resonance mạnh mẽ của Sentinel sẽ va chạm với năng lượng của Chronosorter. Điều này cuối cùng sẽ gây tổn hại cho chính nó.</t>
+          <t>Dù đội tử thần của chúng không phải là đối thủ của Sentinel, nhưng bằng cách buộc nó phải ra tay, năng lực Cộng Hưởng mạnh mẽ của Sentinel sẽ va chạm với năng lượng của Chronosorter. Điều này cuối cùng sẽ gây tổn hại cho chính nó.</t>
         </is>
       </c>
     </row>
@@ -26033,7 +26020,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Trước khi Jinhsi lên Núi Kiền Khôn, vảy bắt đầu xuất hiện trên người cô, và Resonance Ability của cô cũng dần yếu đi.</t>
+          <t>Trước khi Jinhsi lên Núi Kiền Khôn, vảy bắt đầu xuất hiện trên người cô, và Khả Năng Cộng Hưởng của cô cũng dần yếu đi.</t>
         </is>
       </c>
     </row>
@@ -26163,7 +26150,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Ta phải nói sự thật với cậu... Bởi cậu luôn là ưu tiên hàng đầu—không, là mục tiêu duy nhất của kẻ thù. Bọn The Fractsidus.</t>
+          <t>Ta phải nói sự thật với cậu... Bởi cậu luôn là ưu tiên hàng đầu—không, là mục tiêu duy nhất của kẻ thù. Bọn Fractsidus.</t>
         </is>
       </c>
     </row>
@@ -26293,7 +26280,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Bằng cách va chạm hai nguồn Resonance Energy, ta có thể kích hoạt Thức Tỉnh Resonance Thứ Hai. Qua đó, ta có thể đẩy năng lực Resonance của mình vượt giới hạn và triệu hồi Quyết Định Thời Gian để khôi phục dòng chảy thời gian.</t>
+          <t>Bằng cách va chạm hai nguồn năng lượng cộng hưởng, ta có thể kích hoạt Thức Tỉnh Cộng Hưởng Thứ Hai. Qua đó, ta có thể đẩy năng lực Cộng Hưởng của mình vượt giới hạn và triệu hồi Quyết Định Thời Gian để khôi phục dòng chảy thời gian.</t>
         </is>
       </c>
     </row>
@@ -26358,7 +26345,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Nếu cậu đối đầu với sức mạnh Resonance của tôi, chỉ cần một sai lầm nhỏ thôi cũng đủ khiến cậu bị Quá Tải và chỉ còn lại cái xác rỗng.</t>
+          <t>Nếu cậu đối đầu với sức mạnh Cộng Hưởng của tôi, chỉ cần một sai lầm nhỏ thôi cũng đủ khiến cậu bị Quá Tải và chỉ còn lại cái xác rỗng.</t>
         </is>
       </c>
     </row>
@@ -26878,7 +26865,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>May mắn thay, với Resonance Ability của Jinhsi, họ sẽ an toàn miễn là vẫn ở trên núi.</t>
+          <t>May mắn thay, với Khả Năng Cộng Hưởng của Jinhsi, họ sẽ an toàn miễn là vẫn ở trên núi.</t>
         </is>
       </c>
     </row>
@@ -26943,7 +26930,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>—Với Sự Thức Tỉnh Resonance Thứ Hai, chúng ta sẽ khai phá sức mạnh sánh ngang với các Sentinel... Quyền kiểm soát hoàn toàn quá trình Thức Tỉnh Resonator nhân tạo đã nằm trong tầm tay.</t>
+          <t>—Với Sự Thức Tỉnh Cộng Hưởng Thứ Hai, chúng ta sẽ khai phá sức mạnh sánh ngang với các Sentinel... Quyền kiểm soát hoàn toàn quá trình Thức Tỉnh Resonator nhân tạo đã nằm trong tầm tay.</t>
         </is>
       </c>
     </row>
@@ -27008,7 +26995,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Có người đã dùng Năng Lực Resonance ở đây, nhưng cảm giác này không phải sự hung hãn của Fractsidus... Đó là Jinhsi.</t>
+          <t>Có người đã dùng Năng Lực Cộng Hưởng ở đây, nhưng cảm giác này không phải sự hung hãn của Fractsidus... Đó là Jinhsi.</t>
         </is>
       </c>
     </row>
@@ -27138,7 +27125,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Hồng Trấn giống như một nơi trong giấc mơ của cậu vậy. Changli đoán rằng giấc mơ ấy có thể là ánh nhìn về quá khứ và ngọn đuốc dẫn lối tương lai. Nơi đây, cậu gặp gỡ Fractsidus, phát hiện dấu vết Resonance Ability của Jinhsi, và quyết định theo đuổi chúng.</t>
+          <t>Hongzhen giống như một nơi trong giấc mơ của cậu vậy. Changli đoán rằng giấc mơ ấy có thể là ánh nhìn về quá khứ và ngọn đuốc dẫn lối tương lai. Nơi đây, cậu gặp gỡ Fractsidus, phát hiện dấu vết Khả Năng Cộng Hưởng của Jinhsi, và quyết định theo đuổi chúng.</t>
         </is>
       </c>
     </row>
@@ -27268,7 +27255,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>"Cộng Hưởng".</t>
+          <t>"Sự Cộng Hưởng".</t>
         </is>
       </c>
     </row>
@@ -27333,7 +27320,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Sentinel không thể sửa chữa được, nên họ quyết định sao chép sức mạnh của nó lên một Resonator thông qua Resonance cưỡng bức...</t>
+          <t>Sentinel không thể sửa chữa được, nên họ quyết định sao chép sức mạnh của nó lên một Resonator thông qua Cộng Hưởng cưỡng bức...</t>
         </is>
       </c>
     </row>
@@ -27398,7 +27385,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Những thí nghiệm của họ đã tạo ra Chronosorter đầu tiên—một Vật Thể Resonance nhân tạo.</t>
+          <t>Những thí nghiệm của họ đã tạo ra Chronosorter đầu tiên—một Vật Thể Cộng Hưởng nhân tạo.</t>
         </is>
       </c>
     </row>
@@ -27528,7 +27515,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Tập tài liệu này xác nhận Chronosorters chính là các Vật Thể Resonance nhân tạo.</t>
+          <t>Tập tài liệu này xác nhận Chronosorters chính là các Vật Thể Cộng Hưởng nhân tạo.</t>
         </is>
       </c>
     </row>
@@ -27593,7 +27580,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Chúng kích hoạt khi chịu tác động mạnh để tạo ra Hiệu Ứng Resonance tương ứng.</t>
+          <t>Chúng kích hoạt khi chịu tác động mạnh để tạo ra Hiệu Ứng Cộng Hưởng tương ứng.</t>
         </is>
       </c>
     </row>
@@ -27658,7 +27645,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Ngoài ra, là những Vật Thể Resonance nhân tạo, khả năng của chúng cũng có giới hạn.</t>
+          <t>Ngoài ra, là những Vật Thể Cộng Hưởng nhân tạo, khả năng của chúng cũng có giới hạn.</t>
         </is>
       </c>
     </row>
@@ -27723,7 +27710,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Theo nghiên cứu của các học giả Tòa án Savantae, có một giả thuyết có thể giúp họ trở nên mạnh mẽ hơn—giả thuyết về Sự Thức Tỉnh Resonance Thứ Hai.</t>
+          <t>Theo nghiên cứu của các học giả Tòa án Savantae, có một giả thuyết có thể giúp họ trở nên mạnh mẽ hơn—giả thuyết về Sự Thức Tỉnh Cộng Hưởng Thứ Hai.</t>
         </is>
       </c>
     </row>
@@ -27788,7 +27775,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Đoạn nào nói về việc va chạm giữa hai tần số cộng hưởng có thể gây ra Sự Thức Tỉnh Resonance Thứ Hai...</t>
+          <t>Đoạn nào nói về việc va chạm giữa hai tần số cộng hưởng có thể gây ra Sự Thức Tỉnh Cộng Hưởng Thứ Hai...</t>
         </is>
       </c>
     </row>
@@ -27853,7 +27840,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>...Yes. Trận chiến đó phải xảy ra để kích hoạt Sự Thức Tỉnh Resonance Thứ Hai cho Jinhsi, giúp cô ấy phát huy sức mạnh Resonance mạnh mẽ hơn... Những khả năng cho phép khôi phục dòng chảy thời gian.</t>
+          <t>...Đúng vậy. Trận chiến đó phải xảy ra để kích hoạt Sự Thức Tỉnh Cộng Hưởng Thứ Hai cho Jinhsi, giúp cô ấy phát huy sức mạnh Cộng Hưởng mạnh mẽ hơn... Những khả năng cho phép khôi phục dòng chảy thời gian.</t>
         </is>
       </c>
     </row>
@@ -27983,7 +27970,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Điều này đã chứng minh rằng Sự Thức Tỉnh Lần Hai thực sự có thể cải thiện Resonance Ability.</t>
+          <t>Điều này đã chứng minh rằng Sự Thức Tỉnh Lần Hai thực sự có thể cải thiện Khả Năng Cộng Hưởng.</t>
         </is>
       </c>
     </row>
@@ -28048,7 +28035,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Để đảo ngược hiệu ứng lão hóa nhanh do Rối Loạn Thời Gian, tôi phải cố tình va chạm với năng lượng Resonance của Người Bảo Vệ trong trận chiến – kích hoạt Thức Tỉnh Resonance Thứ Hai. Điều đó sẽ đẩy sức mạnh của tôi vượt qua giới hạn.</t>
+          <t>Để đảo ngược hiệu ứng lão hóa nhanh do Rối Loạn Thời Gian, tôi phải cố tình va chạm với năng lượng Cộng Hưởng của Người Bảo Vệ trong trận chiến – kích hoạt Thức Tỉnh Cộng Hưởng Thứ Hai. Điều đó sẽ đẩy sức mạnh của tôi vượt qua giới hạn.</t>
         </is>
       </c>
     </row>
@@ -28113,7 +28100,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Chỉ Resonator Được Chỉ Định của Sentinel mới có thể phục hồi &lt;ano=ability to control time&gt;Temporal Mandate&lt;/ano&gt; của nó...</t>
+          <t>Chỉ có Resonator được Sentinel chỉ định mới có thể khôi phục &lt;ano=ability to control time&gt;Thẩm Quyền Thời Gian&lt;/ano&gt; của nó...</t>
         </is>
       </c>
     </row>
@@ -28178,7 +28165,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>...Ta có mối liên kết Resonance với Jué, nhưng chưa bao giờ thực sự dành thời gian để hiểu nó... Ta đã mù quáng trước nỗi đau của nó quá lâu rồi...</t>
+          <t>...Ta có mối liên kết Cộng Hưởng với Jué, nhưng chưa bao giờ thực sự dành thời gian để hiểu nó... Ta đã mù quáng trước nỗi đau của nó quá lâu rồi...</t>
         </is>
       </c>
     </row>
@@ -28373,7 +28360,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Tài liệu cho thấy Tòa án Savantae đã sử dụng Chronosorter để thử nghiệm giả thuyết về Sự Thức Tỉnh Resonance Thứ Hai, cho rằng va chạm giữa các tần số có thể khai phá tiềm năng lớn hơn trong một Resonator. Anh đưa ra giả thuyết rằng cuộc xung đột được tiên tri giữa Jinhsi và Sentinel nhằm giúp Jinhsi đạt được khả năng thao túng thời gian thông qua Sự Thức Tỉnh Thứ Hai này. Tuy nhiên, các thí nghiệm chỉ ra rằng việc Overlocking Resonator có thể là cần thiết để đạt được sức mạnh đó.</t>
+          <t>Tài liệu cho thấy Tòa án Savantae đã sử dụng Chronosorter để thử nghiệm giả thuyết về Sự Thức Tỉnh Cộng Hưởng Thứ Hai, cho rằng va chạm giữa các tần số có thể khai phá tiềm năng lớn hơn trong một Resonator. Anh đưa ra giả thuyết rằng cuộc xung đột được tiên tri giữa Jinhsi và Sentinel nhằm giúp Jinhsi đạt được khả năng thao túng thời gian thông qua Sự Thức Tỉnh Thứ Hai này. Tuy nhiên, các thí nghiệm chỉ ra rằng việc Overlocking Resonator có thể là cần thiết để đạt được sức mạnh đó.</t>
         </is>
       </c>
     </row>
@@ -28438,7 +28425,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Cuối cùng cậu cũng tìm thấy Jinhsi, nhưng trông cô đang rất suy yếu. Từ những ghi chép của Tòa án Savantae, cô biết được Sentinel đã bị thương khi đến Núi Firmament, và tình trạng ngày càng tồi tệ của nó đang khiến dòng thời gian trở nên bất ổn hơn bao giờ hết. Với Jinzhou đang lâm nguy, Jinhsi quyết định tự mình xác minh lời tuyên bố của Tòa án. Nếu cần, cô sẵn sàng giao chiến với Sentinel để kích hoạt Lần Resonance Thứ Hai, dù phải đánh đổi cả tính mạng.</t>
+          <t>Cuối cùng cậu cũng tìm thấy Jinhsi, nhưng trông cô đang rất suy yếu. Từ những ghi chép của Tòa án Savantae, cô biết được Sentinel đã bị thương khi đến Núi Firmament, và tình trạng ngày càng tồi tệ của nó đang khiến dòng thời gian trở nên bất ổn hơn bao giờ hết. Với Jinzhou đang lâm nguy, Jinhsi quyết định tự mình xác minh lời tuyên bố của Tòa án. Nếu cần, cô sẵn sàng giao chiến với Sentinel để kích hoạt Lần Cộng Hưởng Thứ Hai, dù phải đánh đổi cả tính mạng.</t>
         </is>
       </c>
     </row>
@@ -29088,7 +29075,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Con đường duy nhất để thoát là đốt cháy Quả Cầu Sonoro mà không làm tổn thương ai bên trong. Điều đó đòi hỏi sự điều khiển Forte điêu luyện. Nghĩ lại, có lẽ đó là bài test cuối cùng hắn dành cho ta.</t>
+          <t>Con đường duy nhất để thoát là đốt cháy Sonoro Sphere mà không làm tổn thương ai bên trong. Điều đó đòi hỏi sự điều khiển Forte điêu luyện. Nghĩ lại, có lẽ đó là bài kiểm tra cuối cùng hắn dành cho ta.</t>
         </is>
       </c>
     </row>
@@ -29478,7 +29465,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Resonator dạy ta về "Forte" bảo nếu không dùng nó cho đúng, ta sẽ chết sớm.</t>
+          <t>Resonator dạy tao về "Forte" bảo nếu không dùng nó cho đúng, tao sẽ chết sớm.</t>
         </is>
       </c>
     </row>
@@ -30518,7 +30505,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Ừ, ta hiếm khi phải dùng đến Forte trong cuộc sống hàng ngày.</t>
+          <t>Ừ, tao hiếm khi phải dùng đến Forte trong cuộc sống hàng ngày.</t>
         </is>
       </c>
     </row>
@@ -30648,7 +30635,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Yes. Có thể liên quan đến Khả Năng của ta...</t>
+          <t>Đúng vậy. Có thể liên quan đến Khả Năng của ta...</t>
         </is>
       </c>
     </row>
@@ -30908,7 +30895,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Cô ấy đã từng thấy tớ sử dụng năng lực Resonance một lần.</t>
+          <t>Cô ấy đã từng thấy tớ sử dụng năng lực Cộng Hưởng một lần.</t>
         </is>
       </c>
     </row>
@@ -30973,7 +30960,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Theo ta, lũ quái vật này là một loại Discord mới. Vì chưa được ghi nhận, Terminal của chúng ta không thể kích hoạt cảnh báo khi chúng xuất hiện gần đây.</t>
+          <t>Theo ta, lũ quái vật này là một loại Tacet Discord mới. Vì chưa được ghi nhận, Thiết bị đầu cuối của chúng ta không thể kích hoạt cảnh báo khi chúng xuất hiện gần đây.</t>
         </is>
       </c>
     </row>
@@ -31103,7 +31090,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Tất nhiên, tác phẩm này sở hữu một sức sống chân thực mà không thứ gì khác có thể sánh bằng, tất cả đều nhờ khả năng Resonance của Nghệ Nhân Bí Ẩn—Mingyan.</t>
+          <t>Tất nhiên, tác phẩm này sở hữu một sức sống chân thực mà không thứ gì khác có thể sánh bằng, tất cả đều nhờ khả năng Cộng Hưởng của Nghệ Nhân Bí Ẩn—Mingyan.</t>
         </is>
       </c>
     </row>
@@ -31428,7 +31415,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Zhezhi đoán rằng có thể một con Gulpuff đã trốn khỏi studio. Dù giả thuyết này có vẻ không mấy thuyết phục, cậu vẫn trân trọng nỗ lực của cô bé, khiến Zhezhi càng thêm quyết tâm thử lại. Ấn tượng trước khả năng sử dụng Forte của cô, cậu biết được Zhezhi hiếm khi dùng năng lực Resonance của mình. Zhezhi thú nhận rằng Forte của cô có Dodget giống với của Mingyan, và có lẽ vì thế mà nó liên quan đến cơn thịnh nộ bất thường của Mingyan.</t>
+          <t>Zhezhi đoán rằng có thể một con Gulpuff đã trốn khỏi studio. Dù giả thuyết này có vẻ không mấy thuyết phục, cậu vẫn trân trọng nỗ lực của cô bé, khiến Zhezhi càng thêm quyết tâm thử lại. Ấn tượng trước khả năng sử dụng Forte của cô, cậu biết được Zhezhi hiếm khi dùng năng lực Cộng Hưởng của mình. Zhezhi thú nhận rằng Forte của cô có nét giống với của Mingyan, và có lẽ vì thế mà nó liên quan đến cơn thịnh nộ bất thường của Mingyan.</t>
         </is>
       </c>
     </row>
@@ -31558,7 +31545,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Zhezhi đối diện với quá khứ và làm chủ Âm Sắc của mình, sẵn sàng sử dụng nó để chứng minh năng lực và gánh vác trách nhiệm đi kèm với tài năng ấy.</t>
+          <t>Triết Chi đối diện với quá khứ và làm chủ Âm Sắc của mình, sẵn sàng sử dụng nó để chứng minh năng lực và gánh vác trách nhiệm đi kèm với tài năng ấy.</t>
         </is>
       </c>
     </row>
@@ -31818,7 +31805,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Huh Ta thấy câu đó cộng hưởng tốt mà. Kiện ta đi!</t>
+          <t>Hử? Tao thấy câu đó cộng hưởng tốt mà. Kiện tao đi!</t>
         </is>
       </c>
     </row>
@@ -32208,7 +32195,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Nếu chúng ta dùng Forte thì sao?</t>
+          <t>Nếu dùng Forte thì sao nhỉ?</t>
         </is>
       </c>
     </row>
@@ -32338,7 +32325,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Một Người Mang Hoa với Forte là điều khiển trọng lực... Ta đã tra cứu tất cả hồ sơ về Resonators lẫn Người Mang Hoa, nhưng không thấy ai trùng khớp với mô tả của ngươi.</t>
+          <t>Một Người Mang Hoa với Forte là điều khiển trọng lực... Ta đã tra cứu tất cả hồ sơ về Resonator lẫn Người Mang Hoa, nhưng không thấy ai trùng khớp với mô tả của ngươi.</t>
         </is>
       </c>
     </row>
@@ -32598,7 +32585,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Đúng vậy, đó là lý do Tethys Hệ thống phái chúng ta đến định vị và thu hồi tần số này càng sớm càng tốt, để ngăn chặn một thảm họa tiềm tàng.</t>
+          <t>Đúng vậy, đó là lý do Hệ Thống Tethys phái chúng ta đến định vị và thu hồi tần số này càng sớm càng tốt, để ngăn chặn một thảm họa tiềm tàng.</t>
         </is>
       </c>
     </row>
@@ -32663,7 +32650,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Port City of Guixu đã bị Lament tàn phá. Nếu tần số này không được kiểm soát, nó có thể gây ra một thảm họa khác...</t>
+          <t>Thành Phố Cảng Guixu đã bị Lament tàn phá. Nếu tần số này không được kiểm soát, nó có thể gây ra một thảm họa khác...</t>
         </is>
       </c>
     </row>
@@ -32728,7 +32715,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Tại Port City of Guixu, ngươi gặp Niya, một Người Mang Hoa, người nhanh chóng nhận ra ngươi. Cô cảnh báo về một tần số bất thường được phát hiện ở Guixu cần phải được đưa gấp về Bờ Đen. Nếu không giải quyết, nó có thể kích hoạt một Lament khác...</t>
+          <t>Tại Thành Phố Cảng Guixu, ngươi gặp Niya, một Người Mang Hoa, người nhanh chóng nhận ra ngươi. Cô cảnh báo về một tần số bất thường được phát hiện ở Guixu cần phải được đưa gấp về Bờ Đen. Nếu không giải quyết, nó có thể kích hoạt một Lament khác...</t>
         </is>
       </c>
     </row>
@@ -32793,7 +32780,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Astral Modulator, Người Dẫn Dắt Văn Minh, Bậc Thầy Bờ Đen... những danh hiệu này phản ánh những thành tựu của ngươi. Trên bầu trời ngầm đầy sao, Sao Chết vụt lao đi như một thiên thạch. The Shorekeeper yêu cầu ngươi tìm lại Sao Chết và khôi phục cân bằng tại Modulation Hall.</t>
+          <t>Bộ Điều Tần Tinh Tú, Người Dẫn Dắt Văn Minh, Bậc Thầy Bờ Đen... những danh hiệu này phản ánh những thành tựu của ngươi. Trên bầu trời ngầm đầy sao, Sao Chết vụt lao đi như một thiên thạch. Người Gác Bờ yêu cầu ngươi tìm lại Sao Chết và khôi phục cân bằng tại Đại Sảnh Điều Tần.</t>
         </is>
       </c>
     </row>
@@ -32923,7 +32910,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Trời &lt;i&gt;bleep&lt;/i&gt; ạ! Giảm kích thước bộ nhớ đi! Đừng dành quá nhiều không gian xử lý cho lỗi nữa!</t>
+          <t>Mẹ kiếp! Giảm kích thước bộ nhớ đi! Đừng để lỗi chiếm quá nhiều tài nguyên xử lý!</t>
         </is>
       </c>
     </row>
@@ -32988,7 +32975,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>The Tethys Hệ thống thao túng Necrostar, cố gắng nuốt chửng cậu để biến cậu thành lõi của nó. Trong nỗ lực tuyệt vọng để cứu cậu, Shorekeeper đã bị nuốt chửng vào bên trong Necrostar. Khi tỉnh dậy, cậu thấy mình đang ở nơi sâu thẳm nhất của The Tethys Hệ thống, được gọi là "End Lang Thang". Trong khoảnh khắc cuối cùng, Shorekeeper đã nói lời từ biệt với cậu.</t>
+          <t>Hệ Thống Tethys thao túng Necrostar, cố gắng nuốt chửng cậu để biến cậu thành lõi của nó. Trong nỗ lực tuyệt vọng để cứu cậu, Shorekeeper đã bị nuốt chửng vào bên trong Necrostar. Khi tỉnh dậy, cậu thấy mình đang ở nơi sâu thẳm nhất của Hệ Thống Tethys, được gọi là "Kết Thúc Lang Thang". Trong khoảnh khắc cuối cùng, Shorekeeper đã nói lời từ biệt với cậu.</t>
         </is>
       </c>
     </row>
@@ -33313,7 +33300,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Xác nhận mục tiêu: Quản gia trưởng.</t>
+          <t>Xác nhận mục tiêu: Quản gia Trưởng.</t>
         </is>
       </c>
     </row>
@@ -33573,7 +33560,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Xác nhận mục tiêu: Quản gia trưởng.</t>
+          <t>Xác nhận mục tiêu: Quản gia Trưởng.</t>
         </is>
       </c>
     </row>
